--- a/Case Size.xlsx
+++ b/Case Size.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\product catalogue\product catalogue app v2\.claude\worktrees\youthful-dhawan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478C4E3F-C5EB-4338-8716-16C1C669B462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3FD38F-9D45-47F5-854C-7B6271E4771C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="248">
   <si>
     <t>Description</t>
   </si>
@@ -623,19 +623,191 @@
   </si>
   <si>
     <t>PREMIUM MASALA INCENSE (Hexa 15Stik)</t>
+  </si>
+  <si>
+    <t>SMUDGE CANDLE 90 GMS</t>
+  </si>
+  <si>
+    <t>"1 pack Contain -7 pcs of Tea light Candles.12 pcs packed in 1 Outer Carton.6 Outer Cartons in 1 Master Carton"</t>
+  </si>
+  <si>
+    <t>"1 pack Contain - 10 pcs of Tea light Candles.12 pcs packed in 1 Outer Carton.6 Outer Cartons in 1 Master Carton"</t>
+  </si>
+  <si>
+    <t>Glass Jar Smudge Candle 185 gms</t>
+  </si>
+  <si>
+    <t>Manifestation Candles</t>
+  </si>
+  <si>
+    <t>Manifestation series candles are designed to help you focus your intentions and channel positive energy toward your goals. Each candle is crafted with specific colors, scents, and symbols to align with different aspirations, such as love, abundance, or peace</t>
+  </si>
+  <si>
+    <t>36 Pcs</t>
+  </si>
+  <si>
+    <t>7 chakra</t>
+  </si>
+  <si>
+    <t>450 gm of 7 chakra colored uncensted candle with a burning time of 7 days. 12 pcs in one master carton</t>
+  </si>
+  <si>
+    <t>"194 g 7 Chakra Candle Set featuring 7 colored unscented candles.
+Packed 48 sets per master carton."</t>
+  </si>
+  <si>
+    <t>4 Doz</t>
+  </si>
+  <si>
+    <t>48Pcs</t>
+  </si>
+  <si>
+    <t>Spell Candle</t>
+  </si>
+  <si>
+    <t>"Candle Chime Set – Practical, colorful, and fun! This versatile spiritual candle assortment is perfect for chime holders, pagan altars, magic spells, ceremonies, parties, or everyday home décor.Extended Burn Time: Each 4-inch tall unscented candle burns continuously for up to 2 hours.Vibrant Variety: The set includes 40 candle sticks in 5 colors, letting you create striking decorations.
+"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48 Pcs </t>
+  </si>
+  <si>
+    <t>Candle catalogue</t>
+  </si>
+  <si>
+    <t>Sacred element catalogue</t>
+  </si>
+  <si>
+    <t>Affirmation Ritual Kit</t>
+  </si>
+  <si>
+    <t>10 Sticks in one pack with Crystal and Cards with Affirmation. 1 doz in one Outer</t>
+  </si>
+  <si>
+    <t>144 pcs</t>
+  </si>
+  <si>
+    <t>Balanced Living Incense Pouch</t>
+  </si>
+  <si>
+    <t>6 Pouches in one pack</t>
+  </si>
+  <si>
+    <t>CONES SACRED ELEMENT ORGANIC</t>
+  </si>
+  <si>
+    <t>5 cones</t>
+  </si>
+  <si>
+    <t>36 Doz</t>
+  </si>
+  <si>
+    <t>ENERGY CLEANSING KIT</t>
+  </si>
+  <si>
+    <t>24 Pack</t>
+  </si>
+  <si>
+    <t>Manifestation candle 185 grms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glass Jar 185 grams Candle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Doz </t>
+  </si>
+  <si>
+    <t>24 pcs</t>
+  </si>
+  <si>
+    <t>QATARI POWDER HEXA PACK</t>
+  </si>
+  <si>
+    <t>Paper hexa shape 50grams in a golden pouch with wooden spoon. 12 Hexa Qatari Incense Powder in one Display Box</t>
+  </si>
+  <si>
+    <t>SCARED ELEMENTS MANIFESTATION INCENSE</t>
+  </si>
+  <si>
+    <t>15 gms in one pack, 6 Fragrances x 2 in one dispenser outer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Dox </t>
+  </si>
+  <si>
+    <t>SMUDGE CANDLE 185 GMS</t>
+  </si>
+  <si>
+    <t>2 doz</t>
+  </si>
+  <si>
+    <t>Sacred Element Organic Incense Sticks 10 sticks</t>
+  </si>
+  <si>
+    <t>Product - 10 Sticks</t>
+  </si>
+  <si>
+    <t>24 doz</t>
+  </si>
+  <si>
+    <t>Sacred Element Organic Incense Sticks 8 sticks</t>
+  </si>
+  <si>
+    <t>Product - 8 Sticks</t>
+  </si>
+  <si>
+    <t>Sacred Element Room Spray</t>
+  </si>
+  <si>
+    <t>Sacred Elements Dual Series Masala 15gm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 Doz </t>
+  </si>
+  <si>
+    <t>Sacred Elements Jumbo 16</t>
+  </si>
+  <si>
+    <t>Sacred Elements Spiritual Series Masala 15gm</t>
+  </si>
+  <si>
+    <t>Smudge Balls</t>
+  </si>
+  <si>
+    <t>4 Balls in one pack - 2 doz in one inner corrogated box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 Dox </t>
+  </si>
+  <si>
+    <t>Smudge Organic Disc</t>
+  </si>
+  <si>
+    <t>4 Disc in one pack- 2 doz in one inner corrogated box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 doz </t>
+  </si>
+  <si>
+    <t>WITCHCRAFT POUCH</t>
+  </si>
+  <si>
+    <t>144 Pcs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Doz </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -669,8 +841,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -689,6 +869,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="19">
     <border>
@@ -930,7 +1116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1061,9 +1247,6 @@
     <xf numFmtId="165" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1083,9 +1266,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1125,15 +1305,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1160,6 +1331,30 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1185,1238 +1380,10 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Master_infoCase_Size (2)"/>
       <sheetName val="Master_infoCase_Size"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="96">
-          <cell r="A96" t="str">
-            <v>Tall Hexa 10 Doz</v>
-          </cell>
-          <cell r="G96">
-            <v>45.1</v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="A97" t="str">
-            <v>8 FH 600 Pcs</v>
-          </cell>
-          <cell r="G97">
-            <v>34</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="A98" t="str">
-            <v>Gift Pack 58 SET</v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="A99" t="str">
-            <v>WDB MI 4 Pcs</v>
-          </cell>
-          <cell r="G99">
-            <v>34</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="A100" t="str">
-            <v>WDB MI 6 Pcs</v>
-          </cell>
-          <cell r="G100">
-            <v>34</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="A101" t="str">
-            <v>SE OS 12 Doz</v>
-          </cell>
-          <cell r="G101">
-            <v>24.1</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="A102" t="str">
-            <v>10 FH 60 Pcs</v>
-          </cell>
-          <cell r="G102">
-            <v>38</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="A103" t="str">
-            <v>Coffin Box 60 PCS</v>
-          </cell>
-          <cell r="G103">
-            <v>20</v>
-          </cell>
-        </row>
-        <row r="104">
-          <cell r="A104" t="str">
-            <v>Hexa 66 Doz</v>
-          </cell>
-          <cell r="G104">
-            <v>69</v>
-          </cell>
-        </row>
-        <row r="105">
-          <cell r="A105" t="str">
-            <v>Square 48 Box (OP)</v>
-          </cell>
-          <cell r="G105">
-            <v>56</v>
-          </cell>
-        </row>
-        <row r="106">
-          <cell r="A106" t="str">
-            <v>Scentwrap Spray 180 PCS</v>
-          </cell>
-        </row>
-        <row r="107">
-          <cell r="A107" t="str">
-            <v>SMC Candle 6 Pcs</v>
-          </cell>
-        </row>
-        <row r="108">
-          <cell r="A108" t="str">
-            <v>Reed Diffuser 12 SET</v>
-          </cell>
-          <cell r="G108">
-            <v>44</v>
-          </cell>
-        </row>
-        <row r="109">
-          <cell r="A109" t="str">
-            <v>Incense Holder 60 PCS</v>
-          </cell>
-          <cell r="G109">
-            <v>38</v>
-          </cell>
-        </row>
-        <row r="110">
-          <cell r="A110" t="str">
-            <v>CL Wax Diya 48 SET</v>
-          </cell>
-          <cell r="G110">
-            <v>33</v>
-          </cell>
-        </row>
-        <row r="111">
-          <cell r="A111" t="str">
-            <v>CL Wax Diya 28 SET</v>
-          </cell>
-          <cell r="G111">
-            <v>38</v>
-          </cell>
-        </row>
-        <row r="112">
-          <cell r="A112" t="str">
-            <v>CL Wax Diya 47 SET</v>
-          </cell>
-          <cell r="G112">
-            <v>38</v>
-          </cell>
-        </row>
-        <row r="113">
-          <cell r="A113" t="str">
-            <v>Coffin Box 30 PCS -HEXA</v>
-          </cell>
-          <cell r="G113">
-            <v>35</v>
-          </cell>
-        </row>
-        <row r="114">
-          <cell r="A114" t="str">
-            <v>Wooden Tower 30 PCS+ HEXA</v>
-          </cell>
-          <cell r="G114">
-            <v>48</v>
-          </cell>
-        </row>
-        <row r="115">
-          <cell r="A115" t="str">
-            <v>Hexa 50 SET (GBH)</v>
-          </cell>
-          <cell r="G115">
-            <v>46.5</v>
-          </cell>
-        </row>
-        <row r="116">
-          <cell r="A116" t="str">
-            <v>Bag 50 Pcs</v>
-          </cell>
-        </row>
-        <row r="117">
-          <cell r="A117" t="str">
-            <v>Free Samples 12 Pcs</v>
-          </cell>
-        </row>
-        <row r="118">
-          <cell r="A118" t="str">
-            <v>Smudge Candle 24 Pcs</v>
-          </cell>
-          <cell r="G118">
-            <v>38</v>
-          </cell>
-        </row>
-        <row r="119">
-          <cell r="A119" t="str">
-            <v>Burner 60 PCS</v>
-          </cell>
-          <cell r="G119">
-            <v>48.5</v>
-          </cell>
-        </row>
-        <row r="120">
-          <cell r="A120" t="str">
-            <v>Cone Holder 36 Pcs</v>
-          </cell>
-          <cell r="G120">
-            <v>36</v>
-          </cell>
-        </row>
-        <row r="121">
-          <cell r="A121" t="str">
-            <v>Wooden Tower 30 PCS</v>
-          </cell>
-          <cell r="G121">
-            <v>48</v>
-          </cell>
-        </row>
-        <row r="122">
-          <cell r="A122" t="str">
-            <v>Coffin Box 30 PCS</v>
-          </cell>
-          <cell r="G122">
-            <v>36</v>
-          </cell>
-        </row>
-        <row r="123">
-          <cell r="A123" t="str">
-            <v>Cones Display 4 Unit</v>
-          </cell>
-          <cell r="G123">
-            <v>49.5</v>
-          </cell>
-        </row>
-        <row r="124">
-          <cell r="A124" t="str">
-            <v>Sample 1000 Pc</v>
-          </cell>
-        </row>
-        <row r="125">
-          <cell r="A125" t="str">
-            <v>Room Spray 84 Pcs</v>
-          </cell>
-          <cell r="G125">
-            <v>29</v>
-          </cell>
-        </row>
-        <row r="126">
-          <cell r="A126" t="str">
-            <v>Pooja Oil 40 PCS</v>
-          </cell>
-          <cell r="G126">
-            <v>40.5</v>
-          </cell>
-        </row>
-        <row r="127">
-          <cell r="A127" t="str">
-            <v>DISPLAY 30 PCS</v>
-          </cell>
-        </row>
-        <row r="128">
-          <cell r="A128" t="str">
-            <v>Sample 68 Pcs</v>
-          </cell>
-        </row>
-        <row r="129">
-          <cell r="A129" t="str">
-            <v>Cone Holder 300 Pcs</v>
-          </cell>
-          <cell r="G129">
-            <v>36</v>
-          </cell>
-        </row>
-        <row r="130">
-          <cell r="A130" t="str">
-            <v>Cone Holder 100 Pcs</v>
-          </cell>
-          <cell r="G130">
-            <v>34</v>
-          </cell>
-        </row>
-        <row r="131">
-          <cell r="A131" t="str">
-            <v>5 PYR 150 Pcs</v>
-          </cell>
-          <cell r="G131">
-            <v>38</v>
-          </cell>
-        </row>
-        <row r="132">
-          <cell r="A132" t="str">
-            <v>Cone Holder 30 Pcs</v>
-          </cell>
-          <cell r="G132">
-            <v>36</v>
-          </cell>
-        </row>
-        <row r="133">
-          <cell r="A133" t="str">
-            <v>Cone Holder 60 Pcs</v>
-          </cell>
-          <cell r="G133">
-            <v>36</v>
-          </cell>
-        </row>
-        <row r="134">
-          <cell r="A134" t="str">
-            <v>WB 18 PCS</v>
-          </cell>
-          <cell r="G134">
-            <v>34</v>
-          </cell>
-        </row>
-        <row r="135">
-          <cell r="A135" t="str">
-            <v>BFC BUR SET 12 PCS</v>
-          </cell>
-          <cell r="G135">
-            <v>48</v>
-          </cell>
-        </row>
-        <row r="136">
-          <cell r="A136" t="str">
-            <v>Stones 72 SET</v>
-          </cell>
-          <cell r="G136">
-            <v>32.4</v>
-          </cell>
-        </row>
-        <row r="137">
-          <cell r="A137" t="str">
-            <v>Big Cone 9 Pcs</v>
-          </cell>
-        </row>
-        <row r="138">
-          <cell r="A138" t="str">
-            <v>10 FH 600 Pcs</v>
-          </cell>
-          <cell r="G138">
-            <v>36</v>
-          </cell>
-        </row>
-        <row r="139">
-          <cell r="A139" t="str">
-            <v>Scentwraps 11 4 UNT</v>
-          </cell>
-          <cell r="G139">
-            <v>51.3</v>
-          </cell>
-        </row>
-        <row r="140">
-          <cell r="A140" t="str">
-            <v>Jumbo 10 Doz</v>
-          </cell>
-          <cell r="G140">
-            <v>54.3</v>
-          </cell>
-        </row>
-        <row r="141">
-          <cell r="A141" t="str">
-            <v>AOD 4 Set</v>
-          </cell>
-          <cell r="G141">
-            <v>45.5</v>
-          </cell>
-        </row>
-        <row r="142">
-          <cell r="A142" t="str">
-            <v>Ass SceWrap Spray 180 PCS</v>
-          </cell>
-        </row>
-        <row r="143">
-          <cell r="A143" t="str">
-            <v>Frag Sachet 12 Doz</v>
-          </cell>
-        </row>
-        <row r="144">
-          <cell r="A144" t="str">
-            <v>Frag Sachet 36 Doz</v>
-          </cell>
-          <cell r="G144">
-            <v>53.5</v>
-          </cell>
-        </row>
-        <row r="145">
-          <cell r="A145" t="str">
-            <v>Drm catcher 100 PC</v>
-          </cell>
-        </row>
-        <row r="146">
-          <cell r="A146" t="str">
-            <v>Display Hexa 10 Pcs</v>
-          </cell>
-          <cell r="G146">
-            <v>70</v>
-          </cell>
-        </row>
-        <row r="147">
-          <cell r="A147" t="str">
-            <v>Drm catcher 50 PC</v>
-          </cell>
-        </row>
-        <row r="148">
-          <cell r="A148" t="str">
-            <v>Drm catcher 11 PC</v>
-          </cell>
-        </row>
-        <row r="149">
-          <cell r="A149" t="str">
-            <v>Scentwraps 19 2 UNT</v>
-          </cell>
-          <cell r="G149">
-            <v>36</v>
-          </cell>
-        </row>
-        <row r="150">
-          <cell r="A150" t="str">
-            <v>Loose 100 Gm 10 Doz</v>
-          </cell>
-          <cell r="G150">
-            <v>67</v>
-          </cell>
-        </row>
-        <row r="151">
-          <cell r="A151" t="str">
-            <v>Sage Herb 500 bundle</v>
-          </cell>
-          <cell r="G151">
-            <v>650</v>
-          </cell>
-        </row>
-        <row r="152">
-          <cell r="A152" t="str">
-            <v>Family Pack 4 Doz</v>
-          </cell>
-          <cell r="G152">
-            <v>58.5</v>
-          </cell>
-        </row>
-        <row r="153">
-          <cell r="A153" t="str">
-            <v>Flexo Pack 60 Doz</v>
-          </cell>
-          <cell r="G153">
-            <v>58</v>
-          </cell>
-        </row>
-        <row r="154">
-          <cell r="A154" t="str">
-            <v>Drm catcher 200 PCS</v>
-          </cell>
-        </row>
-        <row r="155">
-          <cell r="A155" t="str">
-            <v>Tall Box 20 Doz</v>
-          </cell>
-        </row>
-        <row r="156">
-          <cell r="A156" t="str">
-            <v>Scentwrap11 96 Pac</v>
-          </cell>
-          <cell r="G156">
-            <v>42</v>
-          </cell>
-        </row>
-        <row r="157">
-          <cell r="A157" t="str">
-            <v>Pouch 24 Doz</v>
-          </cell>
-          <cell r="G157">
-            <v>37</v>
-          </cell>
-        </row>
-        <row r="158">
-          <cell r="A158" t="str">
-            <v>Masala 15 Gm 30 Doz</v>
-          </cell>
-          <cell r="G158">
-            <v>41.5</v>
-          </cell>
-        </row>
-        <row r="159">
-          <cell r="A159" t="str">
-            <v>Roll On 6 Doz</v>
-          </cell>
-          <cell r="G159">
-            <v>44.5</v>
-          </cell>
-        </row>
-        <row r="160">
-          <cell r="A160" t="str">
-            <v>Ess Pr Oil 6 Doz</v>
-          </cell>
-          <cell r="G160">
-            <v>44.5</v>
-          </cell>
-        </row>
-        <row r="161">
-          <cell r="A161" t="str">
-            <v>Aroma Pr Oil 12 Doz</v>
-          </cell>
-          <cell r="G161">
-            <v>44.5</v>
-          </cell>
-        </row>
-        <row r="162">
-          <cell r="A162" t="str">
-            <v>Masala 15 Gm 40 Doz</v>
-          </cell>
-          <cell r="G162">
-            <v>50.5</v>
-          </cell>
-        </row>
-        <row r="163">
-          <cell r="A163" t="str">
-            <v>Pure Ghee Diya 72 PC</v>
-          </cell>
-          <cell r="G163">
-            <v>61</v>
-          </cell>
-        </row>
-        <row r="164">
-          <cell r="A164" t="str">
-            <v>Pure Cow Ghee Diya 72 PC</v>
-          </cell>
-          <cell r="G164">
-            <v>61</v>
-          </cell>
-        </row>
-        <row r="165">
-          <cell r="A165" t="str">
-            <v>Pure Ghee Diya 48 PC</v>
-          </cell>
-          <cell r="G165">
-            <v>61</v>
-          </cell>
-        </row>
-        <row r="166">
-          <cell r="A166" t="str">
-            <v>Pure Cow Ghee Diya 48 PC</v>
-          </cell>
-          <cell r="G166">
-            <v>61</v>
-          </cell>
-        </row>
-        <row r="167">
-          <cell r="A167" t="str">
-            <v>Masala 50 Doz</v>
-          </cell>
-          <cell r="G167">
-            <v>66</v>
-          </cell>
-        </row>
-        <row r="168">
-          <cell r="A168" t="str">
-            <v>Masala 50 Gm 24 Doz</v>
-          </cell>
-          <cell r="G168">
-            <v>50</v>
-          </cell>
-        </row>
-        <row r="169">
-          <cell r="A169" t="str">
-            <v>Mini Jumbo 10 Doz</v>
-          </cell>
-          <cell r="G169">
-            <v>37</v>
-          </cell>
-        </row>
-        <row r="170">
-          <cell r="A170" t="str">
-            <v>Top Table 4 UNT 60 Pkt</v>
-          </cell>
-          <cell r="G170">
-            <v>62</v>
-          </cell>
-        </row>
-        <row r="171">
-          <cell r="A171" t="str">
-            <v>STEP RETAIL READY 2 UNT</v>
-          </cell>
-        </row>
-        <row r="172">
-          <cell r="A172" t="str">
-            <v>Gift Pack 120 Pcs</v>
-          </cell>
-        </row>
-        <row r="173">
-          <cell r="A173" t="str">
-            <v>Gift Pack 56 Pac</v>
-          </cell>
-          <cell r="G173">
-            <v>54</v>
-          </cell>
-        </row>
-        <row r="174">
-          <cell r="A174" t="str">
-            <v>Gift Pack 48 SET</v>
-          </cell>
-          <cell r="G174">
-            <v>40</v>
-          </cell>
-        </row>
-        <row r="175">
-          <cell r="A175" t="str">
-            <v>Airfreshner Spray 48 Pcs</v>
-          </cell>
-          <cell r="G175">
-            <v>45</v>
-          </cell>
-        </row>
-        <row r="176">
-          <cell r="A176" t="str">
-            <v>Ess Oil 12 Doz</v>
-          </cell>
-          <cell r="G176">
-            <v>400</v>
-          </cell>
-        </row>
-        <row r="177">
-          <cell r="A177" t="str">
-            <v>Gift Pack 52 Pcs</v>
-          </cell>
-          <cell r="G177">
-            <v>58.5</v>
-          </cell>
-        </row>
-        <row r="178">
-          <cell r="A178" t="str">
-            <v>SE OS 24 Doz</v>
-          </cell>
-          <cell r="G178">
-            <v>47.5</v>
-          </cell>
-        </row>
-        <row r="179">
-          <cell r="A179" t="str">
-            <v>Jumbo BFC 12 Doz</v>
-          </cell>
-          <cell r="G179">
-            <v>36</v>
-          </cell>
-        </row>
-        <row r="180">
-          <cell r="A180" t="str">
-            <v>SMC Candle 72 Pcs</v>
-          </cell>
-          <cell r="G180">
-            <v>36</v>
-          </cell>
-        </row>
-        <row r="181">
-          <cell r="A181" t="str">
-            <v>Gift Pack 36 PCS</v>
-          </cell>
-          <cell r="G181">
-            <v>42</v>
-          </cell>
-        </row>
-        <row r="182">
-          <cell r="A182" t="str">
-            <v>Pooja Oil 20 Pcs</v>
-          </cell>
-          <cell r="G182">
-            <v>40.5</v>
-          </cell>
-        </row>
-        <row r="183">
-          <cell r="A183" t="str">
-            <v>Spray 4 UNT (80 Bottles)</v>
-          </cell>
-          <cell r="G183">
-            <v>40</v>
-          </cell>
-        </row>
-        <row r="184">
-          <cell r="A184" t="str">
-            <v>Pouch 20 Gms 48 Doz</v>
-          </cell>
-        </row>
-        <row r="185">
-          <cell r="A185" t="str">
-            <v>Pouch 144 Pcs</v>
-          </cell>
-          <cell r="G185">
-            <v>41</v>
-          </cell>
-        </row>
-        <row r="186">
-          <cell r="A186" t="str">
-            <v>Masala Display 4 Unit</v>
-          </cell>
-          <cell r="G186">
-            <v>78</v>
-          </cell>
-        </row>
-        <row r="187">
-          <cell r="A187" t="str">
-            <v>SMC Candle 24 SET</v>
-          </cell>
-          <cell r="G187">
-            <v>36</v>
-          </cell>
-        </row>
-        <row r="188">
-          <cell r="A188" t="str">
-            <v>Frag Oil 12 Doz</v>
-          </cell>
-          <cell r="G188">
-            <v>29</v>
-          </cell>
-        </row>
-        <row r="189">
-          <cell r="A189" t="str">
-            <v>10 FH 50 Doz</v>
-          </cell>
-          <cell r="G189">
-            <v>34</v>
-          </cell>
-        </row>
-        <row r="190">
-          <cell r="A190" t="str">
-            <v>Candle 24 Pcs</v>
-          </cell>
-          <cell r="G190">
-            <v>36.5</v>
-          </cell>
-        </row>
-        <row r="191">
-          <cell r="A191" t="str">
-            <v>Pure Ghee Diya 50 PC</v>
-          </cell>
-          <cell r="G191">
-            <v>610</v>
-          </cell>
-        </row>
-        <row r="192">
-          <cell r="A192" t="str">
-            <v>Pure Cow Ghee Diya 50 PC</v>
-          </cell>
-          <cell r="G192">
-            <v>61</v>
-          </cell>
-        </row>
-        <row r="193">
-          <cell r="A193" t="str">
-            <v>Tall Box 24 Doz</v>
-          </cell>
-          <cell r="G193">
-            <v>39.5</v>
-          </cell>
-        </row>
-        <row r="194">
-          <cell r="A194" t="str">
-            <v>Car Air Freshener 96 Pcs</v>
-          </cell>
-          <cell r="G194">
-            <v>33</v>
-          </cell>
-        </row>
-        <row r="195">
-          <cell r="A195" t="str">
-            <v>Spray 36 SET</v>
-          </cell>
-          <cell r="G195">
-            <v>28</v>
-          </cell>
-        </row>
-        <row r="196">
-          <cell r="A196" t="str">
-            <v>Pouch 12 Doz</v>
-          </cell>
-          <cell r="G196">
-            <v>41</v>
-          </cell>
-        </row>
-        <row r="197">
-          <cell r="A197" t="str">
-            <v>Hexa 50 SET</v>
-          </cell>
-          <cell r="G197">
-            <v>46.5</v>
-          </cell>
-        </row>
-        <row r="198">
-          <cell r="A198" t="str">
-            <v>Sample 2500 Pc</v>
-          </cell>
-          <cell r="G198">
-            <v>410</v>
-          </cell>
-        </row>
-        <row r="199">
-          <cell r="A199" t="str">
-            <v>Resins Dhoop 48 Box</v>
-          </cell>
-          <cell r="G199">
-            <v>37.5</v>
-          </cell>
-        </row>
-        <row r="200">
-          <cell r="A200" t="str">
-            <v>10 FH 450 Pcs</v>
-          </cell>
-          <cell r="G200">
-            <v>34</v>
-          </cell>
-        </row>
-        <row r="201">
-          <cell r="A201" t="str">
-            <v>10 FH 800 Pcs</v>
-          </cell>
-          <cell r="G201">
-            <v>34</v>
-          </cell>
-        </row>
-        <row r="202">
-          <cell r="A202" t="str">
-            <v>Dhoop 24 Doz</v>
-          </cell>
-          <cell r="G202">
-            <v>45</v>
-          </cell>
-        </row>
-        <row r="203">
-          <cell r="A203" t="str">
-            <v>Aroma Oil 12 Doz</v>
-          </cell>
-          <cell r="G203">
-            <v>29</v>
-          </cell>
-        </row>
-        <row r="204">
-          <cell r="A204" t="str">
-            <v>Hexa Gift Pack 48 Pcs</v>
-          </cell>
-          <cell r="G204">
-            <v>39.200000000000003</v>
-          </cell>
-        </row>
-        <row r="205">
-          <cell r="A205" t="str">
-            <v>Cone 24 Doz (Asrt 4 Dz)</v>
-          </cell>
-          <cell r="G205">
-            <v>39</v>
-          </cell>
-        </row>
-        <row r="206">
-          <cell r="A206" t="str">
-            <v>Coaster 60 Pcs</v>
-          </cell>
-          <cell r="G206">
-            <v>45</v>
-          </cell>
-        </row>
-        <row r="207">
-          <cell r="A207" t="str">
-            <v>BFC Holder 24 Pc</v>
-          </cell>
-          <cell r="G207">
-            <v>68.58</v>
-          </cell>
-        </row>
-        <row r="208">
-          <cell r="A208" t="str">
-            <v>None</v>
-          </cell>
-        </row>
-        <row r="209">
-          <cell r="A209" t="str">
-            <v>12 TWR 30 Pcs</v>
-          </cell>
-          <cell r="G209">
-            <v>48</v>
-          </cell>
-        </row>
-        <row r="210">
-          <cell r="A210" t="str">
-            <v>12 FH 600 Pcs</v>
-          </cell>
-        </row>
-        <row r="211">
-          <cell r="A211" t="str">
-            <v>12 CB 30 Pcs</v>
-          </cell>
-          <cell r="G211">
-            <v>36</v>
-          </cell>
-        </row>
-        <row r="212">
-          <cell r="A212" t="str">
-            <v>10 FH 660 Pcs</v>
-          </cell>
-          <cell r="G212">
-            <v>44</v>
-          </cell>
-        </row>
-        <row r="213">
-          <cell r="A213" t="str">
-            <v>4 PYR 60 Pcs</v>
-          </cell>
-          <cell r="G213">
-            <v>48</v>
-          </cell>
-        </row>
-        <row r="214">
-          <cell r="A214" t="str">
-            <v>Wax Melts 96 Pcs</v>
-          </cell>
-          <cell r="G214">
-            <v>61</v>
-          </cell>
-        </row>
-        <row r="215">
-          <cell r="A215" t="str">
-            <v>Zipper 4 in 1 Pouch 6 Doz</v>
-          </cell>
-          <cell r="G215">
-            <v>30</v>
-          </cell>
-        </row>
-        <row r="216">
-          <cell r="A216" t="str">
-            <v>Zipper Pouch 12 Doz</v>
-          </cell>
-          <cell r="G216">
-            <v>52</v>
-          </cell>
-        </row>
-        <row r="217">
-          <cell r="A217" t="str">
-            <v>Zipper Pouch 6 Doz</v>
-          </cell>
-          <cell r="G217">
-            <v>52</v>
-          </cell>
-        </row>
-        <row r="218">
-          <cell r="A218" t="str">
-            <v>Pop Twelve 48 Doz</v>
-          </cell>
-          <cell r="G218">
-            <v>56</v>
-          </cell>
-        </row>
-        <row r="219">
-          <cell r="A219" t="str">
-            <v>Scentwrap11 36 Pcs</v>
-          </cell>
-          <cell r="G219">
-            <v>51.3</v>
-          </cell>
-        </row>
-        <row r="220">
-          <cell r="A220" t="str">
-            <v>Scentwrap19 48 Pcs</v>
-          </cell>
-          <cell r="G220">
-            <v>36</v>
-          </cell>
-        </row>
-        <row r="221">
-          <cell r="A221" t="str">
-            <v>Pooja Samagri 72 Pcs</v>
-          </cell>
-          <cell r="G221">
-            <v>80</v>
-          </cell>
-        </row>
-        <row r="222">
-          <cell r="A222" t="str">
-            <v>Ar Camphor 50 Gms 192</v>
-          </cell>
-          <cell r="G222">
-            <v>37</v>
-          </cell>
-        </row>
-        <row r="223">
-          <cell r="A223" t="str">
-            <v>Ar Camphor 100 Gms 108</v>
-          </cell>
-          <cell r="G223">
-            <v>37</v>
-          </cell>
-        </row>
-        <row r="224">
-          <cell r="A224" t="str">
-            <v>Car Freshener 12 Doz</v>
-          </cell>
-          <cell r="G224">
-            <v>45</v>
-          </cell>
-        </row>
-        <row r="225">
-          <cell r="A225" t="str">
-            <v>Airfreshner Spray 72 Pcs</v>
-          </cell>
-          <cell r="G225">
-            <v>47</v>
-          </cell>
-        </row>
-        <row r="226">
-          <cell r="A226" t="str">
-            <v>Room Spray 72 Pcs</v>
-          </cell>
-          <cell r="G226">
-            <v>28</v>
-          </cell>
-        </row>
-        <row r="227">
-          <cell r="A227" t="str">
-            <v>Potpouri 4 Doz</v>
-          </cell>
-          <cell r="G227">
-            <v>52</v>
-          </cell>
-        </row>
-        <row r="228">
-          <cell r="A228" t="str">
-            <v>Reed Diffuser 2 Doz</v>
-          </cell>
-          <cell r="G228">
-            <v>39</v>
-          </cell>
-        </row>
-        <row r="229">
-          <cell r="A229" t="str">
-            <v>Soap 100g 8 Doz</v>
-          </cell>
-          <cell r="G229">
-            <v>41.5</v>
-          </cell>
-        </row>
-        <row r="230">
-          <cell r="A230" t="str">
-            <v>Soap 75g 12 Doz</v>
-          </cell>
-          <cell r="G230">
-            <v>37.299999999999997</v>
-          </cell>
-        </row>
-        <row r="231">
-          <cell r="A231" t="str">
-            <v>Resin 30g 24 Doz</v>
-          </cell>
-          <cell r="G231">
-            <v>63</v>
-          </cell>
-        </row>
-        <row r="232">
-          <cell r="A232" t="str">
-            <v>Resin 20 KG</v>
-          </cell>
-          <cell r="G232">
-            <v>43</v>
-          </cell>
-        </row>
-        <row r="233">
-          <cell r="A233" t="str">
-            <v>Display SQ 10 Pcs</v>
-          </cell>
-          <cell r="G233">
-            <v>64</v>
-          </cell>
-        </row>
-        <row r="234">
-          <cell r="A234" t="str">
-            <v>Tall Eco 12 Doz</v>
-          </cell>
-          <cell r="G234">
-            <v>51.5</v>
-          </cell>
-        </row>
-        <row r="235">
-          <cell r="A235" t="str">
-            <v>Hexa 50 Doz (OP)</v>
-          </cell>
-          <cell r="G235">
-            <v>62</v>
-          </cell>
-        </row>
-        <row r="236">
-          <cell r="A236" t="str">
-            <v>Square 70 Box (OP)</v>
-          </cell>
-          <cell r="G236">
-            <v>56.6</v>
-          </cell>
-        </row>
-        <row r="237">
-          <cell r="A237" t="str">
-            <v>Loose 250g 20 Kg</v>
-          </cell>
-          <cell r="G237">
-            <v>49</v>
-          </cell>
-        </row>
-        <row r="238">
-          <cell r="A238" t="str">
-            <v>Masala 250g 4 Doz</v>
-          </cell>
-          <cell r="G238">
-            <v>58.5</v>
-          </cell>
-        </row>
-        <row r="239">
-          <cell r="A239" t="str">
-            <v>Festival Pack 56 Pcs</v>
-          </cell>
-          <cell r="G239">
-            <v>54</v>
-          </cell>
-        </row>
-        <row r="240">
-          <cell r="A240" t="str">
-            <v>Pop Tall 24 Doz</v>
-          </cell>
-          <cell r="G240">
-            <v>39.5</v>
-          </cell>
-        </row>
-        <row r="241">
-          <cell r="A241" t="str">
-            <v>Pop Tall 48 Doz</v>
-          </cell>
-          <cell r="G241">
-            <v>57</v>
-          </cell>
-        </row>
-        <row r="242">
-          <cell r="A242" t="str">
-            <v>Pop Tall 10 Doz</v>
-          </cell>
-          <cell r="G242">
-            <v>45</v>
-          </cell>
-        </row>
-        <row r="243">
-          <cell r="A243" t="str">
-            <v>Dhoop 12 Doz</v>
-          </cell>
-          <cell r="G243">
-            <v>58</v>
-          </cell>
-        </row>
-        <row r="244">
-          <cell r="A244" t="str">
-            <v xml:space="preserve"> </v>
-          </cell>
-          <cell r="G244">
-            <v>61.5</v>
-          </cell>
-        </row>
-        <row r="245">
-          <cell r="A245" t="str">
-            <v>Eco 12 Doz 3 in 1</v>
-          </cell>
-          <cell r="G245">
-            <v>46.5</v>
-          </cell>
-        </row>
-        <row r="246">
-          <cell r="A246" t="str">
-            <v>Eco 12 Doz</v>
-          </cell>
-          <cell r="G246">
-            <v>42.5</v>
-          </cell>
-        </row>
-        <row r="247">
-          <cell r="A247" t="str">
-            <v>Masala 50 Gm 6 Doz</v>
-          </cell>
-          <cell r="G247">
-            <v>49</v>
-          </cell>
-        </row>
-        <row r="248">
-          <cell r="A248" t="str">
-            <v>Masala 15 Gm 24 Doz</v>
-          </cell>
-          <cell r="G248">
-            <v>49</v>
-          </cell>
-        </row>
-        <row r="249">
-          <cell r="A249" t="str">
-            <v>Flora Masala Sq 36 Box</v>
-          </cell>
-          <cell r="G249">
-            <v>52.5</v>
-          </cell>
-        </row>
-        <row r="250">
-          <cell r="A250" t="str">
-            <v>7 Series 12 Box</v>
-          </cell>
-          <cell r="G250">
-            <v>41</v>
-          </cell>
-        </row>
-        <row r="251">
-          <cell r="A251" t="str">
-            <v>Big Cone 24 Doz</v>
-          </cell>
-          <cell r="G251">
-            <v>47.5</v>
-          </cell>
-        </row>
-        <row r="252">
-          <cell r="A252" t="str">
-            <v>BFC 10 Pc 24 Doz</v>
-          </cell>
-          <cell r="G252">
-            <v>39.5</v>
-          </cell>
-        </row>
-        <row r="253">
-          <cell r="A253" t="str">
-            <v>BFC 6 Doz</v>
-          </cell>
-          <cell r="G253">
-            <v>31.5</v>
-          </cell>
-        </row>
-        <row r="254">
-          <cell r="A254" t="str">
-            <v>Cone 30 Doz</v>
-          </cell>
-          <cell r="G254">
-            <v>40</v>
-          </cell>
-        </row>
-        <row r="255">
-          <cell r="A255" t="str">
-            <v>Tall Hexa 12 Doz</v>
-          </cell>
-          <cell r="G255">
-            <v>60</v>
-          </cell>
-        </row>
-        <row r="256">
-          <cell r="A256" t="str">
-            <v>Tall Hexa 6 Doz</v>
-          </cell>
-          <cell r="G256">
-            <v>36</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="0" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2685,7 +1652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="44.36328125" style="13" bestFit="1" customWidth="1"/>
@@ -2697,7 +1664,7 @@
     <col min="7" max="7" width="8.7265625" style="13" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.81640625" style="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.54296875" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7" style="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.36328125" style="79" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -2733,7 +1700,7 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="65" t="s">
         <v>183</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -2765,7 +1732,7 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="65" t="s">
         <v>183</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -2797,7 +1764,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="70" t="s">
+      <c r="A4" s="65" t="s">
         <v>183</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -2829,7 +1796,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="70" t="s">
+      <c r="A5" s="65" t="s">
         <v>183</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -2943,9 +1910,9 @@
       <c r="F8" s="34">
         <v>14.1</v>
       </c>
-      <c r="G8" s="34">
-        <f>_xlfn.XLOOKUP(D8,'[1]Master_infoCase_Size (2)'!$A$96:$A$256,'[1]Master_infoCase_Size (2)'!$G$96:$G$256,"")</f>
-        <v>45.1</v>
+      <c r="G8" s="34" t="e">
+        <f>_xlfn.XLOOKUP(D8,#REF!,#REF!,"")</f>
+        <v>#REF!</v>
       </c>
       <c r="H8" s="34">
         <v>36.5</v>
@@ -2976,9 +1943,9 @@
       <c r="F9" s="34">
         <v>8.1999999999999993</v>
       </c>
-      <c r="G9" s="34">
-        <f>_xlfn.XLOOKUP(D9,'[1]Master_infoCase_Size (2)'!$A$96:$A$256,'[1]Master_infoCase_Size (2)'!$G$96:$G$256,"")</f>
-        <v>36</v>
+      <c r="G9" s="34" t="e">
+        <f>_xlfn.XLOOKUP(D9,#REF!,#REF!,"")</f>
+        <v>#REF!</v>
       </c>
       <c r="H9" s="34">
         <v>30</v>
@@ -3050,7 +2017,7 @@
       <c r="I11" s="21">
         <v>45</v>
       </c>
-      <c r="J11" s="21" t="s">
+      <c r="J11" s="48" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3082,12 +2049,12 @@
       <c r="I12" s="21">
         <v>47</v>
       </c>
-      <c r="J12" s="21">
+      <c r="J12" s="48">
         <v>0.13</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="71" t="s">
+      <c r="A13" s="66" t="s">
         <v>116</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -3114,12 +2081,12 @@
       <c r="I13" s="21">
         <v>24</v>
       </c>
-      <c r="J13" s="21">
+      <c r="J13" s="48">
         <v>0.02</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="75" t="s">
+      <c r="A14" s="70" t="s">
         <v>56</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -3146,12 +2113,12 @@
       <c r="I14" s="21">
         <v>45</v>
       </c>
-      <c r="J14" s="21">
+      <c r="J14" s="48">
         <v>0.06</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="75" t="s">
+      <c r="A15" s="70" t="s">
         <v>56</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -3178,12 +2145,12 @@
       <c r="I15" s="21">
         <v>47.5</v>
       </c>
-      <c r="J15" s="21">
+      <c r="J15" s="48">
         <v>0.08</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="75" t="s">
+      <c r="A16" s="70" t="s">
         <v>56</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -3210,7 +2177,7 @@
       <c r="I16" s="21">
         <v>51</v>
       </c>
-      <c r="J16" s="21">
+      <c r="J16" s="48">
         <v>0.09</v>
       </c>
     </row>
@@ -3242,7 +2209,7 @@
       <c r="I17" s="21">
         <v>45</v>
       </c>
-      <c r="J17" s="21" t="s">
+      <c r="J17" s="48" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3280,7 +2247,7 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="70" t="s">
+      <c r="A19" s="65" t="s">
         <v>50</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -3313,10 +2280,10 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="70" t="s">
+      <c r="A20" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="69" t="s">
+      <c r="B20" s="64" t="s">
         <v>182</v>
       </c>
       <c r="C20" s="3" t="s">
@@ -3345,7 +2312,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="59" t="s">
+      <c r="A21" s="57" t="s">
         <v>50</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -3372,12 +2339,12 @@
       <c r="I21" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="J21" s="21" t="s">
+      <c r="J21" s="48" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="57" t="s">
         <v>50</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -3409,7 +2376,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="59" t="s">
+      <c r="A23" s="57" t="s">
         <v>50</v>
       </c>
       <c r="B23" s="5" t="s">
@@ -3441,7 +2408,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="70" t="s">
+      <c r="A24" s="65" t="s">
         <v>50</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -3474,7 +2441,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="70" t="s">
+      <c r="A25" s="65" t="s">
         <v>50</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -3539,7 +2506,7 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="59" t="s">
+      <c r="A27" s="57" t="s">
         <v>76</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -3571,7 +2538,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="59" t="s">
+      <c r="A28" s="57" t="s">
         <v>72</v>
       </c>
       <c r="B28" s="6"/>
@@ -3601,7 +2568,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="76" t="s">
+      <c r="A29" s="71" t="s">
         <v>103</v>
       </c>
       <c r="B29" s="6"/>
@@ -3844,7 +2811,7 @@
       <c r="I36" s="43">
         <v>48</v>
       </c>
-      <c r="J36" s="44">
+      <c r="J36" s="76">
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
@@ -3876,7 +2843,7 @@
       <c r="I37" s="43">
         <v>28.5</v>
       </c>
-      <c r="J37" s="44">
+      <c r="J37" s="76">
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
@@ -3906,7 +2873,7 @@
       <c r="I38" s="6">
         <v>35</v>
       </c>
-      <c r="J38" s="6">
+      <c r="J38" s="77">
         <v>0.05</v>
       </c>
     </row>
@@ -3936,7 +2903,7 @@
       <c r="I39" s="6">
         <v>67.5</v>
       </c>
-      <c r="J39" s="6">
+      <c r="J39" s="77">
         <v>0.05</v>
       </c>
     </row>
@@ -3966,7 +2933,7 @@
       <c r="I40" s="6">
         <v>35</v>
       </c>
-      <c r="J40" s="6">
+      <c r="J40" s="77">
         <v>0.05</v>
       </c>
     </row>
@@ -3996,12 +2963,12 @@
       <c r="I41" s="6">
         <v>27</v>
       </c>
-      <c r="J41" s="6">
+      <c r="J41" s="77">
         <v>0.04</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="76" t="s">
+      <c r="A42" s="71" t="s">
         <v>55</v>
       </c>
       <c r="B42" s="6"/>
@@ -4026,7 +2993,7 @@
       <c r="I42" s="6">
         <v>35</v>
       </c>
-      <c r="J42" s="6">
+      <c r="J42" s="77">
         <v>0.05</v>
       </c>
     </row>
@@ -4034,13 +3001,13 @@
       <c r="A43" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B43" s="55" t="s">
+      <c r="B43" s="53" t="s">
         <v>51</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="55" t="s">
+      <c r="D43" s="53" t="s">
         <v>17</v>
       </c>
       <c r="E43" s="41">
@@ -4058,12 +3025,12 @@
       <c r="I43" s="41">
         <v>32.5</v>
       </c>
-      <c r="J43" s="56">
+      <c r="J43" s="54">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="76" t="s">
+      <c r="A44" s="71" t="s">
         <v>189</v>
       </c>
       <c r="B44" s="3" t="s">
@@ -4095,7 +3062,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="61" t="s">
+      <c r="A45" s="59" t="s">
         <v>68</v>
       </c>
       <c r="B45" s="3"/>
@@ -4120,12 +3087,12 @@
       <c r="I45" s="34">
         <v>0</v>
       </c>
-      <c r="J45" s="45">
+      <c r="J45" s="44">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="61" t="s">
+      <c r="A46" s="59" t="s">
         <v>68</v>
       </c>
       <c r="B46" s="3"/>
@@ -4150,12 +3117,12 @@
       <c r="I46" s="34">
         <v>42.5</v>
       </c>
-      <c r="J46" s="45">
+      <c r="J46" s="44">
         <v>0.05</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="77" t="s">
+      <c r="A47" s="72" t="s">
         <v>68</v>
       </c>
       <c r="B47" s="3" t="s">
@@ -4182,7 +3149,7 @@
       <c r="I47" s="34">
         <v>27.5</v>
       </c>
-      <c r="J47" s="45">
+      <c r="J47" s="44">
         <f t="shared" ref="J47" si="1">G47*H47*I47/1000000</f>
         <v>3.5145000000000003E-2</v>
       </c>
@@ -4194,7 +3161,7 @@
       <c r="B48" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C48" s="64" t="s">
+      <c r="C48" s="62" t="s">
         <v>178</v>
       </c>
       <c r="D48" s="3" t="s">
@@ -4227,7 +3194,7 @@
       <c r="B49" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C49" s="64" t="s">
+      <c r="C49" s="62" t="s">
         <v>58</v>
       </c>
       <c r="D49" s="7" t="s">
@@ -4265,22 +3232,22 @@
       <c r="D50" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="E50" s="46">
+      <c r="E50" s="45">
         <v>15</v>
       </c>
-      <c r="F50" s="46">
+      <c r="F50" s="45">
         <v>14.15</v>
       </c>
-      <c r="G50" s="46">
+      <c r="G50" s="45">
         <v>41</v>
       </c>
-      <c r="H50" s="46">
+      <c r="H50" s="45">
         <v>30</v>
       </c>
-      <c r="I50" s="46">
+      <c r="I50" s="45">
         <v>45.5</v>
       </c>
-      <c r="J50" s="47">
+      <c r="J50" s="46">
         <v>5.5E-2</v>
       </c>
     </row>
@@ -4291,28 +3258,28 @@
       <c r="B51" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C51" s="63" t="s">
+      <c r="C51" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="D51" s="57" t="s">
+      <c r="D51" s="55" t="s">
         <v>149</v>
       </c>
-      <c r="E51" s="46">
+      <c r="E51" s="45">
         <v>12.6</v>
       </c>
-      <c r="F51" s="46">
+      <c r="F51" s="45">
         <v>11.1</v>
       </c>
-      <c r="G51" s="46">
+      <c r="G51" s="45">
         <v>39.5</v>
       </c>
-      <c r="H51" s="46">
+      <c r="H51" s="45">
         <v>38.5</v>
       </c>
-      <c r="I51" s="46">
+      <c r="I51" s="45">
         <v>54.5</v>
       </c>
-      <c r="J51" s="47">
+      <c r="J51" s="46">
         <v>0.09</v>
       </c>
     </row>
@@ -4320,58 +3287,58 @@
       <c r="A52" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="C52" s="63" t="s">
+      <c r="C52" s="61" t="s">
         <v>79</v>
       </c>
-      <c r="D52" s="57" t="s">
+      <c r="D52" s="55" t="s">
         <v>150</v>
       </c>
-      <c r="E52" s="46">
+      <c r="E52" s="45">
         <v>25.3</v>
       </c>
-      <c r="F52" s="46">
+      <c r="F52" s="45">
         <v>22.4</v>
       </c>
-      <c r="G52" s="46">
+      <c r="G52" s="45">
         <v>57</v>
       </c>
-      <c r="H52" s="46">
+      <c r="H52" s="45">
         <v>53</v>
       </c>
-      <c r="I52" s="46">
+      <c r="I52" s="45">
         <v>55</v>
       </c>
-      <c r="J52" s="47">
+      <c r="J52" s="46">
         <v>0.17</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="76" t="s">
+      <c r="A53" s="71" t="s">
         <v>93</v>
       </c>
       <c r="B53" s="9"/>
-      <c r="C53" s="63" t="s">
+      <c r="C53" s="61" t="s">
         <v>164</v>
       </c>
-      <c r="D53" s="57" t="s">
+      <c r="D53" s="55" t="s">
         <v>151</v>
       </c>
-      <c r="E53" s="46">
+      <c r="E53" s="45">
         <v>8</v>
       </c>
-      <c r="F53" s="46">
+      <c r="F53" s="45">
         <v>7.5</v>
       </c>
-      <c r="G53" s="46">
+      <c r="G53" s="45">
         <v>45</v>
       </c>
-      <c r="H53" s="46">
+      <c r="H53" s="45">
         <v>37</v>
       </c>
-      <c r="I53" s="46">
+      <c r="I53" s="45">
         <v>28</v>
       </c>
-      <c r="J53" s="47">
+      <c r="J53" s="46">
         <v>0.05</v>
       </c>
     </row>
@@ -4379,19 +3346,19 @@
       <c r="A54" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="B54" s="66" t="s">
+      <c r="B54" s="73" t="s">
         <v>71</v>
       </c>
-      <c r="C54" s="63" t="s">
+      <c r="C54" s="61" t="s">
         <v>67</v>
       </c>
       <c r="D54" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="E54" s="48">
+      <c r="E54" s="47">
         <v>24</v>
       </c>
-      <c r="F54" s="48">
+      <c r="F54" s="47">
         <v>23</v>
       </c>
       <c r="G54" s="36">
@@ -4403,15 +3370,15 @@
       <c r="I54" s="36">
         <v>60</v>
       </c>
-      <c r="J54" s="49">
+      <c r="J54" s="48">
         <v>0.104</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="73" t="s">
+      <c r="A55" s="68" t="s">
         <v>106</v>
       </c>
-      <c r="B55" s="68"/>
+      <c r="B55" s="75"/>
       <c r="C55" s="6" t="s">
         <v>67</v>
       </c>
@@ -4438,10 +3405,10 @@
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A56" s="76" t="s">
+      <c r="A56" s="71" t="s">
         <v>101</v>
       </c>
-      <c r="B56" s="66" t="s">
+      <c r="B56" s="73" t="s">
         <v>73</v>
       </c>
       <c r="C56" s="8" t="s">
@@ -4465,15 +3432,15 @@
       <c r="I56" s="36">
         <v>49</v>
       </c>
-      <c r="J56" s="49">
+      <c r="J56" s="48">
         <v>6.6640000000000005E-2</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A57" s="74" t="s">
+      <c r="A57" s="69" t="s">
         <v>187</v>
       </c>
-      <c r="B57" s="67"/>
+      <c r="B57" s="74"/>
       <c r="C57" s="10" t="s">
         <v>67</v>
       </c>
@@ -4500,7 +3467,7 @@
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A58" s="58" t="s">
+      <c r="A58" s="56" t="s">
         <v>41</v>
       </c>
       <c r="B58" s="10" t="s">
@@ -4512,15 +3479,15 @@
       <c r="D58" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="E58" s="50"/>
-      <c r="F58" s="50"/>
-      <c r="G58" s="50"/>
-      <c r="H58" s="50"/>
-      <c r="I58" s="50"/>
-      <c r="J58" s="51"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49"/>
+      <c r="G58" s="49"/>
+      <c r="H58" s="49"/>
+      <c r="I58" s="49"/>
+      <c r="J58" s="50"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A59" s="62" t="s">
+      <c r="A59" s="60" t="s">
         <v>41</v>
       </c>
       <c r="B59" s="10" t="s">
@@ -4532,27 +3499,27 @@
       <c r="D59" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="49">
         <v>29.4</v>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="49">
         <v>28</v>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="49">
         <v>45</v>
       </c>
-      <c r="H59" s="50">
+      <c r="H59" s="49">
         <v>41</v>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="49">
         <v>54</v>
       </c>
-      <c r="J59" s="51">
+      <c r="J59" s="50">
         <v>9.9629999999999996E-2</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="60" t="s">
+      <c r="A60" s="58" t="s">
         <v>41</v>
       </c>
       <c r="B60" s="5" t="s">
@@ -4584,7 +3551,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="70" t="s">
+      <c r="A61" s="65" t="s">
         <v>41</v>
       </c>
       <c r="B61" s="1" t="s">
@@ -4616,7 +3583,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="70" t="s">
+      <c r="A62" s="65" t="s">
         <v>41</v>
       </c>
       <c r="B62" s="1" t="s">
@@ -4648,7 +3615,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="70" t="s">
+      <c r="A63" s="65" t="s">
         <v>41</v>
       </c>
       <c r="B63" s="1" t="s">
@@ -4680,7 +3647,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="70" t="s">
+      <c r="A64" s="65" t="s">
         <v>41</v>
       </c>
       <c r="B64" s="1" t="s">
@@ -4772,7 +3739,7 @@
       <c r="I66" s="3">
         <v>46</v>
       </c>
-      <c r="J66" s="52">
+      <c r="J66" s="78">
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
@@ -4810,7 +3777,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="72" t="s">
+      <c r="A68" s="67" t="s">
         <v>70</v>
       </c>
       <c r="B68" s="1" t="s">
@@ -4837,7 +3804,7 @@
       <c r="I68" s="34">
         <v>34.5</v>
       </c>
-      <c r="J68" s="34">
+      <c r="J68" s="35">
         <v>2.7047999999999999E-2</v>
       </c>
     </row>
@@ -4848,7 +3815,7 @@
       <c r="B69" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="C69" s="65" t="s">
+      <c r="C69" s="63" t="s">
         <v>58</v>
       </c>
       <c r="D69" s="3" t="s">
@@ -4934,7 +3901,7 @@
       <c r="I71" s="34">
         <v>39</v>
       </c>
-      <c r="J71" s="34">
+      <c r="J71" s="35">
         <v>0.03</v>
       </c>
     </row>
@@ -4957,13 +3924,13 @@
       <c r="F72" s="34">
         <v>8.4</v>
       </c>
-      <c r="G72" s="53">
+      <c r="G72" s="51">
         <v>28.4</v>
       </c>
-      <c r="H72" s="53">
+      <c r="H72" s="51">
         <v>31.6</v>
       </c>
-      <c r="I72" s="54">
+      <c r="I72" s="52">
         <v>30</v>
       </c>
       <c r="J72" s="35">
@@ -4998,7 +3965,7 @@
       <c r="I73" s="34">
         <v>28.5</v>
       </c>
-      <c r="J73" s="34">
+      <c r="J73" s="35">
         <f t="shared" ref="J73:J74" si="4">G73*H73*I73/1000000</f>
         <v>9.7854750000000004E-2</v>
       </c>
@@ -5031,13 +3998,13 @@
       <c r="I74" s="34">
         <v>29</v>
       </c>
-      <c r="J74" s="34">
+      <c r="J74" s="35">
         <f t="shared" si="4"/>
         <v>7.9931249999999995E-2</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="72"/>
+      <c r="A75" s="67"/>
       <c r="B75" s="3" t="s">
         <v>117</v>
       </c>
@@ -5061,11 +4028,11 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="70"/>
+      <c r="A76" s="65"/>
       <c r="B76" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="C76" s="65">
+      <c r="C76" s="63">
         <v>4</v>
       </c>
       <c r="D76" s="3">
@@ -5085,8 +4052,8 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="59"/>
-      <c r="B77" s="59" t="s">
+      <c r="A77" s="65"/>
+      <c r="B77" s="65" t="s">
         <v>184</v>
       </c>
       <c r="C77" s="3" t="s">
@@ -5110,9 +4077,811 @@
       <c r="I77" s="3">
         <v>28.5</v>
       </c>
-      <c r="J77" s="3">
+      <c r="J77" s="35">
         <v>0.1</v>
       </c>
+    </row>
+    <row r="79" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="80" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A80" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E80" s="34">
+        <v>12.75</v>
+      </c>
+      <c r="F80" s="34">
+        <v>11.2</v>
+      </c>
+      <c r="G80" s="34">
+        <v>37.5</v>
+      </c>
+      <c r="H80" s="34">
+        <v>28.2</v>
+      </c>
+      <c r="I80" s="34">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="J80" s="35">
+        <v>3.6999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A81" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E81" s="34">
+        <v>11</v>
+      </c>
+      <c r="F81" s="34">
+        <v>13</v>
+      </c>
+      <c r="G81" s="34">
+        <v>35</v>
+      </c>
+      <c r="H81" s="34">
+        <v>22</v>
+      </c>
+      <c r="I81" s="34">
+        <v>39</v>
+      </c>
+      <c r="J81" s="35">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E82" s="34">
+        <v>11.08</v>
+      </c>
+      <c r="F82" s="34">
+        <v>10.08</v>
+      </c>
+      <c r="G82" s="34">
+        <v>37</v>
+      </c>
+      <c r="H82" s="34">
+        <v>28</v>
+      </c>
+      <c r="I82" s="34">
+        <v>21</v>
+      </c>
+      <c r="J82" s="35">
+        <v>2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E83" s="34">
+        <v>9.0519999999999996</v>
+      </c>
+      <c r="F83" s="34">
+        <v>8.0519999999999996</v>
+      </c>
+      <c r="G83" s="34">
+        <v>28.5</v>
+      </c>
+      <c r="H83" s="34">
+        <v>21.5</v>
+      </c>
+      <c r="I83" s="34">
+        <v>23.5</v>
+      </c>
+      <c r="J83" s="35">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A84" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E84" s="34">
+        <v>11.8</v>
+      </c>
+      <c r="F84" s="34">
+        <v>11.6</v>
+      </c>
+      <c r="G84" s="34">
+        <v>28.4</v>
+      </c>
+      <c r="H84" s="34">
+        <v>31.6</v>
+      </c>
+      <c r="I84" s="34">
+        <v>30</v>
+      </c>
+      <c r="J84" s="35">
+        <v>2.7E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A85" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E85" s="34">
+        <v>12.75</v>
+      </c>
+      <c r="F85" s="34">
+        <v>11.2</v>
+      </c>
+      <c r="G85" s="34">
+        <v>37.5</v>
+      </c>
+      <c r="H85" s="34">
+        <v>28.2</v>
+      </c>
+      <c r="I85" s="34">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="J85" s="35">
+        <v>3.6999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A86" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E86" s="34">
+        <v>12</v>
+      </c>
+      <c r="F86" s="34">
+        <v>11.23</v>
+      </c>
+      <c r="G86" s="34">
+        <v>36</v>
+      </c>
+      <c r="H86" s="34">
+        <v>27</v>
+      </c>
+      <c r="I86" s="34">
+        <v>27</v>
+      </c>
+      <c r="J86" s="35">
+        <v>2.6244E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A87" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E87" s="34">
+        <v>9.5440000000000005</v>
+      </c>
+      <c r="F87" s="34">
+        <v>8.5440000000000005</v>
+      </c>
+      <c r="G87" s="34">
+        <v>44.8</v>
+      </c>
+      <c r="H87" s="34">
+        <v>30</v>
+      </c>
+      <c r="I87" s="34">
+        <v>10</v>
+      </c>
+      <c r="J87" s="35">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A90" s="80" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A91" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E91" s="34">
+        <v>7</v>
+      </c>
+      <c r="F91" s="34">
+        <v>5</v>
+      </c>
+      <c r="G91" s="34">
+        <v>46.5</v>
+      </c>
+      <c r="H91" s="34">
+        <v>36.5</v>
+      </c>
+      <c r="I91" s="34">
+        <v>55</v>
+      </c>
+      <c r="J91" s="35">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A92" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E92" s="34">
+        <v>30</v>
+      </c>
+      <c r="F92" s="34">
+        <v>28</v>
+      </c>
+      <c r="G92" s="34">
+        <v>48</v>
+      </c>
+      <c r="H92" s="34">
+        <v>51</v>
+      </c>
+      <c r="I92" s="34">
+        <v>45</v>
+      </c>
+      <c r="J92" s="35">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A93" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C93" s="1"/>
+      <c r="D93" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E93" s="34">
+        <v>20</v>
+      </c>
+      <c r="F93" s="34">
+        <v>19.2</v>
+      </c>
+      <c r="G93" s="34">
+        <v>48.5</v>
+      </c>
+      <c r="H93" s="34">
+        <v>40.5</v>
+      </c>
+      <c r="I93" s="34">
+        <v>42</v>
+      </c>
+      <c r="J93" s="35">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A94" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C94" s="1"/>
+      <c r="D94" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E94" s="34">
+        <v>16</v>
+      </c>
+      <c r="F94" s="34">
+        <v>15</v>
+      </c>
+      <c r="G94" s="34">
+        <v>22</v>
+      </c>
+      <c r="H94" s="34">
+        <v>7.8</v>
+      </c>
+      <c r="I94" s="34">
+        <v>21</v>
+      </c>
+      <c r="J94" s="35">
+        <v>9.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A95" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E95" s="34">
+        <v>9.5</v>
+      </c>
+      <c r="F95" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="G95" s="34">
+        <v>36</v>
+      </c>
+      <c r="H95" s="34">
+        <v>28</v>
+      </c>
+      <c r="I95" s="34">
+        <v>33.5</v>
+      </c>
+      <c r="J95" s="35">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A96" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D96" s="3"/>
+      <c r="E96" s="34">
+        <v>8</v>
+      </c>
+      <c r="F96" s="34">
+        <v>6</v>
+      </c>
+      <c r="G96" s="34">
+        <v>38</v>
+      </c>
+      <c r="H96" s="34">
+        <v>56</v>
+      </c>
+      <c r="I96" s="34">
+        <v>33</v>
+      </c>
+      <c r="J96" s="35">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A97" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E97" s="34">
+        <v>7</v>
+      </c>
+      <c r="F97" s="34">
+        <v>5</v>
+      </c>
+      <c r="G97" s="34">
+        <v>46.5</v>
+      </c>
+      <c r="H97" s="34">
+        <v>36.5</v>
+      </c>
+      <c r="I97" s="34">
+        <v>55</v>
+      </c>
+      <c r="J97" s="35">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A98" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C98" s="1"/>
+      <c r="D98" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E98" s="34">
+        <v>12.75</v>
+      </c>
+      <c r="F98" s="34">
+        <v>11.2</v>
+      </c>
+      <c r="G98" s="34">
+        <v>37.5</v>
+      </c>
+      <c r="H98" s="34">
+        <v>28.2</v>
+      </c>
+      <c r="I98" s="34">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="J98" s="35">
+        <v>3.6999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A99" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C99" s="1"/>
+      <c r="D99" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E99" s="34">
+        <v>10.3</v>
+      </c>
+      <c r="F99" s="34">
+        <v>9.6</v>
+      </c>
+      <c r="G99" s="34">
+        <v>21.8</v>
+      </c>
+      <c r="H99" s="34">
+        <v>5.6</v>
+      </c>
+      <c r="I99" s="34">
+        <v>14.1</v>
+      </c>
+      <c r="J99" s="35">
+        <v>9.4E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A100" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C100" s="1"/>
+      <c r="D100" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E100" s="34">
+        <v>10.3</v>
+      </c>
+      <c r="F100" s="34">
+        <v>9.6</v>
+      </c>
+      <c r="G100" s="34">
+        <v>21.8</v>
+      </c>
+      <c r="H100" s="34">
+        <v>5.6</v>
+      </c>
+      <c r="I100" s="34">
+        <v>14.1</v>
+      </c>
+      <c r="J100" s="35">
+        <v>9.4E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A101" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E101" s="34">
+        <v>10.72</v>
+      </c>
+      <c r="F101" s="34">
+        <v>9.7200000000000006</v>
+      </c>
+      <c r="G101" s="34">
+        <v>28</v>
+      </c>
+      <c r="H101" s="34">
+        <v>28</v>
+      </c>
+      <c r="I101" s="34">
+        <v>34.5</v>
+      </c>
+      <c r="J101" s="35">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A102" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E102" s="34">
+        <v>10.3</v>
+      </c>
+      <c r="F102" s="34">
+        <v>9.6</v>
+      </c>
+      <c r="G102" s="34">
+        <v>49</v>
+      </c>
+      <c r="H102" s="34">
+        <v>27</v>
+      </c>
+      <c r="I102" s="34">
+        <v>45</v>
+      </c>
+      <c r="J102" s="35">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A103" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
+      <c r="D103" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E103" s="34">
+        <v>15.6</v>
+      </c>
+      <c r="F103" s="34">
+        <v>14.6</v>
+      </c>
+      <c r="G103" s="34">
+        <v>54</v>
+      </c>
+      <c r="H103" s="34">
+        <v>30</v>
+      </c>
+      <c r="I103" s="34">
+        <v>44.5</v>
+      </c>
+      <c r="J103" s="35">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A104" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E104" s="34">
+        <v>10.3</v>
+      </c>
+      <c r="F104" s="34">
+        <v>9.6</v>
+      </c>
+      <c r="G104" s="34">
+        <v>49</v>
+      </c>
+      <c r="H104" s="34">
+        <v>27</v>
+      </c>
+      <c r="I104" s="34">
+        <v>45</v>
+      </c>
+      <c r="J104" s="35">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A105" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E105" s="34">
+        <v>27</v>
+      </c>
+      <c r="F105" s="34">
+        <v>24</v>
+      </c>
+      <c r="G105" s="34">
+        <v>55</v>
+      </c>
+      <c r="H105" s="34">
+        <v>33</v>
+      </c>
+      <c r="I105" s="34">
+        <v>70</v>
+      </c>
+      <c r="J105" s="35">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A106" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E106" s="34"/>
+      <c r="F106" s="34"/>
+      <c r="G106" s="34">
+        <v>50.9</v>
+      </c>
+      <c r="H106" s="34">
+        <v>39.6</v>
+      </c>
+      <c r="I106" s="34">
+        <v>60</v>
+      </c>
+      <c r="J106" s="35">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A107" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E107" s="34">
+        <v>30</v>
+      </c>
+      <c r="F107" s="34">
+        <v>28</v>
+      </c>
+      <c r="G107" s="34">
+        <v>48</v>
+      </c>
+      <c r="H107" s="34">
+        <v>51</v>
+      </c>
+      <c r="I107" s="34">
+        <v>45</v>
+      </c>
+      <c r="J107" s="35">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A108" s="16"/>
+      <c r="B108" s="1"/>
+      <c r="C108" s="1"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="34"/>
+      <c r="F108" s="34"/>
+      <c r="G108" s="34"/>
+      <c r="H108" s="34"/>
+      <c r="I108" s="34"/>
+      <c r="J108" s="35"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J77" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Case Size.xlsx
+++ b/Case Size.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\product catalogue\product catalogue app v2\.claude\worktrees\youthful-dhawan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3FD38F-9D45-47F5-854C-7B6271E4771C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F54408-604A-44CE-8E42-A1C9BF5D3350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$77</definedName>
   </definedNames>
@@ -42,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="246">
   <si>
     <t>Description</t>
   </si>
@@ -670,12 +667,6 @@
   </si>
   <si>
     <t xml:space="preserve">48 Pcs </t>
-  </si>
-  <si>
-    <t>Candle catalogue</t>
-  </si>
-  <si>
-    <t>Sacred element catalogue</t>
   </si>
   <si>
     <t>Affirmation Ritual Kit</t>
@@ -805,9 +796,9 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -841,16 +832,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -869,12 +852,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="19">
     <border>
@@ -1116,7 +1093,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1268,7 +1245,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1332,6 +1309,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1339,21 +1328,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1371,22 +1345,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Master_infoCase_Size"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1652,7 +1610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="44.36328125" style="13" bestFit="1" customWidth="1"/>
@@ -1664,7 +1622,7 @@
     <col min="7" max="7" width="8.7265625" style="13" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.81640625" style="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.54296875" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.36328125" style="79" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.36328125" style="76" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -2811,7 +2769,7 @@
       <c r="I36" s="43">
         <v>48</v>
       </c>
-      <c r="J36" s="76">
+      <c r="J36" s="73">
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
@@ -2843,7 +2801,7 @@
       <c r="I37" s="43">
         <v>28.5</v>
       </c>
-      <c r="J37" s="76">
+      <c r="J37" s="73">
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
@@ -2873,7 +2831,7 @@
       <c r="I38" s="6">
         <v>35</v>
       </c>
-      <c r="J38" s="77">
+      <c r="J38" s="74">
         <v>0.05</v>
       </c>
     </row>
@@ -2903,7 +2861,7 @@
       <c r="I39" s="6">
         <v>67.5</v>
       </c>
-      <c r="J39" s="77">
+      <c r="J39" s="74">
         <v>0.05</v>
       </c>
     </row>
@@ -2933,7 +2891,7 @@
       <c r="I40" s="6">
         <v>35</v>
       </c>
-      <c r="J40" s="77">
+      <c r="J40" s="74">
         <v>0.05</v>
       </c>
     </row>
@@ -2963,7 +2921,7 @@
       <c r="I41" s="6">
         <v>27</v>
       </c>
-      <c r="J41" s="77">
+      <c r="J41" s="74">
         <v>0.04</v>
       </c>
     </row>
@@ -2993,7 +2951,7 @@
       <c r="I42" s="6">
         <v>35</v>
       </c>
-      <c r="J42" s="77">
+      <c r="J42" s="74">
         <v>0.05</v>
       </c>
     </row>
@@ -3346,7 +3304,7 @@
       <c r="A54" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="B54" s="73" t="s">
+      <c r="B54" s="77" t="s">
         <v>71</v>
       </c>
       <c r="C54" s="61" t="s">
@@ -3378,7 +3336,7 @@
       <c r="A55" s="68" t="s">
         <v>106</v>
       </c>
-      <c r="B55" s="75"/>
+      <c r="B55" s="79"/>
       <c r="C55" s="6" t="s">
         <v>67</v>
       </c>
@@ -3408,7 +3366,7 @@
       <c r="A56" s="71" t="s">
         <v>101</v>
       </c>
-      <c r="B56" s="73" t="s">
+      <c r="B56" s="77" t="s">
         <v>73</v>
       </c>
       <c r="C56" s="8" t="s">
@@ -3440,7 +3398,7 @@
       <c r="A57" s="69" t="s">
         <v>187</v>
       </c>
-      <c r="B57" s="74"/>
+      <c r="B57" s="78"/>
       <c r="C57" s="10" t="s">
         <v>67</v>
       </c>
@@ -3739,7 +3697,7 @@
       <c r="I66" s="3">
         <v>46</v>
       </c>
-      <c r="J66" s="78">
+      <c r="J66" s="75">
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
@@ -4081,73 +4039,132 @@
         <v>0.1</v>
       </c>
     </row>
+    <row r="78" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E78" s="34">
+        <v>12.75</v>
+      </c>
+      <c r="F78" s="34">
+        <v>11.2</v>
+      </c>
+      <c r="G78" s="34">
+        <v>37.5</v>
+      </c>
+      <c r="H78" s="34">
+        <v>28.2</v>
+      </c>
+      <c r="I78" s="34">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="J78" s="35">
+        <v>3.6999999999999998E-2</v>
+      </c>
+    </row>
     <row r="79" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="80" t="s">
-        <v>206</v>
+      <c r="A79" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E79" s="34">
+        <v>11</v>
+      </c>
+      <c r="F79" s="34">
+        <v>13</v>
+      </c>
+      <c r="G79" s="34">
+        <v>35</v>
+      </c>
+      <c r="H79" s="34">
+        <v>22</v>
+      </c>
+      <c r="I79" s="34">
+        <v>39</v>
+      </c>
+      <c r="J79" s="35">
+        <v>0.03</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="16" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>102</v>
+        <v>200</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>58</v>
+        <v>201</v>
       </c>
       <c r="E80" s="34">
-        <v>12.75</v>
+        <v>11.08</v>
       </c>
       <c r="F80" s="34">
-        <v>11.2</v>
+        <v>10.08</v>
       </c>
       <c r="G80" s="34">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="H80" s="34">
-        <v>28.2</v>
+        <v>28</v>
       </c>
       <c r="I80" s="34">
-        <v>34.799999999999997</v>
+        <v>21</v>
       </c>
       <c r="J80" s="35">
-        <v>3.6999999999999998E-2</v>
+        <v>2.1999999999999999E-2</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="16" t="s">
-        <v>106</v>
+        <v>198</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>64</v>
+        <v>178</v>
       </c>
       <c r="E81" s="34">
-        <v>11</v>
+        <v>9.0519999999999996</v>
       </c>
       <c r="F81" s="34">
-        <v>13</v>
+        <v>8.0519999999999996</v>
       </c>
       <c r="G81" s="34">
-        <v>35</v>
+        <v>28.5</v>
       </c>
       <c r="H81" s="34">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="I81" s="34">
-        <v>39</v>
+        <v>23.5</v>
       </c>
       <c r="J81" s="35">
-        <v>0.03</v>
+        <v>1.4E-2</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4155,456 +4172,541 @@
         <v>198</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>201</v>
+        <v>64</v>
       </c>
       <c r="E82" s="34">
-        <v>11.08</v>
+        <v>11.8</v>
       </c>
       <c r="F82" s="34">
-        <v>10.08</v>
+        <v>11.6</v>
       </c>
       <c r="G82" s="34">
-        <v>37</v>
+        <v>28.4</v>
       </c>
       <c r="H82" s="34">
-        <v>28</v>
+        <v>31.6</v>
       </c>
       <c r="I82" s="34">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J82" s="35">
-        <v>2.1999999999999999E-2</v>
+        <v>2.7E-2</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="16" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>199</v>
+        <v>104</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>178</v>
+        <v>105</v>
       </c>
       <c r="E83" s="34">
-        <v>9.0519999999999996</v>
+        <v>12.75</v>
       </c>
       <c r="F83" s="34">
-        <v>8.0519999999999996</v>
+        <v>11.2</v>
       </c>
       <c r="G83" s="34">
-        <v>28.5</v>
+        <v>37.5</v>
       </c>
       <c r="H83" s="34">
-        <v>21.5</v>
+        <v>28.2</v>
       </c>
       <c r="I83" s="34">
-        <v>23.5</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="J83" s="35">
-        <v>1.4E-2</v>
+        <v>3.6999999999999998E-2</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="16" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="E84" s="34">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="F84" s="34">
-        <v>11.6</v>
+        <v>11.23</v>
       </c>
       <c r="G84" s="34">
-        <v>28.4</v>
+        <v>36</v>
       </c>
       <c r="H84" s="34">
-        <v>31.6</v>
+        <v>27</v>
       </c>
       <c r="I84" s="34">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J84" s="35">
-        <v>2.7E-2</v>
+        <v>2.6244E-2</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="16" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>104</v>
+        <v>204</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>105</v>
+        <v>201</v>
       </c>
       <c r="E85" s="34">
-        <v>12.75</v>
+        <v>9.5440000000000005</v>
       </c>
       <c r="F85" s="34">
-        <v>11.2</v>
+        <v>8.5440000000000005</v>
       </c>
       <c r="G85" s="34">
-        <v>37.5</v>
+        <v>44.8</v>
       </c>
       <c r="H85" s="34">
-        <v>28.2</v>
+        <v>30</v>
       </c>
       <c r="I85" s="34">
-        <v>34.799999999999997</v>
+        <v>10</v>
       </c>
       <c r="J85" s="35">
-        <v>3.6999999999999998E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="16" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="E86" s="34">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F86" s="34">
-        <v>11.23</v>
+        <v>5</v>
       </c>
       <c r="G86" s="34">
-        <v>36</v>
+        <v>46.5</v>
       </c>
       <c r="H86" s="34">
-        <v>27</v>
+        <v>36.5</v>
       </c>
       <c r="I86" s="34">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="J86" s="35">
-        <v>2.6244E-2</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="16" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>201</v>
+        <v>67</v>
       </c>
       <c r="E87" s="34">
-        <v>9.5440000000000005</v>
+        <v>30</v>
       </c>
       <c r="F87" s="34">
-        <v>8.5440000000000005</v>
+        <v>28</v>
       </c>
       <c r="G87" s="34">
-        <v>44.8</v>
+        <v>48</v>
       </c>
       <c r="H87" s="34">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="I87" s="34">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="J87" s="35">
-        <v>1.2999999999999999E-2</v>
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A88" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C88" s="1"/>
+      <c r="D88" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E88" s="34">
+        <v>20</v>
+      </c>
+      <c r="F88" s="34">
+        <v>19.2</v>
+      </c>
+      <c r="G88" s="34">
+        <v>48.5</v>
+      </c>
+      <c r="H88" s="34">
+        <v>40.5</v>
+      </c>
+      <c r="I88" s="34">
+        <v>42</v>
+      </c>
+      <c r="J88" s="35">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A89" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C89" s="1"/>
+      <c r="D89" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E89" s="34">
+        <v>16</v>
+      </c>
+      <c r="F89" s="34">
+        <v>15</v>
+      </c>
+      <c r="G89" s="34">
+        <v>22</v>
+      </c>
+      <c r="H89" s="34">
+        <v>7.8</v>
+      </c>
+      <c r="I89" s="34">
+        <v>21</v>
+      </c>
+      <c r="J89" s="35">
+        <v>9.2999999999999999E-2</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="80" t="s">
-        <v>207</v>
+      <c r="A90" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E90" s="34">
+        <v>9.5</v>
+      </c>
+      <c r="F90" s="34">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="G90" s="34">
+        <v>36</v>
+      </c>
+      <c r="H90" s="34">
+        <v>28</v>
+      </c>
+      <c r="I90" s="34">
+        <v>33.5</v>
+      </c>
+      <c r="J90" s="35">
+        <v>0.03</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="16" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>67</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="D91" s="3"/>
       <c r="E91" s="34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F91" s="34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G91" s="34">
-        <v>46.5</v>
+        <v>38</v>
       </c>
       <c r="H91" s="34">
-        <v>36.5</v>
+        <v>56</v>
       </c>
       <c r="I91" s="34">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="J91" s="35">
-        <v>0.09</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="16" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>67</v>
+        <v>224</v>
       </c>
       <c r="E92" s="34">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="F92" s="34">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G92" s="34">
-        <v>48</v>
+        <v>46.5</v>
       </c>
       <c r="H92" s="34">
-        <v>51</v>
+        <v>36.5</v>
       </c>
       <c r="I92" s="34">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="J92" s="35">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="16" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>214</v>
+        <v>104</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="3" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="E93" s="34">
-        <v>20</v>
+        <v>12.75</v>
       </c>
       <c r="F93" s="34">
-        <v>19.2</v>
+        <v>11.2</v>
       </c>
       <c r="G93" s="34">
-        <v>48.5</v>
+        <v>37.5</v>
       </c>
       <c r="H93" s="34">
-        <v>40.5</v>
+        <v>28.2</v>
       </c>
       <c r="I93" s="34">
-        <v>42</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="J93" s="35">
-        <v>0.08</v>
+        <v>3.6999999999999998E-2</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="16" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="3" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="E94" s="34">
-        <v>16</v>
+        <v>10.3</v>
       </c>
       <c r="F94" s="34">
-        <v>15</v>
+        <v>9.6</v>
       </c>
       <c r="G94" s="34">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="H94" s="34">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="I94" s="34">
-        <v>21</v>
+        <v>14.1</v>
       </c>
       <c r="J94" s="35">
-        <v>9.2999999999999999E-2</v>
+        <v>9.4E-2</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="16" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>221</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="C95" s="1"/>
       <c r="D95" s="3" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="E95" s="34">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="F95" s="34">
-        <v>9.3000000000000007</v>
+        <v>9.6</v>
       </c>
       <c r="G95" s="34">
-        <v>36</v>
+        <v>21.8</v>
       </c>
       <c r="H95" s="34">
-        <v>28</v>
+        <v>5.6</v>
       </c>
       <c r="I95" s="34">
-        <v>33.5</v>
+        <v>14.1</v>
       </c>
       <c r="J95" s="35">
-        <v>0.03</v>
+        <v>9.4E-2</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="16" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>223</v>
+        <v>100</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D96" s="3"/>
+      <c r="D96" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="E96" s="34">
-        <v>8</v>
+        <v>10.72</v>
       </c>
       <c r="F96" s="34">
-        <v>6</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="G96" s="34">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H96" s="34">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="I96" s="34">
-        <v>33</v>
+        <v>34.5</v>
       </c>
       <c r="J96" s="35">
-        <v>7.0000000000000007E-2</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="16" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>225</v>
+        <v>19</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>210</v>
+        <v>165</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="E97" s="34">
-        <v>7</v>
+        <v>10.3</v>
       </c>
       <c r="F97" s="34">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="G97" s="34">
-        <v>46.5</v>
+        <v>49</v>
       </c>
       <c r="H97" s="34">
-        <v>36.5</v>
+        <v>27</v>
       </c>
       <c r="I97" s="34">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J97" s="35">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="16" t="s">
-        <v>227</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="B98" s="1"/>
       <c r="C98" s="1"/>
       <c r="D98" s="3" t="s">
-        <v>228</v>
+        <v>164</v>
       </c>
       <c r="E98" s="34">
-        <v>12.75</v>
+        <v>15.6</v>
       </c>
       <c r="F98" s="34">
-        <v>11.2</v>
+        <v>14.6</v>
       </c>
       <c r="G98" s="34">
-        <v>37.5</v>
+        <v>54</v>
       </c>
       <c r="H98" s="34">
-        <v>28.2</v>
+        <v>30</v>
       </c>
       <c r="I98" s="34">
-        <v>34.799999999999997</v>
+        <v>44.5</v>
       </c>
       <c r="J98" s="35">
-        <v>3.6999999999999998E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="16" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C99" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>165</v>
+      </c>
       <c r="D99" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E99" s="34">
         <v>10.3</v>
@@ -4613,275 +4715,121 @@
         <v>9.6</v>
       </c>
       <c r="G99" s="34">
-        <v>21.8</v>
+        <v>49</v>
       </c>
       <c r="H99" s="34">
-        <v>5.6</v>
+        <v>27</v>
       </c>
       <c r="I99" s="34">
-        <v>14.1</v>
+        <v>45</v>
       </c>
       <c r="J99" s="35">
-        <v>9.4E-2</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="16" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="C100" s="1"/>
+        <v>238</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>165</v>
+      </c>
       <c r="D100" s="3" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="E100" s="34">
-        <v>10.3</v>
+        <v>27</v>
       </c>
       <c r="F100" s="34">
-        <v>9.6</v>
+        <v>24</v>
       </c>
       <c r="G100" s="34">
-        <v>21.8</v>
+        <v>55</v>
       </c>
       <c r="H100" s="34">
-        <v>5.6</v>
+        <v>33</v>
       </c>
       <c r="I100" s="34">
-        <v>14.1</v>
+        <v>70</v>
       </c>
       <c r="J100" s="35">
-        <v>9.4E-2</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="16" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>100</v>
+        <v>241</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E101" s="34">
-        <v>10.72</v>
-      </c>
-      <c r="F101" s="34">
-        <v>9.7200000000000006</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="E101" s="34"/>
+      <c r="F101" s="34"/>
       <c r="G101" s="34">
-        <v>28</v>
+        <v>50.9</v>
       </c>
       <c r="H101" s="34">
-        <v>28</v>
+        <v>39.6</v>
       </c>
       <c r="I101" s="34">
-        <v>34.5</v>
+        <v>60</v>
       </c>
       <c r="J101" s="35">
-        <v>0.03</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="16" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>165</v>
+        <v>244</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="E102" s="34">
-        <v>10.3</v>
+        <v>30</v>
       </c>
       <c r="F102" s="34">
-        <v>9.6</v>
+        <v>28</v>
       </c>
       <c r="G102" s="34">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H102" s="34">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="I102" s="34">
         <v>45</v>
       </c>
       <c r="J102" s="35">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="103" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="16" t="s">
-        <v>237</v>
-      </c>
+      <c r="A103" s="16"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
-      <c r="D103" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E103" s="34">
-        <v>15.6</v>
-      </c>
-      <c r="F103" s="34">
-        <v>14.6</v>
-      </c>
-      <c r="G103" s="34">
-        <v>54</v>
-      </c>
-      <c r="H103" s="34">
-        <v>30</v>
-      </c>
-      <c r="I103" s="34">
-        <v>44.5</v>
-      </c>
-      <c r="J103" s="35">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A104" s="16" t="s">
-        <v>238</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E104" s="34">
-        <v>10.3</v>
-      </c>
-      <c r="F104" s="34">
-        <v>9.6</v>
-      </c>
-      <c r="G104" s="34">
-        <v>49</v>
-      </c>
-      <c r="H104" s="34">
-        <v>27</v>
-      </c>
-      <c r="I104" s="34">
-        <v>45</v>
-      </c>
-      <c r="J104" s="35">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A105" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E105" s="34">
-        <v>27</v>
-      </c>
-      <c r="F105" s="34">
-        <v>24</v>
-      </c>
-      <c r="G105" s="34">
-        <v>55</v>
-      </c>
-      <c r="H105" s="34">
-        <v>33</v>
-      </c>
-      <c r="I105" s="34">
-        <v>70</v>
-      </c>
-      <c r="J105" s="35">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="16" t="s">
-        <v>242</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E106" s="34"/>
-      <c r="F106" s="34"/>
-      <c r="G106" s="34">
-        <v>50.9</v>
-      </c>
-      <c r="H106" s="34">
-        <v>39.6</v>
-      </c>
-      <c r="I106" s="34">
-        <v>60</v>
-      </c>
-      <c r="J106" s="35">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A107" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="E107" s="34">
-        <v>30</v>
-      </c>
-      <c r="F107" s="34">
-        <v>28</v>
-      </c>
-      <c r="G107" s="34">
-        <v>48</v>
-      </c>
-      <c r="H107" s="34">
-        <v>51</v>
-      </c>
-      <c r="I107" s="34">
-        <v>45</v>
-      </c>
-      <c r="J107" s="35">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A108" s="16"/>
-      <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
-      <c r="D108" s="3"/>
-      <c r="E108" s="34"/>
-      <c r="F108" s="34"/>
-      <c r="G108" s="34"/>
-      <c r="H108" s="34"/>
-      <c r="I108" s="34"/>
-      <c r="J108" s="35"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="34"/>
+      <c r="F103" s="34"/>
+      <c r="G103" s="34"/>
+      <c r="H103" s="34"/>
+      <c r="I103" s="34"/>
+      <c r="J103" s="35"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J77" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Case Size.xlsx
+++ b/Case Size.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\product catalogue\product catalogue app v2\.claude\worktrees\youthful-dhawan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F54408-604A-44CE-8E42-A1C9BF5D3350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C739EE-4E21-4850-97F9-5E5FDDFB6E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="246">
   <si>
     <t>Description</t>
   </si>
@@ -732,18 +732,12 @@
     <t>2 doz</t>
   </si>
   <si>
-    <t>Sacred Element Organic Incense Sticks 10 sticks</t>
-  </si>
-  <si>
     <t>Product - 10 Sticks</t>
   </si>
   <si>
     <t>24 doz</t>
   </si>
   <si>
-    <t>Sacred Element Organic Incense Sticks 8 sticks</t>
-  </si>
-  <si>
     <t>Product - 8 Sticks</t>
   </si>
   <si>
@@ -787,6 +781,12 @@
   </si>
   <si>
     <t xml:space="preserve">12 Doz </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sacred Element Organic Incense Sticks 10 sticks </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sacred Element Organic Incense Sticks 8 sticks </t>
   </si>
 </sst>
 </file>
@@ -4366,7 +4366,9 @@
       <c r="B88" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C88" s="1"/>
+      <c r="C88" s="3" t="s">
+        <v>213</v>
+      </c>
       <c r="D88" s="3" t="s">
         <v>213</v>
       </c>
@@ -4396,7 +4398,9 @@
       <c r="B89" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C89" s="1"/>
+      <c r="C89" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="D89" s="3" t="s">
         <v>215</v>
       </c>
@@ -4545,15 +4549,15 @@
     </row>
     <row r="94" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="C94" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C94" s="1"/>
-      <c r="D94" s="3" t="s">
-        <v>229</v>
-      </c>
+      <c r="D94" s="3"/>
       <c r="E94" s="34">
         <v>10.3</v>
       </c>
@@ -4575,15 +4579,15 @@
     </row>
     <row r="95" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="16" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C95" s="1"/>
-      <c r="D95" s="3" t="s">
         <v>229</v>
       </c>
+      <c r="C95" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D95" s="3"/>
       <c r="E95" s="34">
         <v>10.3</v>
       </c>
@@ -4605,7 +4609,7 @@
     </row>
     <row r="96" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="16" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>100</v>
@@ -4637,7 +4641,7 @@
     </row>
     <row r="97" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="16" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>19</v>
@@ -4646,7 +4650,7 @@
         <v>165</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E97" s="34">
         <v>10.3</v>
@@ -4669,13 +4673,13 @@
     </row>
     <row r="98" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="16" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B98" s="1"/>
-      <c r="C98" s="1"/>
-      <c r="D98" s="3" t="s">
+      <c r="C98" s="1" t="s">
         <v>164</v>
       </c>
+      <c r="D98" s="3"/>
       <c r="E98" s="34">
         <v>15.6</v>
       </c>
@@ -4697,7 +4701,7 @@
     </row>
     <row r="99" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="16" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>19</v>
@@ -4706,7 +4710,7 @@
         <v>165</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E99" s="34">
         <v>10.3</v>
@@ -4729,16 +4733,16 @@
     </row>
     <row r="100" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="16" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>165</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E100" s="34">
         <v>27</v>
@@ -4761,16 +4765,16 @@
     </row>
     <row r="101" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="16" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>165</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E101" s="34"/>
       <c r="F101" s="34"/>
@@ -4789,16 +4793,16 @@
     </row>
     <row r="102" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="16" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>210</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E102" s="34">
         <v>30</v>

--- a/Case Size.xlsx
+++ b/Case Size.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\product catalogue\product catalogue app v2\.claude\worktrees\youthful-dhawan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C739EE-4E21-4850-97F9-5E5FDDFB6E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EADBB645-6F6A-471D-95CF-FD3BB376FF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -613,9 +613,6 @@
     <t>SMUDGING INDULGENCE MASALA GIFT PACK</t>
   </si>
   <si>
-    <t xml:space="preserve">7 CHAKRA </t>
-  </si>
-  <si>
     <t>NEW AGE MASALA 15 GMS</t>
   </si>
   <si>
@@ -632,9 +629,6 @@
   </si>
   <si>
     <t>Glass Jar Smudge Candle 185 gms</t>
-  </si>
-  <si>
-    <t>Manifestation Candles</t>
   </si>
   <si>
     <t>Manifestation series candles are designed to help you focus your intentions and channel positive energy toward your goals. Each candle is crafted with specific colors, scents, and symbols to align with different aspirations, such as love, abundance, or peace</t>
@@ -787,6 +781,12 @@
   </si>
   <si>
     <t xml:space="preserve">Sacred Element Organic Incense Sticks 8 sticks </t>
+  </si>
+  <si>
+    <t>Manifestation Candle</t>
+  </si>
+  <si>
+    <t>7 CHAKRA STONE</t>
   </si>
 </sst>
 </file>
@@ -1917,7 +1917,7 @@
     </row>
     <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="16" t="s">
-        <v>188</v>
+        <v>245</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>14</v>
@@ -2989,7 +2989,7 @@
     </row>
     <row r="44" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="71" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>57</v>
@@ -3147,7 +3147,7 @@
     </row>
     <row r="49" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>63</v>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="78" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>102</v>
@@ -4076,7 +4076,7 @@
         <v>106</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>177</v>
@@ -4105,16 +4105,16 @@
     </row>
     <row r="80" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="C80" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C80" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="D80" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E80" s="34">
         <v>11.08</v>
@@ -4137,10 +4137,10 @@
     </row>
     <row r="81" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="16" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>180</v>
@@ -4169,10 +4169,10 @@
     </row>
     <row r="82" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="16" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>177</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="83" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>104</v>
@@ -4233,13 +4233,13 @@
     </row>
     <row r="84" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>197</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>40</v>
@@ -4265,16 +4265,16 @@
     </row>
     <row r="85" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="D85" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E85" s="34">
         <v>9.5440000000000005</v>
@@ -4297,13 +4297,13 @@
     </row>
     <row r="86" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>208</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>67</v>
@@ -4329,13 +4329,13 @@
     </row>
     <row r="87" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="16" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>67</v>
@@ -4361,16 +4361,16 @@
     </row>
     <row r="88" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="D88" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E88" s="34">
         <v>20</v>
@@ -4393,16 +4393,16 @@
     </row>
     <row r="89" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="16" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E89" s="34">
         <v>16</v>
@@ -4425,16 +4425,16 @@
     </row>
     <row r="90" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="E90" s="34">
         <v>9.5</v>
@@ -4457,10 +4457,10 @@
     </row>
     <row r="91" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="16" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>177</v>
@@ -4487,16 +4487,16 @@
     </row>
     <row r="92" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D92" s="3" t="s">
         <v>222</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>224</v>
       </c>
       <c r="E92" s="34">
         <v>7</v>
@@ -4519,14 +4519,14 @@
     </row>
     <row r="93" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="16" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>104</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E93" s="34">
         <v>12.75</v>
@@ -4549,13 +4549,13 @@
     </row>
     <row r="94" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="16" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D94" s="3"/>
       <c r="E94" s="34">
@@ -4579,13 +4579,13 @@
     </row>
     <row r="95" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="16" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D95" s="3"/>
       <c r="E95" s="34">
@@ -4609,7 +4609,7 @@
     </row>
     <row r="96" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>100</v>
@@ -4641,7 +4641,7 @@
     </row>
     <row r="97" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="16" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>19</v>
@@ -4650,7 +4650,7 @@
         <v>165</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E97" s="34">
         <v>10.3</v>
@@ -4673,7 +4673,7 @@
     </row>
     <row r="98" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="16" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="1" t="s">
@@ -4701,7 +4701,7 @@
     </row>
     <row r="99" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="16" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>19</v>
@@ -4710,7 +4710,7 @@
         <v>165</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E99" s="34">
         <v>10.3</v>
@@ -4733,16 +4733,16 @@
     </row>
     <row r="100" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="16" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>165</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E100" s="34">
         <v>27</v>
@@ -4765,16 +4765,16 @@
     </row>
     <row r="101" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="16" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>165</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E101" s="34"/>
       <c r="F101" s="34"/>
@@ -4793,16 +4793,16 @@
     </row>
     <row r="102" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D102" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>243</v>
       </c>
       <c r="E102" s="34">
         <v>30</v>

--- a/Case Size.xlsx
+++ b/Case Size.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\product catalogue\product catalogue app v2\.claude\worktrees\youthful-dhawan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EADBB645-6F6A-471D-95CF-FD3BB376FF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8941C7CC-601B-416E-8CE9-F3AF13022790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4836,7 +4836,6 @@
       <c r="J103" s="35"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J77" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A77">
     <sortCondition ref="A8:A77"/>
   </sortState>

--- a/Case Size.xlsx
+++ b/Case Size.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\product catalogue\product catalogue app v2\.claude\worktrees\youthful-dhawan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8941C7CC-601B-416E-8CE9-F3AF13022790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A4DEB8-D745-4D1A-85D0-9722EB1721AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="246">
   <si>
     <t>Description</t>
   </si>
@@ -777,16 +777,16 @@
     <t xml:space="preserve">12 Doz </t>
   </si>
   <si>
-    <t xml:space="preserve">Sacred Element Organic Incense Sticks 10 sticks </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sacred Element Organic Incense Sticks 8 sticks </t>
-  </si>
-  <si>
     <t>Manifestation Candle</t>
   </si>
   <si>
     <t>7 CHAKRA STONE</t>
+  </si>
+  <si>
+    <t>Sacred Element Organic Incense Sticks 10</t>
+  </si>
+  <si>
+    <t>Sacred Element Organic Incense Sticks 8</t>
   </si>
 </sst>
 </file>
@@ -798,7 +798,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -832,6 +832,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1093,7 +1099,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1329,6 +1335,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1610,7 +1619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="44.36328125" style="13" bestFit="1" customWidth="1"/>
@@ -1917,7 +1926,7 @@
     </row>
     <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="16" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>14</v>
@@ -4233,7 +4242,7 @@
     </row>
     <row r="84" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="16" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>194</v>
@@ -4296,43 +4305,23 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E86" s="34">
-        <v>7</v>
-      </c>
-      <c r="F86" s="34">
-        <v>5</v>
-      </c>
-      <c r="G86" s="34">
-        <v>46.5</v>
-      </c>
-      <c r="H86" s="34">
-        <v>36.5</v>
-      </c>
-      <c r="I86" s="34">
-        <v>55</v>
-      </c>
-      <c r="J86" s="35">
-        <v>0.09</v>
-      </c>
+      <c r="A86" s="16"/>
+      <c r="B86" s="1"/>
+      <c r="C86" s="1"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="34"/>
+      <c r="F86" s="34"/>
+      <c r="G86" s="34"/>
+      <c r="H86" s="34"/>
+      <c r="I86" s="34"/>
+      <c r="J86" s="35"/>
     </row>
     <row r="87" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="16" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>206</v>
@@ -4341,253 +4330,257 @@
         <v>67</v>
       </c>
       <c r="E87" s="34">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="F87" s="34">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G87" s="34">
-        <v>48</v>
+        <v>46.5</v>
       </c>
       <c r="H87" s="34">
-        <v>51</v>
+        <v>36.5</v>
       </c>
       <c r="I87" s="34">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="J87" s="35">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="16" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>211</v>
+        <v>67</v>
       </c>
       <c r="E88" s="34">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F88" s="34">
-        <v>19.2</v>
+        <v>28</v>
       </c>
       <c r="G88" s="34">
-        <v>48.5</v>
+        <v>48</v>
       </c>
       <c r="H88" s="34">
-        <v>40.5</v>
+        <v>51</v>
       </c>
       <c r="I88" s="34">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J88" s="35">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="16" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E89" s="34">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F89" s="34">
-        <v>15</v>
+        <v>19.2</v>
       </c>
       <c r="G89" s="34">
-        <v>22</v>
+        <v>48.5</v>
       </c>
       <c r="H89" s="34">
-        <v>7.8</v>
+        <v>40.5</v>
       </c>
       <c r="I89" s="34">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="J89" s="35">
-        <v>9.2999999999999999E-2</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="16" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>217</v>
+        <v>212</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>213</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E90" s="34">
-        <v>9.5</v>
+        <v>16</v>
       </c>
       <c r="F90" s="34">
-        <v>9.3000000000000007</v>
+        <v>15</v>
       </c>
       <c r="G90" s="34">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="H90" s="34">
-        <v>28</v>
+        <v>7.8</v>
       </c>
       <c r="I90" s="34">
-        <v>33.5</v>
+        <v>21</v>
       </c>
       <c r="J90" s="35">
-        <v>0.03</v>
+        <v>9.2999999999999999E-2</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="16" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="D91" s="3"/>
+        <v>217</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>216</v>
+      </c>
       <c r="E91" s="34">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="F91" s="34">
-        <v>6</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="G91" s="34">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H91" s="34">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="I91" s="34">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="J91" s="35">
-        <v>7.0000000000000007E-2</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="16" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>222</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="D92" s="3"/>
       <c r="E92" s="34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F92" s="34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G92" s="34">
-        <v>46.5</v>
+        <v>38</v>
       </c>
       <c r="H92" s="34">
-        <v>36.5</v>
+        <v>56</v>
       </c>
       <c r="I92" s="34">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="J92" s="35">
-        <v>0.09</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="16" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C93" s="1"/>
+        <v>221</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>206</v>
+      </c>
       <c r="D93" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E93" s="34">
-        <v>12.75</v>
+        <v>7</v>
       </c>
       <c r="F93" s="34">
-        <v>11.2</v>
+        <v>5</v>
       </c>
       <c r="G93" s="34">
-        <v>37.5</v>
+        <v>46.5</v>
       </c>
       <c r="H93" s="34">
-        <v>28.2</v>
+        <v>36.5</v>
       </c>
       <c r="I93" s="34">
-        <v>34.799999999999997</v>
+        <v>55</v>
       </c>
       <c r="J93" s="35">
-        <v>3.6999999999999998E-2</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="16" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="B94" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C94" s="1"/>
+      <c r="D94" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E94" s="34">
+        <v>12.75</v>
+      </c>
+      <c r="F94" s="34">
+        <v>11.2</v>
+      </c>
+      <c r="G94" s="34">
+        <v>37.5</v>
+      </c>
+      <c r="H94" s="34">
+        <v>28.2</v>
+      </c>
+      <c r="I94" s="34">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="J94" s="35">
+        <v>3.6999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A95" s="80" t="s">
+        <v>244</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D94" s="3"/>
-      <c r="E94" s="34">
-        <v>10.3</v>
-      </c>
-      <c r="F94" s="34">
-        <v>9.6</v>
-      </c>
-      <c r="G94" s="34">
-        <v>21.8</v>
-      </c>
-      <c r="H94" s="34">
-        <v>5.6</v>
-      </c>
-      <c r="I94" s="34">
-        <v>14.1</v>
-      </c>
-      <c r="J94" s="35">
-        <v>9.4E-2</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="16" t="s">
-        <v>243</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>227</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="D95" s="3"/>
+      <c r="D95" s="3" t="s">
+        <v>226</v>
+      </c>
       <c r="E95" s="34">
         <v>10.3</v>
       </c>
@@ -4608,232 +4601,264 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="16" t="s">
-        <v>228</v>
+      <c r="A96" s="80" t="s">
+        <v>245</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>177</v>
+        <v>227</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>226</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>64</v>
+        <v>226</v>
       </c>
       <c r="E96" s="34">
-        <v>10.72</v>
+        <v>10.3</v>
       </c>
       <c r="F96" s="34">
-        <v>9.7200000000000006</v>
+        <v>9.6</v>
       </c>
       <c r="G96" s="34">
-        <v>28</v>
+        <v>21.8</v>
       </c>
       <c r="H96" s="34">
-        <v>28</v>
+        <v>5.6</v>
       </c>
       <c r="I96" s="34">
-        <v>34.5</v>
+        <v>14.1</v>
       </c>
       <c r="J96" s="35">
-        <v>0.03</v>
+        <v>9.4E-2</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>230</v>
+        <v>64</v>
       </c>
       <c r="E97" s="34">
-        <v>10.3</v>
+        <v>10.72</v>
       </c>
       <c r="F97" s="34">
-        <v>9.6</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="G97" s="34">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="H97" s="34">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I97" s="34">
-        <v>45</v>
+        <v>34.5</v>
       </c>
       <c r="J97" s="35">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="B98" s="1"/>
+        <v>229</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="C98" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D98" s="3"/>
+        <v>165</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>230</v>
+      </c>
       <c r="E98" s="34">
-        <v>15.6</v>
+        <v>10.3</v>
       </c>
       <c r="F98" s="34">
-        <v>14.6</v>
+        <v>9.6</v>
       </c>
       <c r="G98" s="34">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H98" s="34">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I98" s="34">
-        <v>44.5</v>
+        <v>45</v>
       </c>
       <c r="J98" s="35">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="B99" s="1"/>
       <c r="C99" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>230</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="D99" s="3"/>
       <c r="E99" s="34">
-        <v>10.3</v>
+        <v>15.6</v>
       </c>
       <c r="F99" s="34">
-        <v>9.6</v>
+        <v>14.6</v>
       </c>
       <c r="G99" s="34">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H99" s="34">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I99" s="34">
-        <v>45</v>
+        <v>44.5</v>
       </c>
       <c r="J99" s="35">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>234</v>
+        <v>19</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>165</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E100" s="34">
+        <v>10.3</v>
+      </c>
+      <c r="F100" s="34">
+        <v>9.6</v>
+      </c>
+      <c r="G100" s="34">
+        <v>49</v>
+      </c>
+      <c r="H100" s="34">
         <v>27</v>
       </c>
-      <c r="F100" s="34">
-        <v>24</v>
-      </c>
-      <c r="G100" s="34">
-        <v>55</v>
-      </c>
-      <c r="H100" s="34">
-        <v>33</v>
-      </c>
       <c r="I100" s="34">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="J100" s="35">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="16" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>165</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="E101" s="34"/>
-      <c r="F101" s="34"/>
+        <v>235</v>
+      </c>
+      <c r="E101" s="34">
+        <v>27</v>
+      </c>
+      <c r="F101" s="34">
+        <v>24</v>
+      </c>
       <c r="G101" s="34">
-        <v>50.9</v>
+        <v>55</v>
       </c>
       <c r="H101" s="34">
-        <v>39.6</v>
+        <v>33</v>
       </c>
       <c r="I101" s="34">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J101" s="35">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E102" s="34"/>
+      <c r="F102" s="34"/>
+      <c r="G102" s="34">
+        <v>50.9</v>
+      </c>
+      <c r="H102" s="34">
+        <v>39.6</v>
+      </c>
+      <c r="I102" s="34">
+        <v>60</v>
+      </c>
+      <c r="J102" s="35">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A103" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B103" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="C103" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="D103" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="E102" s="34">
+      <c r="E103" s="34">
         <v>30</v>
       </c>
-      <c r="F102" s="34">
+      <c r="F103" s="34">
         <v>28</v>
       </c>
-      <c r="G102" s="34">
+      <c r="G103" s="34">
         <v>48</v>
       </c>
-      <c r="H102" s="34">
+      <c r="H103" s="34">
         <v>51</v>
       </c>
-      <c r="I102" s="34">
+      <c r="I103" s="34">
         <v>45</v>
       </c>
-      <c r="J102" s="35">
+      <c r="J103" s="35">
         <v>0.11</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="16"/>
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
-      <c r="D103" s="3"/>
-      <c r="E103" s="34"/>
-      <c r="F103" s="34"/>
-      <c r="G103" s="34"/>
-      <c r="H103" s="34"/>
-      <c r="I103" s="34"/>
-      <c r="J103" s="35"/>
+    <row r="104" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A104" s="16"/>
+      <c r="B104" s="1"/>
+      <c r="C104" s="1"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="34"/>
+      <c r="F104" s="34"/>
+      <c r="G104" s="34"/>
+      <c r="H104" s="34"/>
+      <c r="I104" s="34"/>
+      <c r="J104" s="35"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A77">

--- a/Case Size.xlsx
+++ b/Case Size.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\product catalogue\product catalogue app v2\.claude\worktrees\youthful-dhawan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A4DEB8-D745-4D1A-85D0-9722EB1721AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E54F4F40-C0FB-4BDF-9B83-27F6FB36F664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -783,10 +783,10 @@
     <t>7 CHAKRA STONE</t>
   </si>
   <si>
-    <t>Sacred Element Organic Incense Sticks 10</t>
-  </si>
-  <si>
     <t>Sacred Element Organic Incense Sticks 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Sacred Element Organic Incense Sticks 10 ** </t>
   </si>
 </sst>
 </file>
@@ -1099,7 +1099,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1338,6 +1338,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4569,8 +4572,8 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="80" t="s">
-        <v>244</v>
+      <c r="A95" s="81" t="s">
+        <v>245</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>225</v>
@@ -4602,7 +4605,7 @@
     </row>
     <row r="96" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="80" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>227</v>

--- a/Case Size.xlsx
+++ b/Case Size.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\product catalogue\product catalogue app v2\.claude\worktrees\youthful-dhawan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E54F4F40-C0FB-4BDF-9B83-27F6FB36F664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{361E4F06-222F-4216-A2BA-27222018355E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -783,10 +783,10 @@
     <t>7 CHAKRA STONE</t>
   </si>
   <si>
-    <t>Sacred Element Organic Incense Sticks 8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**Sacred Element Organic Incense Sticks 10 ** </t>
+    <t>Sacred Element Organic Incense 8 Sticks</t>
+  </si>
+  <si>
+    <t>Sacred Element Organic Incense 10 Sticks</t>
   </si>
 </sst>
 </file>
@@ -1099,7 +1099,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1338,9 +1338,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4572,7 +4569,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="81" t="s">
+      <c r="A95" s="80" t="s">
         <v>245</v>
       </c>
       <c r="B95" s="1" t="s">

--- a/Case Size.xlsx
+++ b/Case Size.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\product catalogue\product catalogue app v2\.claude\worktrees\youthful-dhawan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{361E4F06-222F-4216-A2BA-27222018355E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BDA9CAA-0BC9-4F4E-A961-CCB5A5330522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$102</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="246">
   <si>
     <t>Description</t>
   </si>
@@ -798,7 +798,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -832,12 +832,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -859,7 +853,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1095,11 +1089,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1336,8 +1339,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1619,7 +1628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="44.36328125" style="13" bestFit="1" customWidth="1"/>
@@ -2246,7 +2255,7 @@
         <v>9.2851200000000009E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="65" t="s">
         <v>50</v>
       </c>
@@ -4113,7 +4122,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="16" t="s">
+      <c r="A80" s="80" t="s">
         <v>196</v>
       </c>
       <c r="B80" s="1" t="s">
@@ -4145,9 +4154,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="16" t="s">
-        <v>196</v>
-      </c>
+      <c r="A81" s="81"/>
       <c r="B81" s="1" t="s">
         <v>197</v>
       </c>
@@ -4177,9 +4184,7 @@
       </c>
     </row>
     <row r="82" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="16" t="s">
-        <v>196</v>
-      </c>
+      <c r="A82" s="82"/>
       <c r="B82" s="1" t="s">
         <v>191</v>
       </c>
@@ -4305,23 +4310,43 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="16"/>
-      <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="34"/>
-      <c r="F86" s="34"/>
-      <c r="G86" s="34"/>
-      <c r="H86" s="34"/>
-      <c r="I86" s="34"/>
-      <c r="J86" s="35"/>
+      <c r="A86" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E86" s="34">
+        <v>7</v>
+      </c>
+      <c r="F86" s="34">
+        <v>5</v>
+      </c>
+      <c r="G86" s="34">
+        <v>46.5</v>
+      </c>
+      <c r="H86" s="34">
+        <v>36.5</v>
+      </c>
+      <c r="I86" s="34">
+        <v>55</v>
+      </c>
+      <c r="J86" s="35">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="87" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="16" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>206</v>
@@ -4330,250 +4355,250 @@
         <v>67</v>
       </c>
       <c r="E87" s="34">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="F87" s="34">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="G87" s="34">
-        <v>46.5</v>
+        <v>48</v>
       </c>
       <c r="H87" s="34">
-        <v>36.5</v>
+        <v>51</v>
       </c>
       <c r="I87" s="34">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J87" s="35">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="16" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>211</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>67</v>
+        <v>211</v>
       </c>
       <c r="E88" s="34">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F88" s="34">
-        <v>28</v>
+        <v>19.2</v>
       </c>
       <c r="G88" s="34">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="H88" s="34">
-        <v>51</v>
+        <v>40.5</v>
       </c>
       <c r="I88" s="34">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J88" s="35">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="16" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E89" s="34">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F89" s="34">
-        <v>19.2</v>
+        <v>15</v>
       </c>
       <c r="G89" s="34">
-        <v>48.5</v>
+        <v>22</v>
       </c>
       <c r="H89" s="34">
-        <v>40.5</v>
+        <v>7.8</v>
       </c>
       <c r="I89" s="34">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="J89" s="35">
-        <v>0.08</v>
+        <v>9.2999999999999999E-2</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="16" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>217</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E90" s="34">
-        <v>16</v>
+        <v>9.5</v>
       </c>
       <c r="F90" s="34">
-        <v>15</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="G90" s="34">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="H90" s="34">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="I90" s="34">
-        <v>21</v>
+        <v>33.5</v>
       </c>
       <c r="J90" s="35">
-        <v>9.2999999999999999E-2</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="16" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>216</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="D91" s="3"/>
       <c r="E91" s="34">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="F91" s="34">
-        <v>9.3000000000000007</v>
+        <v>6</v>
       </c>
       <c r="G91" s="34">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H91" s="34">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="I91" s="34">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="J91" s="35">
-        <v>0.03</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="16" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="D92" s="3"/>
+        <v>206</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>222</v>
+      </c>
       <c r="E92" s="34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F92" s="34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G92" s="34">
-        <v>38</v>
+        <v>46.5</v>
       </c>
       <c r="H92" s="34">
-        <v>56</v>
+        <v>36.5</v>
       </c>
       <c r="I92" s="34">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="J92" s="35">
-        <v>7.0000000000000007E-2</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="16" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>206</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="C93" s="1"/>
       <c r="D93" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E93" s="34">
-        <v>7</v>
+        <v>12.75</v>
       </c>
       <c r="F93" s="34">
-        <v>5</v>
+        <v>11.2</v>
       </c>
       <c r="G93" s="34">
-        <v>46.5</v>
+        <v>37.5</v>
       </c>
       <c r="H93" s="34">
-        <v>36.5</v>
+        <v>28.2</v>
       </c>
       <c r="I93" s="34">
-        <v>55</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="J93" s="35">
-        <v>0.09</v>
+        <v>3.6999999999999998E-2</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="16" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C94" s="1"/>
+        <v>225</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>226</v>
+      </c>
       <c r="D94" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E94" s="34">
-        <v>12.75</v>
+        <v>10.3</v>
       </c>
       <c r="F94" s="34">
-        <v>11.2</v>
+        <v>9.6</v>
       </c>
       <c r="G94" s="34">
-        <v>37.5</v>
+        <v>21.8</v>
       </c>
       <c r="H94" s="34">
-        <v>28.2</v>
+        <v>5.6</v>
       </c>
       <c r="I94" s="34">
-        <v>34.799999999999997</v>
+        <v>14.1</v>
       </c>
       <c r="J94" s="35">
-        <v>3.6999999999999998E-2</v>
+        <v>9.4E-2</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="80" t="s">
-        <v>245</v>
+      <c r="A95" s="16" t="s">
+        <v>244</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>226</v>
@@ -4601,272 +4626,242 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="80" t="s">
-        <v>244</v>
+      <c r="A96" s="16" t="s">
+        <v>228</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>226</v>
+        <v>100</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>177</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>226</v>
+        <v>64</v>
       </c>
       <c r="E96" s="34">
-        <v>10.3</v>
+        <v>10.72</v>
       </c>
       <c r="F96" s="34">
-        <v>9.6</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="G96" s="34">
-        <v>21.8</v>
+        <v>28</v>
       </c>
       <c r="H96" s="34">
-        <v>5.6</v>
+        <v>28</v>
       </c>
       <c r="I96" s="34">
-        <v>14.1</v>
+        <v>34.5</v>
       </c>
       <c r="J96" s="35">
-        <v>9.4E-2</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="16" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>64</v>
+        <v>230</v>
       </c>
       <c r="E97" s="34">
-        <v>10.72</v>
+        <v>10.3</v>
       </c>
       <c r="F97" s="34">
-        <v>9.7200000000000006</v>
+        <v>9.6</v>
       </c>
       <c r="G97" s="34">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="H97" s="34">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I97" s="34">
-        <v>34.5</v>
+        <v>45</v>
       </c>
       <c r="J97" s="35">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="B98" s="1"/>
       <c r="C98" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>230</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="D98" s="3"/>
       <c r="E98" s="34">
-        <v>10.3</v>
+        <v>15.6</v>
       </c>
       <c r="F98" s="34">
-        <v>9.6</v>
+        <v>14.6</v>
       </c>
       <c r="G98" s="34">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H98" s="34">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I98" s="34">
-        <v>45</v>
+        <v>44.5</v>
       </c>
       <c r="J98" s="35">
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="B99" s="1"/>
+        <v>232</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="C99" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D99" s="3"/>
+        <v>165</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>230</v>
+      </c>
       <c r="E99" s="34">
-        <v>15.6</v>
+        <v>10.3</v>
       </c>
       <c r="F99" s="34">
-        <v>14.6</v>
+        <v>9.6</v>
       </c>
       <c r="G99" s="34">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H99" s="34">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I99" s="34">
-        <v>44.5</v>
+        <v>45</v>
       </c>
       <c r="J99" s="35">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>19</v>
+        <v>234</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>165</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E100" s="34">
-        <v>10.3</v>
+        <v>27</v>
       </c>
       <c r="F100" s="34">
-        <v>9.6</v>
+        <v>24</v>
       </c>
       <c r="G100" s="34">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H100" s="34">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I100" s="34">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="J100" s="35">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="16" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>165</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="E101" s="34">
-        <v>27</v>
-      </c>
-      <c r="F101" s="34">
-        <v>24</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="E101" s="34"/>
+      <c r="F101" s="34"/>
       <c r="G101" s="34">
-        <v>55</v>
+        <v>50.9</v>
       </c>
       <c r="H101" s="34">
-        <v>33</v>
+        <v>39.6</v>
       </c>
       <c r="I101" s="34">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="J101" s="35">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="16" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>237</v>
+        <v>208</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>165</v>
+        <v>240</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="E102" s="34"/>
-      <c r="F102" s="34"/>
+        <v>241</v>
+      </c>
+      <c r="E102" s="34">
+        <v>30</v>
+      </c>
+      <c r="F102" s="34">
+        <v>28</v>
+      </c>
       <c r="G102" s="34">
-        <v>50.9</v>
+        <v>48</v>
       </c>
       <c r="H102" s="34">
-        <v>39.6</v>
+        <v>51</v>
       </c>
       <c r="I102" s="34">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J102" s="35">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="103" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E103" s="34">
-        <v>30</v>
-      </c>
-      <c r="F103" s="34">
-        <v>28</v>
-      </c>
-      <c r="G103" s="34">
-        <v>48</v>
-      </c>
-      <c r="H103" s="34">
-        <v>51</v>
-      </c>
-      <c r="I103" s="34">
-        <v>45</v>
-      </c>
-      <c r="J103" s="35">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A104" s="16"/>
-      <c r="B104" s="1"/>
-      <c r="C104" s="1"/>
-      <c r="D104" s="3"/>
-      <c r="E104" s="34"/>
-      <c r="F104" s="34"/>
-      <c r="G104" s="34"/>
-      <c r="H104" s="34"/>
-      <c r="I104" s="34"/>
-      <c r="J104" s="35"/>
+      <c r="A103" s="16"/>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="34"/>
+      <c r="F103" s="34"/>
+      <c r="G103" s="34"/>
+      <c r="H103" s="34"/>
+      <c r="I103" s="34"/>
+      <c r="J103" s="35"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J102" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A77">
     <sortCondition ref="A8:A77"/>
   </sortState>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B56:B57"/>
     <mergeCell ref="B54:B55"/>
+    <mergeCell ref="A80:A82"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Case Size.xlsx
+++ b/Case Size.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\product catalogue\product catalogue app v2\.claude\worktrees\youthful-dhawan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BDA9CAA-0BC9-4F4E-A961-CCB5A5330522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282207F5-79EF-4888-913C-9E7AE46DB1D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="246">
   <si>
     <t>Description</t>
   </si>
@@ -853,7 +853,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -1089,20 +1089,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1338,15 +1329,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4122,7 +4104,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="80" t="s">
+      <c r="A80" s="16" t="s">
         <v>196</v>
       </c>
       <c r="B80" s="1" t="s">
@@ -4154,7 +4136,9 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="81"/>
+      <c r="A81" s="16" t="s">
+        <v>196</v>
+      </c>
       <c r="B81" s="1" t="s">
         <v>197</v>
       </c>
@@ -4184,7 +4168,9 @@
       </c>
     </row>
     <row r="82" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="82"/>
+      <c r="A82" s="16" t="s">
+        <v>196</v>
+      </c>
       <c r="B82" s="1" t="s">
         <v>191</v>
       </c>
@@ -4858,10 +4844,9 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A77">
     <sortCondition ref="A8:A77"/>
   </sortState>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="B56:B57"/>
     <mergeCell ref="B54:B55"/>
-    <mergeCell ref="A80:A82"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Case Size.xlsx
+++ b/Case Size.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\product catalogue\product catalogue app v2\.claude\worktrees\youthful-dhawan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282207F5-79EF-4888-913C-9E7AE46DB1D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B269343B-CCAB-42E6-80A5-7A4B2E2DB57F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="268">
   <si>
     <t>Description</t>
   </si>
@@ -787,6 +787,83 @@
   </si>
   <si>
     <t>Sacred Element Organic Incense 10 Sticks</t>
+  </si>
+  <si>
+    <t>12 pcs in 1 box, 12 dozen in 1 Master Carton</t>
+  </si>
+  <si>
+    <t>Cup Dhoop</t>
+  </si>
+  <si>
+    <t>4 doz</t>
+  </si>
+  <si>
+    <t>12 pcs in 1 box, 4 dozen in 1 Master Carton</t>
+  </si>
+  <si>
+    <t>Ghee Diya</t>
+  </si>
+  <si>
+    <t>100 pcs Diya in a box, 4 doz in 1 Master Carton</t>
+  </si>
+  <si>
+    <t>50 pcs Diya in a box, 6 doz in 1 Master Carton</t>
+  </si>
+  <si>
+    <t>HEM Camphor</t>
+  </si>
+  <si>
+    <t>Camphor - 100g</t>
+  </si>
+  <si>
+    <t>9 Doz</t>
+  </si>
+  <si>
+    <t>108 Pcs</t>
+  </si>
+  <si>
+    <r>
+      <t>HEM Gangajal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF3D2020"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>Gangajal, 24 pc in box</t>
+  </si>
+  <si>
+    <t>1 Bottle x 900 ml, 20Pcs in 1 master carton</t>
+  </si>
+  <si>
+    <t>1 Bottle x 450 ml, 40Pcs in 1 master carton</t>
+  </si>
+  <si>
+    <t>Pooja Oil</t>
+  </si>
+  <si>
+    <t>20 pcs</t>
+  </si>
+  <si>
+    <t>40pcs</t>
+  </si>
+  <si>
+    <t>20 Pcs</t>
+  </si>
+  <si>
+    <t>40 Pcs</t>
+  </si>
+  <si>
+    <t>Pooja Samagri</t>
+  </si>
+  <si>
+    <t>White Abhir, Gulal, Kumkum, Haldi, Camphor Tablets, Moli, Pooja Supari, Akhata, Agarbatti, Agarbatti Wooden Stand, Janvi Jod, Goddess Photo, Vastra (Pooja Cloth) &amp; Dhoop.</t>
   </si>
 </sst>
 </file>
@@ -798,7 +875,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -831,6 +908,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF3D2020"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1610,7 +1693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:M116"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="44.36328125" style="13" bestFit="1" customWidth="1"/>
@@ -4643,7 +4726,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="16" t="s">
         <v>229</v>
       </c>
@@ -4675,7 +4758,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="16" t="s">
         <v>231</v>
       </c>
@@ -4703,7 +4786,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="16" t="s">
         <v>232</v>
       </c>
@@ -4735,7 +4818,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="16" t="s">
         <v>233</v>
       </c>
@@ -4767,7 +4850,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="16" t="s">
         <v>236</v>
       </c>
@@ -4795,7 +4878,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="16" t="s">
         <v>239</v>
       </c>
@@ -4827,7 +4910,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="16"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -4838,6 +4921,371 @@
       <c r="H103" s="34"/>
       <c r="I103" s="34"/>
       <c r="J103" s="35"/>
+    </row>
+    <row r="104" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A104" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="B104" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="C104" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="D104" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E104" s="16">
+        <v>25</v>
+      </c>
+      <c r="F104" s="16">
+        <v>24</v>
+      </c>
+      <c r="G104" s="16"/>
+      <c r="H104" s="16"/>
+      <c r="I104" s="16"/>
+      <c r="J104" s="16">
+        <v>0.15</v>
+      </c>
+      <c r="K104" s="16"/>
+      <c r="L104" s="16"/>
+      <c r="M104" s="16"/>
+    </row>
+    <row r="105" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A105" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="B105" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="C105" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="D105" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E105" s="16">
+        <v>29</v>
+      </c>
+      <c r="F105" s="16">
+        <v>27.5</v>
+      </c>
+      <c r="G105" s="16"/>
+      <c r="H105" s="16"/>
+      <c r="I105" s="16"/>
+      <c r="J105" s="16">
+        <v>0.15</v>
+      </c>
+      <c r="K105" s="16"/>
+      <c r="L105" s="16"/>
+      <c r="M105" s="16"/>
+    </row>
+    <row r="106" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A106" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="B106" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="C106" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D106" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="E106" s="16">
+        <v>9.6</v>
+      </c>
+      <c r="F106" s="16">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="G106" s="16"/>
+      <c r="H106" s="16"/>
+      <c r="I106" s="16"/>
+      <c r="J106" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="K106" s="16"/>
+      <c r="L106" s="16"/>
+      <c r="M106" s="16"/>
+    </row>
+    <row r="107" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A107" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="B107" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="C107" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D107" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="E107" s="16">
+        <v>15.7</v>
+      </c>
+      <c r="F107" s="16">
+        <v>14.7</v>
+      </c>
+      <c r="G107" s="16"/>
+      <c r="H107" s="16"/>
+      <c r="I107" s="16"/>
+      <c r="J107" s="16">
+        <v>5.5E-2</v>
+      </c>
+      <c r="K107" s="16"/>
+      <c r="L107" s="16"/>
+      <c r="M107" s="16"/>
+    </row>
+    <row r="108" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A108" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="B108" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="C108" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D108" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="E108" s="16">
+        <v>15.7</v>
+      </c>
+      <c r="F108" s="16">
+        <v>14.7</v>
+      </c>
+      <c r="G108" s="16"/>
+      <c r="H108" s="16"/>
+      <c r="I108" s="16"/>
+      <c r="J108" s="16">
+        <v>5.5E-2</v>
+      </c>
+      <c r="K108" s="16"/>
+      <c r="L108" s="16"/>
+      <c r="M108" s="16"/>
+    </row>
+    <row r="109" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A109" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="B109" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="C109" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="D109" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E109" s="16">
+        <v>12.55</v>
+      </c>
+      <c r="F109" s="16">
+        <v>11.45</v>
+      </c>
+      <c r="G109" s="16"/>
+      <c r="H109" s="16"/>
+      <c r="I109" s="16"/>
+      <c r="J109" s="16">
+        <v>0.06</v>
+      </c>
+      <c r="K109" s="16"/>
+      <c r="L109" s="16"/>
+      <c r="M109" s="16"/>
+    </row>
+    <row r="110" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A110" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="B110" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="C110" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="D110" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E110" s="16">
+        <v>12.55</v>
+      </c>
+      <c r="F110" s="16">
+        <v>11.45</v>
+      </c>
+      <c r="G110" s="16"/>
+      <c r="H110" s="16"/>
+      <c r="I110" s="16"/>
+      <c r="J110" s="16">
+        <v>0.06</v>
+      </c>
+      <c r="K110" s="16"/>
+      <c r="L110" s="16"/>
+      <c r="M110" s="16"/>
+    </row>
+    <row r="111" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A111" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="B111" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="C111" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="D111" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="E111" s="16">
+        <v>15.2</v>
+      </c>
+      <c r="F111" s="16">
+        <v>14.2</v>
+      </c>
+      <c r="G111" s="16"/>
+      <c r="H111" s="16"/>
+      <c r="I111" s="16"/>
+      <c r="J111" s="16">
+        <v>0.06</v>
+      </c>
+      <c r="K111" s="16"/>
+      <c r="L111" s="16"/>
+      <c r="M111" s="16"/>
+    </row>
+    <row r="112" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A112" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="B112" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="C112" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="D112" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E112" s="16">
+        <v>15.2</v>
+      </c>
+      <c r="F112" s="16">
+        <v>14.2</v>
+      </c>
+      <c r="G112" s="16"/>
+      <c r="H112" s="16"/>
+      <c r="I112" s="16"/>
+      <c r="J112" s="16">
+        <v>0.06</v>
+      </c>
+      <c r="K112" s="16"/>
+      <c r="L112" s="16"/>
+      <c r="M112" s="16"/>
+    </row>
+    <row r="113" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A113" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="B113" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="C113" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="D113" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="E113" s="16">
+        <v>13.2</v>
+      </c>
+      <c r="F113" s="16">
+        <v>12.5</v>
+      </c>
+      <c r="G113" s="16"/>
+      <c r="H113" s="16"/>
+      <c r="I113" s="16"/>
+      <c r="J113" s="16">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A114" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="B114" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="C114" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="D114" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="E114" s="16">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="F114" s="16">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="G114" s="16"/>
+      <c r="H114" s="16"/>
+      <c r="I114" s="16"/>
+      <c r="J114" s="16">
+        <v>4.1000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A115" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="B115" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="C115" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="D115" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="E115" s="16">
+        <v>18.86</v>
+      </c>
+      <c r="F115" s="16">
+        <v>17.239999999999998</v>
+      </c>
+      <c r="G115" s="16"/>
+      <c r="H115" s="16"/>
+      <c r="I115" s="16"/>
+      <c r="J115" s="16">
+        <v>4.1000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A116" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="B116" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="C116" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="D116" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E116" s="16">
+        <v>28.5</v>
+      </c>
+      <c r="F116" s="16">
+        <v>27</v>
+      </c>
+      <c r="G116" s="16"/>
+      <c r="H116" s="16"/>
+      <c r="I116" s="16"/>
+      <c r="J116" s="16">
+        <v>0.13500000000000001</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J102" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Case Size.xlsx
+++ b/Case Size.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\product catalogue\product catalogue app v2\.claude\worktrees\youthful-dhawan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B269343B-CCAB-42E6-80A5-7A4B2E2DB57F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A66A73-6461-4CA2-ADAA-43D948FE5577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1693,7 +1693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M116"/>
+  <dimension ref="A1:M115"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="44.36328125" style="13" bestFit="1" customWidth="1"/>
@@ -4911,16 +4911,33 @@
       </c>
     </row>
     <row r="103" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="16"/>
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
-      <c r="D103" s="3"/>
-      <c r="E103" s="34"/>
-      <c r="F103" s="34"/>
-      <c r="G103" s="34"/>
-      <c r="H103" s="34"/>
-      <c r="I103" s="34"/>
-      <c r="J103" s="35"/>
+      <c r="A103" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="B103" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="C103" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="D103" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E103" s="16">
+        <v>25</v>
+      </c>
+      <c r="F103" s="16">
+        <v>24</v>
+      </c>
+      <c r="G103" s="16"/>
+      <c r="H103" s="16"/>
+      <c r="I103" s="16"/>
+      <c r="J103" s="16">
+        <v>0.15</v>
+      </c>
+      <c r="K103" s="16"/>
+      <c r="L103" s="16"/>
+      <c r="M103" s="16"/>
     </row>
     <row r="104" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="16" t="s">
@@ -4936,10 +4953,10 @@
         <v>13</v>
       </c>
       <c r="E104" s="16">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F104" s="16">
-        <v>24</v>
+        <v>27.5</v>
       </c>
       <c r="G104" s="16"/>
       <c r="H104" s="16"/>
@@ -4956,25 +4973,25 @@
         <v>247</v>
       </c>
       <c r="B105" s="16" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C105" s="16" t="s">
-        <v>240</v>
+        <v>22</v>
       </c>
       <c r="D105" s="16" t="s">
-        <v>13</v>
+        <v>248</v>
       </c>
       <c r="E105" s="16">
-        <v>29</v>
+        <v>9.6</v>
       </c>
       <c r="F105" s="16">
-        <v>27.5</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="G105" s="16"/>
       <c r="H105" s="16"/>
       <c r="I105" s="16"/>
       <c r="J105" s="16">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="K105" s="16"/>
       <c r="L105" s="16"/>
@@ -4982,28 +4999,28 @@
     </row>
     <row r="106" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="16" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B106" s="16" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C106" s="16" t="s">
         <v>22</v>
       </c>
       <c r="D106" s="16" t="s">
-        <v>248</v>
+        <v>199</v>
       </c>
       <c r="E106" s="16">
-        <v>9.6</v>
+        <v>15.7</v>
       </c>
       <c r="F106" s="16">
-        <v>8.8000000000000007</v>
+        <v>14.7</v>
       </c>
       <c r="G106" s="16"/>
       <c r="H106" s="16"/>
       <c r="I106" s="16"/>
       <c r="J106" s="16">
-        <v>0.05</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K106" s="16"/>
       <c r="L106" s="16"/>
@@ -5043,25 +5060,25 @@
         <v>250</v>
       </c>
       <c r="B108" s="16" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C108" s="16" t="s">
-        <v>22</v>
+        <v>177</v>
       </c>
       <c r="D108" s="16" t="s">
-        <v>199</v>
+        <v>58</v>
       </c>
       <c r="E108" s="16">
-        <v>15.7</v>
+        <v>12.55</v>
       </c>
       <c r="F108" s="16">
-        <v>14.7</v>
+        <v>11.45</v>
       </c>
       <c r="G108" s="16"/>
       <c r="H108" s="16"/>
       <c r="I108" s="16"/>
       <c r="J108" s="16">
-        <v>5.5E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K108" s="16"/>
       <c r="L108" s="16"/>
@@ -5098,22 +5115,22 @@
     </row>
     <row r="110" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="16" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B110" s="16" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C110" s="16" t="s">
-        <v>177</v>
+        <v>256</v>
       </c>
       <c r="D110" s="16" t="s">
-        <v>58</v>
+        <v>255</v>
       </c>
       <c r="E110" s="16">
-        <v>12.55</v>
+        <v>15.2</v>
       </c>
       <c r="F110" s="16">
-        <v>11.45</v>
+        <v>14.2</v>
       </c>
       <c r="G110" s="16"/>
       <c r="H110" s="16"/>
@@ -5133,10 +5150,10 @@
         <v>254</v>
       </c>
       <c r="C111" s="16" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="D111" s="16" t="s">
-        <v>255</v>
+        <v>67</v>
       </c>
       <c r="E111" s="16">
         <v>15.2</v>
@@ -5156,57 +5173,54 @@
     </row>
     <row r="112" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="16" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B112" s="16" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C112" s="16" t="s">
-        <v>240</v>
+        <v>185</v>
       </c>
       <c r="D112" s="16" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="E112" s="16">
-        <v>15.2</v>
+        <v>13.2</v>
       </c>
       <c r="F112" s="16">
-        <v>14.2</v>
+        <v>12.5</v>
       </c>
       <c r="G112" s="16"/>
       <c r="H112" s="16"/>
       <c r="I112" s="16"/>
       <c r="J112" s="16">
-        <v>0.06</v>
-      </c>
-      <c r="K112" s="16"/>
-      <c r="L112" s="16"/>
-      <c r="M112" s="16"/>
+        <v>0.02</v>
+      </c>
     </row>
     <row r="113" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="16" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B113" s="16" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C113" s="16" t="s">
-        <v>185</v>
+        <v>264</v>
       </c>
       <c r="D113" s="16" t="s">
-        <v>105</v>
+        <v>262</v>
       </c>
       <c r="E113" s="16">
-        <v>13.2</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="F113" s="16">
-        <v>12.5</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="G113" s="16"/>
       <c r="H113" s="16"/>
       <c r="I113" s="16"/>
       <c r="J113" s="16">
-        <v>0.02</v>
+        <v>4.1000000000000002E-2</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5214,19 +5228,19 @@
         <v>261</v>
       </c>
       <c r="B114" s="16" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C114" s="16" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D114" s="16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E114" s="16">
-        <v>17.600000000000001</v>
+        <v>18.86</v>
       </c>
       <c r="F114" s="16">
-        <v>16.600000000000001</v>
+        <v>17.239999999999998</v>
       </c>
       <c r="G114" s="16"/>
       <c r="H114" s="16"/>
@@ -5235,55 +5249,29 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:10" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="16" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B115" s="16" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="C115" s="16" t="s">
-        <v>265</v>
+        <v>177</v>
       </c>
       <c r="D115" s="16" t="s">
-        <v>263</v>
+        <v>58</v>
       </c>
       <c r="E115" s="16">
-        <v>18.86</v>
+        <v>28.5</v>
       </c>
       <c r="F115" s="16">
-        <v>17.239999999999998</v>
+        <v>27</v>
       </c>
       <c r="G115" s="16"/>
       <c r="H115" s="16"/>
       <c r="I115" s="16"/>
       <c r="J115" s="16">
-        <v>4.1000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A116" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="B116" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="C116" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="D116" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="E116" s="16">
-        <v>28.5</v>
-      </c>
-      <c r="F116" s="16">
-        <v>27</v>
-      </c>
-      <c r="G116" s="16"/>
-      <c r="H116" s="16"/>
-      <c r="I116" s="16"/>
-      <c r="J116" s="16">
         <v>0.13500000000000001</v>
       </c>
     </row>

--- a/Case Size.xlsx
+++ b/Case Size.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maa00\product catalogue\product catalogue app v2\.claude\worktrees\youthful-dhawan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A66A73-6461-4CA2-ADAA-43D948FE5577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF167F7-6496-481E-BA06-CC015FB2953F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="268">
   <si>
     <t>Description</t>
   </si>
@@ -936,7 +936,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1172,11 +1172,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1341,21 +1350,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1374,43 +1368,52 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1705,7 +1708,7 @@
     <col min="7" max="7" width="8.7265625" style="13" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.81640625" style="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.54296875" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.36328125" style="76" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.36328125" style="68" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -1741,7 +1744,7 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="15" t="s">
         <v>183</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1773,7 +1776,7 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="15" t="s">
         <v>183</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1805,7 +1808,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="65" t="s">
+      <c r="A4" s="15" t="s">
         <v>183</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1837,7 +1840,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="15" t="s">
         <v>183</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -2095,7 +2098,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="66" t="s">
+      <c r="A13" s="61" t="s">
         <v>116</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -2127,7 +2130,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="70" t="s">
+      <c r="A14" s="61" t="s">
         <v>56</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -2159,7 +2162,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="70" t="s">
+      <c r="A15" s="61" t="s">
         <v>56</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -2191,7 +2194,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="70" t="s">
+      <c r="A16" s="61" t="s">
         <v>56</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -2288,7 +2291,7 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="65" t="s">
+      <c r="A19" s="15" t="s">
         <v>50</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -2321,10 +2324,10 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="65" t="s">
+      <c r="A20" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="64" t="s">
+      <c r="B20" s="59" t="s">
         <v>182</v>
       </c>
       <c r="C20" s="3" t="s">
@@ -2353,7 +2356,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="57" t="s">
+      <c r="A21" s="19" t="s">
         <v>50</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -2385,7 +2388,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="57" t="s">
+      <c r="A22" s="19" t="s">
         <v>50</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -2417,7 +2420,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="57" t="s">
+      <c r="A23" s="19" t="s">
         <v>50</v>
       </c>
       <c r="B23" s="5" t="s">
@@ -2449,7 +2452,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="65" t="s">
+      <c r="A24" s="15" t="s">
         <v>50</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -2482,7 +2485,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="65" t="s">
+      <c r="A25" s="15" t="s">
         <v>50</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -2547,7 +2550,7 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="57" t="s">
+      <c r="A27" s="19" t="s">
         <v>76</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -2579,7 +2582,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="57" t="s">
+      <c r="A28" s="19" t="s">
         <v>72</v>
       </c>
       <c r="B28" s="6"/>
@@ -2609,7 +2612,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="71" t="s">
+      <c r="A29" s="64" t="s">
         <v>103</v>
       </c>
       <c r="B29" s="6"/>
@@ -2852,7 +2855,7 @@
       <c r="I36" s="43">
         <v>48</v>
       </c>
-      <c r="J36" s="73">
+      <c r="J36" s="65">
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
@@ -2884,7 +2887,7 @@
       <c r="I37" s="43">
         <v>28.5</v>
       </c>
-      <c r="J37" s="73">
+      <c r="J37" s="65">
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
@@ -2914,7 +2917,7 @@
       <c r="I38" s="6">
         <v>35</v>
       </c>
-      <c r="J38" s="74">
+      <c r="J38" s="66">
         <v>0.05</v>
       </c>
     </row>
@@ -2944,7 +2947,7 @@
       <c r="I39" s="6">
         <v>67.5</v>
       </c>
-      <c r="J39" s="74">
+      <c r="J39" s="66">
         <v>0.05</v>
       </c>
     </row>
@@ -2974,7 +2977,7 @@
       <c r="I40" s="6">
         <v>35</v>
       </c>
-      <c r="J40" s="74">
+      <c r="J40" s="66">
         <v>0.05</v>
       </c>
     </row>
@@ -3004,12 +3007,12 @@
       <c r="I41" s="6">
         <v>27</v>
       </c>
-      <c r="J41" s="74">
+      <c r="J41" s="66">
         <v>0.04</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="71" t="s">
+      <c r="A42" s="64" t="s">
         <v>55</v>
       </c>
       <c r="B42" s="6"/>
@@ -3034,7 +3037,7 @@
       <c r="I42" s="6">
         <v>35</v>
       </c>
-      <c r="J42" s="74">
+      <c r="J42" s="66">
         <v>0.05</v>
       </c>
     </row>
@@ -3071,7 +3074,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="71" t="s">
+      <c r="A44" s="64" t="s">
         <v>188</v>
       </c>
       <c r="B44" s="3" t="s">
@@ -3103,7 +3106,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="59" t="s">
+      <c r="A45" s="64" t="s">
         <v>68</v>
       </c>
       <c r="B45" s="3"/>
@@ -3133,7 +3136,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="59" t="s">
+      <c r="A46" s="64" t="s">
         <v>68</v>
       </c>
       <c r="B46" s="3"/>
@@ -3163,7 +3166,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="72" t="s">
+      <c r="A47" s="16" t="s">
         <v>68</v>
       </c>
       <c r="B47" s="3" t="s">
@@ -3202,7 +3205,7 @@
       <c r="B48" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C48" s="62" t="s">
+      <c r="C48" s="57" t="s">
         <v>178</v>
       </c>
       <c r="D48" s="3" t="s">
@@ -3235,7 +3238,7 @@
       <c r="B49" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C49" s="62" t="s">
+      <c r="C49" s="57" t="s">
         <v>58</v>
       </c>
       <c r="D49" s="7" t="s">
@@ -3299,7 +3302,7 @@
       <c r="B51" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C51" s="61" t="s">
+      <c r="C51" s="56" t="s">
         <v>17</v>
       </c>
       <c r="D51" s="55" t="s">
@@ -3328,7 +3331,7 @@
       <c r="A52" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="C52" s="61" t="s">
+      <c r="C52" s="56" t="s">
         <v>79</v>
       </c>
       <c r="D52" s="55" t="s">
@@ -3354,11 +3357,11 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="71" t="s">
+      <c r="A53" s="64" t="s">
         <v>93</v>
       </c>
       <c r="B53" s="9"/>
-      <c r="C53" s="61" t="s">
+      <c r="C53" s="56" t="s">
         <v>164</v>
       </c>
       <c r="D53" s="55" t="s">
@@ -3387,10 +3390,10 @@
       <c r="A54" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="B54" s="77" t="s">
+      <c r="B54" s="69" t="s">
         <v>71</v>
       </c>
-      <c r="C54" s="61" t="s">
+      <c r="C54" s="56" t="s">
         <v>67</v>
       </c>
       <c r="D54" s="29" t="s">
@@ -3416,10 +3419,10 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="68" t="s">
+      <c r="A55" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="B55" s="79"/>
+      <c r="B55" s="71"/>
       <c r="C55" s="6" t="s">
         <v>67</v>
       </c>
@@ -3446,10 +3449,10 @@
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A56" s="71" t="s">
+      <c r="A56" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="B56" s="77" t="s">
+      <c r="B56" s="69" t="s">
         <v>73</v>
       </c>
       <c r="C56" s="8" t="s">
@@ -3478,10 +3481,10 @@
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A57" s="69" t="s">
+      <c r="A57" s="63" t="s">
         <v>187</v>
       </c>
-      <c r="B57" s="78"/>
+      <c r="B57" s="70"/>
       <c r="C57" s="10" t="s">
         <v>67</v>
       </c>
@@ -3508,7 +3511,7 @@
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A58" s="56" t="s">
+      <c r="A58" s="75" t="s">
         <v>41</v>
       </c>
       <c r="B58" s="10" t="s">
@@ -3528,7 +3531,7 @@
       <c r="J58" s="50"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A59" s="60" t="s">
+      <c r="A59" s="76" t="s">
         <v>41</v>
       </c>
       <c r="B59" s="10" t="s">
@@ -3560,7 +3563,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="58" t="s">
+      <c r="A60" s="18" t="s">
         <v>41</v>
       </c>
       <c r="B60" s="5" t="s">
@@ -3592,7 +3595,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="65" t="s">
+      <c r="A61" s="15" t="s">
         <v>41</v>
       </c>
       <c r="B61" s="1" t="s">
@@ -3624,7 +3627,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="65" t="s">
+      <c r="A62" s="15" t="s">
         <v>41</v>
       </c>
       <c r="B62" s="1" t="s">
@@ -3656,7 +3659,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="65" t="s">
+      <c r="A63" s="15" t="s">
         <v>41</v>
       </c>
       <c r="B63" s="1" t="s">
@@ -3688,7 +3691,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="65" t="s">
+      <c r="A64" s="15" t="s">
         <v>41</v>
       </c>
       <c r="B64" s="1" t="s">
@@ -3780,7 +3783,7 @@
       <c r="I66" s="3">
         <v>46</v>
       </c>
-      <c r="J66" s="75">
+      <c r="J66" s="67">
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
@@ -3818,7 +3821,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="67" t="s">
+      <c r="A68" s="77" t="s">
         <v>70</v>
       </c>
       <c r="B68" s="1" t="s">
@@ -3856,7 +3859,7 @@
       <c r="B69" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="C69" s="63" t="s">
+      <c r="C69" s="58" t="s">
         <v>58</v>
       </c>
       <c r="D69" s="3" t="s">
@@ -4045,7 +4048,7 @@
       </c>
     </row>
     <row r="75" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="67"/>
+      <c r="A75" s="77"/>
       <c r="B75" s="3" t="s">
         <v>117</v>
       </c>
@@ -4069,11 +4072,11 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="65"/>
+      <c r="A76" s="15"/>
       <c r="B76" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="C76" s="63">
+      <c r="C76" s="58">
         <v>4</v>
       </c>
       <c r="D76" s="3">
@@ -4093,8 +4096,8 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="65"/>
-      <c r="B77" s="65" t="s">
+      <c r="A77" s="15"/>
+      <c r="B77" s="60" t="s">
         <v>184</v>
       </c>
       <c r="C77" s="3" t="s">
@@ -4911,7 +4914,7 @@
       </c>
     </row>
     <row r="103" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="16" t="s">
+      <c r="A103" s="72" t="s">
         <v>247</v>
       </c>
       <c r="B103" s="16" t="s">
@@ -4940,9 +4943,7 @@
       <c r="M103" s="16"/>
     </row>
     <row r="104" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A104" s="16" t="s">
-        <v>247</v>
-      </c>
+      <c r="A104" s="73"/>
       <c r="B104" s="16" t="s">
         <v>246</v>
       </c>
@@ -4969,9 +4970,7 @@
       <c r="M104" s="16"/>
     </row>
     <row r="105" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A105" s="16" t="s">
-        <v>247</v>
-      </c>
+      <c r="A105" s="74"/>
       <c r="B105" s="16" t="s">
         <v>249</v>
       </c>
@@ -4998,7 +4997,7 @@
       <c r="M105" s="16"/>
     </row>
     <row r="106" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="16" t="s">
+      <c r="A106" s="72" t="s">
         <v>250</v>
       </c>
       <c r="B106" s="16" t="s">
@@ -5027,9 +5026,7 @@
       <c r="M106" s="16"/>
     </row>
     <row r="107" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A107" s="16" t="s">
-        <v>250</v>
-      </c>
+      <c r="A107" s="73"/>
       <c r="B107" s="16" t="s">
         <v>251</v>
       </c>
@@ -5056,9 +5053,7 @@
       <c r="M107" s="16"/>
     </row>
     <row r="108" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A108" s="16" t="s">
-        <v>250</v>
-      </c>
+      <c r="A108" s="73"/>
       <c r="B108" s="16" t="s">
         <v>252</v>
       </c>
@@ -5085,9 +5080,7 @@
       <c r="M108" s="16"/>
     </row>
     <row r="109" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A109" s="16" t="s">
-        <v>250</v>
-      </c>
+      <c r="A109" s="74"/>
       <c r="B109" s="16" t="s">
         <v>252</v>
       </c>
@@ -5114,7 +5107,7 @@
       <c r="M109" s="16"/>
     </row>
     <row r="110" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A110" s="16" t="s">
+      <c r="A110" s="72" t="s">
         <v>253</v>
       </c>
       <c r="B110" s="16" t="s">
@@ -5143,9 +5136,7 @@
       <c r="M110" s="16"/>
     </row>
     <row r="111" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A111" s="16" t="s">
-        <v>253</v>
-      </c>
+      <c r="A111" s="74"/>
       <c r="B111" s="16" t="s">
         <v>254</v>
       </c>
@@ -5198,7 +5189,7 @@
       </c>
     </row>
     <row r="113" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A113" s="16" t="s">
+      <c r="A113" s="72" t="s">
         <v>261</v>
       </c>
       <c r="B113" s="16" t="s">
@@ -5224,9 +5215,7 @@
       </c>
     </row>
     <row r="114" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A114" s="16" t="s">
-        <v>261</v>
-      </c>
+      <c r="A114" s="74"/>
       <c r="B114" s="16" t="s">
         <v>260</v>
       </c>
@@ -5280,9 +5269,13 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A77">
     <sortCondition ref="A8:A77"/>
   </sortState>
-  <mergeCells count="2">
+  <mergeCells count="6">
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A113:A114"/>
     <mergeCell ref="B56:B57"/>
     <mergeCell ref="B54:B55"/>
+    <mergeCell ref="A103:A105"/>
+    <mergeCell ref="A106:A109"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Case Size.xlsx
+++ b/Case Size.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ee11846ce882123f/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="276" documentId="8_{B5CB9DC2-2DBC-48FC-8A4C-3FED4FBFDA8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A254269-DFA7-44A7-96E3-8858676BCCEE}"/>
+  <xr:revisionPtr revIDLastSave="297" documentId="8_{B5CB9DC2-2DBC-48FC-8A4C-3FED4FBFDA8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56518CD2-2572-42FA-B83D-418CBBC903D3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{94297B88-8998-40EB-8FA5-F929672964CF}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="99">
   <si>
     <t>Category</t>
   </si>
@@ -76,9 +76,6 @@
   </si>
   <si>
     <t>MASALA 15 GMS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PREMIUM MASALA INCENSE HEXA </t>
   </si>
   <si>
     <t>24 Doz</t>
@@ -116,20 +113,6 @@
   <si>
     <r>
       <t>AROMA OIL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <color rgb="FF3D2020"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CAR FRESHNER</t>
     </r>
     <r>
       <rPr>
@@ -409,12 +392,38 @@
   <si>
     <t>Candle Catalogue</t>
   </si>
+  <si>
+    <t>PREMIUM MASALA INCENSE (Hexa 15Stik)</t>
+  </si>
+  <si>
+    <r>
+      <t>CAR FRESHENER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF3D2020"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>ENERGY CLEANSING KIT</t>
+  </si>
+  <si>
+    <t>QATARI POWDER HEXA PACK</t>
+  </si>
+  <si>
+    <t>7 CHAKRA STONE</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -624,6 +633,12 @@
       <color rgb="FF1A0A0A"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="26">
@@ -9152,7 +9167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{624BC790-9AE4-4E34-8AB5-C11F6DB95162}">
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="41.453125" bestFit="1" customWidth="1"/>
@@ -9168,7 +9183,7 @@
   <sheetData>
     <row r="1" spans="1:10" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C1" s="3"/>
       <c r="I1" s="13"/>
@@ -9204,11 +9219,11 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" s="3">
         <v>4</v>
@@ -9231,11 +9246,11 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3">
         <v>8</v>
@@ -9258,11 +9273,11 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D5" s="3">
         <v>13</v>
@@ -9285,11 +9300,11 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6" s="3">
         <v>15.8</v>
@@ -9312,7 +9327,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="3" t="s">
@@ -9339,11 +9354,11 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" s="3">
         <v>9</v>
@@ -9366,11 +9381,11 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D9" s="3">
         <v>15</v>
@@ -9393,11 +9408,11 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="3">
         <v>16.5</v>
@@ -9420,7 +9435,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="3" t="s">
@@ -9452,7 +9467,7 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12" s="3">
         <v>10.3</v>
@@ -9476,11 +9491,11 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D13" s="3">
         <v>10.3</v>
@@ -9498,17 +9513,17 @@
         <v>45</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J13" s="5"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D14" s="3">
         <v>13.8</v>
@@ -9532,11 +9547,11 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D15" s="3">
         <v>13.8</v>
@@ -9560,11 +9575,11 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D16" s="3">
         <v>20.55</v>
@@ -9586,59 +9601,58 @@
       </c>
       <c r="J16" s="5"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="3" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="D17" s="3">
+        <v>12</v>
+      </c>
+      <c r="E17" s="3">
+        <v>10</v>
+      </c>
+      <c r="F17" s="3">
+        <v>32.4</v>
+      </c>
+      <c r="G17" s="3">
         <v>15</v>
       </c>
-      <c r="E17" s="3">
-        <v>14.15</v>
-      </c>
-      <c r="F17" s="3">
-        <v>41</v>
-      </c>
-      <c r="G17" s="3">
-        <v>30</v>
-      </c>
       <c r="H17" s="3">
-        <v>45.5</v>
+        <v>32</v>
       </c>
       <c r="I17" s="15">
-        <v>5.5E-2</v>
-      </c>
-      <c r="J17" s="5"/>
+        <v>1.6E-2</v>
+      </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D18" s="3">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E18" s="3">
-        <v>6</v>
+        <v>14.15</v>
       </c>
       <c r="F18" s="3">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="G18" s="3">
-        <v>24.5</v>
+        <v>30</v>
       </c>
       <c r="H18" s="3">
-        <v>16</v>
+        <v>45.5</v>
       </c>
       <c r="I18" s="15">
-        <v>1.1368E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="J18" s="5"/>
     </row>
@@ -9651,387 +9665,384 @@
         <v>19</v>
       </c>
       <c r="D19" s="3">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="E19" s="3">
-        <v>8.85</v>
+        <v>6</v>
       </c>
       <c r="F19" s="3">
-        <v>31.5</v>
+        <v>29</v>
       </c>
       <c r="G19" s="3">
-        <v>27.5</v>
+        <v>24.5</v>
       </c>
       <c r="H19" s="3">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="I19" s="15">
-        <v>0.04</v>
-      </c>
-      <c r="J19" s="3"/>
+        <v>1.1368E-2</v>
+      </c>
+      <c r="J19" s="5"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A20" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="6"/>
+      <c r="A20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="7"/>
       <c r="C20" s="3" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D20" s="3">
-        <v>6.5</v>
+        <v>9.6</v>
       </c>
       <c r="E20" s="3">
-        <v>5</v>
+        <v>8.85</v>
       </c>
       <c r="F20" s="3">
-        <v>33.5</v>
+        <v>31.5</v>
       </c>
       <c r="G20" s="3">
-        <v>29</v>
+        <v>27.5</v>
       </c>
       <c r="H20" s="3">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="I20" s="15">
-        <v>3.1088000000000001E-2</v>
+        <v>0.04</v>
       </c>
       <c r="J20" s="3"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D21" s="3">
-        <v>8.3000000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="E21" s="3">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="F21" s="3">
-        <v>38</v>
+        <v>33.5</v>
       </c>
       <c r="G21" s="3">
-        <v>33.5</v>
+        <v>29</v>
       </c>
       <c r="H21" s="3">
-        <v>28.5</v>
+        <v>32</v>
       </c>
       <c r="I21" s="15">
-        <v>3.5999999999999997E-2</v>
+        <v>3.1088000000000001E-2</v>
       </c>
       <c r="J21" s="3"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D22" s="3">
-        <v>10.4</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="E22" s="3">
-        <v>9.3000000000000007</v>
+        <v>7.5</v>
       </c>
       <c r="F22" s="3">
-        <v>34.5</v>
+        <v>38</v>
       </c>
       <c r="G22" s="3">
-        <v>26.5</v>
+        <v>33.5</v>
       </c>
       <c r="H22" s="3">
-        <v>48</v>
+        <v>28.5</v>
       </c>
       <c r="I22" s="15">
-        <v>4.3999999999999997E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="J22" s="3"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D23" s="3">
-        <v>29.4</v>
+        <v>10.4</v>
       </c>
       <c r="E23" s="3">
-        <v>28</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="F23" s="3">
-        <v>45</v>
+        <v>34.5</v>
       </c>
       <c r="G23" s="3">
-        <v>41</v>
+        <v>26.5</v>
       </c>
       <c r="H23" s="3">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="I23" s="15">
-        <v>9.9629999999999996E-2</v>
+        <v>4.3999999999999997E-2</v>
       </c>
       <c r="J23" s="3"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="3" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D24" s="3">
-        <v>27</v>
+        <v>29.4</v>
       </c>
       <c r="E24" s="3">
-        <v>25.3</v>
+        <v>28</v>
       </c>
       <c r="F24" s="3">
-        <v>61.5</v>
+        <v>45</v>
       </c>
       <c r="G24" s="3">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H24" s="3">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="I24" s="15">
-        <v>9.9015000000000006E-2</v>
+        <v>9.9629999999999996E-2</v>
       </c>
       <c r="J24" s="3"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D25" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E25" s="3">
-        <v>19</v>
+        <v>25.3</v>
       </c>
       <c r="F25" s="3">
-        <v>42.5</v>
+        <v>61.5</v>
       </c>
       <c r="G25" s="3">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="H25" s="3">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="I25" s="15">
-        <v>6.6640000000000005E-2</v>
+        <v>9.9015000000000006E-2</v>
       </c>
       <c r="J25" s="3"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D26" s="3">
-        <v>12.75</v>
+        <v>20</v>
       </c>
       <c r="E26" s="3">
-        <v>11.2</v>
+        <v>19</v>
       </c>
       <c r="F26" s="3">
-        <v>37.5</v>
+        <v>42.5</v>
       </c>
       <c r="G26" s="3">
-        <v>28.2</v>
+        <v>32</v>
       </c>
       <c r="H26" s="3">
-        <v>34.799999999999997</v>
+        <v>49</v>
       </c>
       <c r="I26" s="15">
-        <v>3.6801E-2</v>
+        <v>6.6640000000000005E-2</v>
       </c>
       <c r="J26" s="3"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D27" s="3">
-        <v>13.8</v>
+        <v>12.75</v>
       </c>
       <c r="E27" s="3">
-        <v>12.8</v>
+        <v>11.2</v>
       </c>
       <c r="F27" s="3">
-        <v>58.5</v>
+        <v>37.5</v>
       </c>
       <c r="G27" s="3">
-        <v>31</v>
+        <v>28.2</v>
       </c>
       <c r="H27" s="3">
-        <v>51.2</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="I27" s="15">
-        <v>9.2851200000000009E-2</v>
+        <v>3.6801E-2</v>
       </c>
       <c r="J27" s="3"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B28" s="6"/>
-      <c r="C28" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="9">
-        <v>13.5</v>
-      </c>
-      <c r="E28" s="9">
-        <v>12.4</v>
-      </c>
-      <c r="F28" s="9">
-        <v>47.5</v>
-      </c>
-      <c r="G28" s="9">
-        <v>44.3</v>
-      </c>
-      <c r="H28" s="9">
-        <v>32.5</v>
-      </c>
-      <c r="I28" s="14">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
+      <c r="C28" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="3">
+        <v>13.8</v>
+      </c>
+      <c r="E28" s="3">
+        <v>12.8</v>
+      </c>
+      <c r="F28" s="3">
+        <v>58.5</v>
+      </c>
+      <c r="G28" s="3">
+        <v>31</v>
+      </c>
+      <c r="H28" s="3">
+        <v>51.2</v>
+      </c>
+      <c r="I28" s="15">
+        <v>9.2851200000000009E-2</v>
+      </c>
+      <c r="J28" s="3"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="9" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D29" s="9">
-        <v>15.3</v>
+        <v>13.5</v>
       </c>
       <c r="E29" s="9">
-        <v>13.95</v>
-      </c>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="14"/>
+        <v>12.4</v>
+      </c>
+      <c r="F29" s="9">
+        <v>47.5</v>
+      </c>
+      <c r="G29" s="9">
+        <v>44.3</v>
+      </c>
+      <c r="H29" s="9">
+        <v>32.5</v>
+      </c>
+      <c r="I29" s="14">
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D30" s="9">
-        <v>11</v>
+        <v>15.3</v>
       </c>
       <c r="E30" s="9">
-        <v>10</v>
-      </c>
-      <c r="F30" s="9">
-        <v>41.5</v>
-      </c>
-      <c r="G30" s="9">
-        <v>27.5</v>
-      </c>
-      <c r="H30" s="9">
-        <v>21</v>
-      </c>
-      <c r="I30" s="14">
-        <v>2.3966250000000001E-2</v>
-      </c>
+        <v>13.95</v>
+      </c>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="14"/>
       <c r="J30" s="6"/>
       <c r="K30" s="6"/>
       <c r="L30" s="6"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A31" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" s="3">
-        <v>15</v>
-      </c>
-      <c r="E31" s="3">
-        <v>14</v>
-      </c>
-      <c r="F31" s="3">
-        <v>63</v>
-      </c>
-      <c r="G31" s="3">
-        <v>32</v>
-      </c>
-      <c r="H31" s="3">
-        <v>41</v>
-      </c>
-      <c r="I31" s="15">
-        <v>8.2655999999999993E-2</v>
-      </c>
-      <c r="J31" s="18"/>
-      <c r="K31" s="18"/>
-      <c r="L31" s="18"/>
-      <c r="M31" s="18"/>
+      <c r="A31" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="9">
+        <v>11</v>
+      </c>
+      <c r="E31" s="9">
+        <v>10</v>
+      </c>
+      <c r="F31" s="9">
+        <v>41.5</v>
+      </c>
+      <c r="G31" s="9">
+        <v>27.5</v>
+      </c>
+      <c r="H31" s="9">
+        <v>21</v>
+      </c>
+      <c r="I31" s="14">
+        <v>2.3966250000000001E-2</v>
+      </c>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B32" s="7"/>
       <c r="C32" s="3" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="D32" s="3">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="E32" s="3">
-        <v>9.6999999999999993</v>
+        <v>14</v>
       </c>
       <c r="F32" s="3">
-        <v>37.5</v>
+        <v>63</v>
       </c>
       <c r="G32" s="3">
-        <v>30.5</v>
+        <v>32</v>
       </c>
       <c r="H32" s="3">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I32" s="15">
-        <v>5.2999999999999999E-2</v>
+        <v>8.2655999999999993E-2</v>
       </c>
       <c r="J32" s="18"/>
       <c r="K32" s="18"/>
@@ -10040,29 +10051,29 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="3" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="D33" s="3">
-        <v>10.72</v>
+        <v>10.5</v>
       </c>
       <c r="E33" s="3">
-        <v>9.7200000000000006</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="F33" s="3">
-        <v>28</v>
+        <v>37.5</v>
       </c>
       <c r="G33" s="3">
-        <v>28</v>
+        <v>30.5</v>
       </c>
       <c r="H33" s="3">
-        <v>34.5</v>
+        <v>46</v>
       </c>
       <c r="I33" s="15">
-        <v>2.7047999999999999E-2</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="J33" s="18"/>
       <c r="K33" s="18"/>
@@ -10071,29 +10082,29 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="3" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="D34" s="3">
-        <v>13</v>
+        <v>10.72</v>
       </c>
       <c r="E34" s="3">
-        <v>11</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="F34" s="3">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G34" s="3">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H34" s="3">
-        <v>39</v>
+        <v>34.5</v>
       </c>
       <c r="I34" s="15">
-        <v>0.03</v>
+        <v>2.7047999999999999E-2</v>
       </c>
       <c r="J34" s="18"/>
       <c r="K34" s="18"/>
@@ -10102,29 +10113,29 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="3" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="D35" s="3">
-        <v>11.4</v>
+        <v>13</v>
       </c>
       <c r="E35" s="3">
         <v>11</v>
       </c>
       <c r="F35" s="3">
-        <v>37.5</v>
+        <v>35</v>
       </c>
       <c r="G35" s="3">
-        <v>28.2</v>
+        <v>22</v>
       </c>
       <c r="H35" s="3">
-        <v>34.799999999999997</v>
+        <v>39</v>
       </c>
       <c r="I35" s="15">
-        <v>3.6801E-2</v>
+        <v>0.03</v>
       </c>
       <c r="J35" s="18"/>
       <c r="K35" s="18"/>
@@ -10133,29 +10144,29 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="3" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="D36" s="3">
-        <v>23</v>
+        <v>11.4</v>
       </c>
       <c r="E36" s="3">
-        <v>21.5</v>
+        <v>11</v>
       </c>
       <c r="F36" s="3">
-        <v>41.5</v>
+        <v>37.5</v>
       </c>
       <c r="G36" s="3">
-        <v>41.5</v>
+        <v>28.2</v>
       </c>
       <c r="H36" s="3">
-        <v>54.7</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="I36" s="15">
-        <v>9.4207075000000001E-2</v>
+        <v>3.6801E-2</v>
       </c>
       <c r="J36" s="18"/>
       <c r="K36" s="18"/>
@@ -10164,29 +10175,29 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="3" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="D37" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E37" s="3">
-        <v>23</v>
+        <v>21.5</v>
       </c>
       <c r="F37" s="3">
-        <v>51.5</v>
+        <v>41.5</v>
       </c>
       <c r="G37" s="3">
-        <v>33.5</v>
+        <v>41.5</v>
       </c>
       <c r="H37" s="3">
-        <v>60</v>
+        <v>54.7</v>
       </c>
       <c r="I37" s="15">
-        <v>0.104</v>
+        <v>9.4207075000000001E-2</v>
       </c>
       <c r="J37" s="18"/>
       <c r="K37" s="18"/>
@@ -10194,23 +10205,38 @@
       <c r="M37" s="18"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A38" s="18"/>
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
+      <c r="A38" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" s="7"/>
+      <c r="C38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="3">
+        <v>24</v>
+      </c>
+      <c r="E38" s="3">
+        <v>23</v>
+      </c>
+      <c r="F38" s="3">
+        <v>51.5</v>
+      </c>
+      <c r="G38" s="3">
+        <v>33.5</v>
+      </c>
+      <c r="H38" s="3">
+        <v>60</v>
+      </c>
+      <c r="I38" s="15">
+        <v>0.104</v>
+      </c>
       <c r="J38" s="18"/>
       <c r="K38" s="18"/>
       <c r="L38" s="18"/>
       <c r="M38" s="18"/>
     </row>
-    <row r="39" spans="1:13" ht="23" x14ac:dyDescent="0.35">
-      <c r="A39" s="20" t="s">
-        <v>71</v>
-      </c>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A39" s="18"/>
       <c r="B39" s="18"/>
       <c r="C39" s="18"/>
       <c r="D39" s="18"/>
@@ -10223,268 +10249,255 @@
       <c r="L39" s="18"/>
       <c r="M39" s="18"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A40" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="F40" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="G40" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="H40" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="I40" s="16" t="s">
-        <v>7</v>
-      </c>
+    <row r="40" spans="1:13" ht="23" x14ac:dyDescent="0.35">
+      <c r="A40" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
       <c r="J40" s="18"/>
       <c r="K40" s="18"/>
       <c r="L40" s="18"/>
       <c r="M40" s="18"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A41" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3">
-        <v>50.9</v>
-      </c>
-      <c r="G41" s="3">
-        <v>39.6</v>
-      </c>
-      <c r="H41" s="3">
-        <v>60</v>
-      </c>
-      <c r="I41" s="15">
-        <v>0.12093840000000002</v>
-      </c>
-      <c r="J41" s="6"/>
+      <c r="A41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="G41" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="H41" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="I41" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="18"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D42" s="3">
-        <v>27</v>
-      </c>
-      <c r="E42" s="3">
-        <v>24</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
       <c r="F42" s="3">
-        <v>55</v>
+        <v>50.9</v>
       </c>
       <c r="G42" s="3">
-        <v>33</v>
+        <v>39.6</v>
       </c>
       <c r="H42" s="3">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I42" s="15">
-        <v>0.12705</v>
+        <v>0.12093840000000002</v>
       </c>
       <c r="J42" s="6"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="9" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E43" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F43" s="3">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G43" s="3">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="H43" s="3">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="I43" s="15">
-        <v>0.11015999999999999</v>
+        <v>0.12705</v>
       </c>
       <c r="J43" s="6"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B44" s="6"/>
-      <c r="C44" s="9"/>
+      <c r="C44" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="D44" s="3">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E44" s="3">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="F44" s="3">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G44" s="3">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H44" s="3">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="I44" s="15">
-        <v>7.0223999999999995E-2</v>
+        <v>0.11015999999999999</v>
       </c>
       <c r="J44" s="6"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="B45" s="6"/>
-      <c r="C45" s="9" t="s">
-        <v>20</v>
-      </c>
+      <c r="C45" s="9"/>
       <c r="D45" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E45" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F45" s="3">
-        <v>46.5</v>
+        <v>38</v>
       </c>
       <c r="G45" s="3">
-        <v>36.5</v>
+        <v>56</v>
       </c>
       <c r="H45" s="3">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="I45" s="15">
-        <f>(F45*G45*H45)/1000000</f>
-        <v>9.3348749999999994E-2</v>
+        <v>7.0223999999999995E-2</v>
       </c>
       <c r="J45" s="6"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="9" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D46" s="3">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="E46" s="3">
-        <v>9.3000000000000007</v>
+        <v>5</v>
       </c>
       <c r="F46" s="3">
-        <v>36</v>
+        <v>46.5</v>
       </c>
       <c r="G46" s="3">
-        <v>28</v>
+        <v>36.5</v>
       </c>
       <c r="H46" s="3">
-        <v>33.5</v>
+        <v>55</v>
       </c>
       <c r="I46" s="15">
         <f>(F46*G46*H46)/1000000</f>
-        <v>3.3767999999999999E-2</v>
+        <v>9.3348749999999994E-2</v>
       </c>
       <c r="J46" s="6"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="9" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="D47" s="3">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="E47" s="3">
-        <v>5</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="F47" s="3">
-        <v>46.5</v>
+        <v>36</v>
       </c>
       <c r="G47" s="3">
-        <v>36.5</v>
+        <v>28</v>
       </c>
       <c r="H47" s="3">
-        <v>55</v>
+        <v>33.5</v>
       </c>
       <c r="I47" s="15">
         <f>(F47*G47*H47)/1000000</f>
-        <v>9.3348749999999994E-2</v>
+        <v>3.3767999999999999E-2</v>
       </c>
       <c r="J47" s="6"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="9" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="D48" s="3">
-        <v>10.3</v>
+        <v>7</v>
       </c>
       <c r="E48" s="3">
-        <v>9.6</v>
+        <v>5</v>
       </c>
       <c r="F48" s="3">
-        <v>49</v>
+        <v>46.5</v>
       </c>
       <c r="G48" s="3">
-        <v>27</v>
+        <v>36.5</v>
       </c>
       <c r="H48" s="3">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="I48" s="15">
         <f>(F48*G48*H48)/1000000</f>
-        <v>5.9534999999999998E-2</v>
+        <v>9.3348749999999994E-2</v>
       </c>
       <c r="J48" s="6"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" s="6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D49" s="3">
         <v>10.3</v>
@@ -10502,128 +10515,129 @@
         <v>45</v>
       </c>
       <c r="I49" s="15">
-        <f t="shared" ref="I49" si="0">(F49*G49*H49)/1000000</f>
+        <f>(F49*G49*H49)/1000000</f>
         <v>5.9534999999999998E-2</v>
       </c>
       <c r="J49" s="6"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="9" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="D50" s="3">
-        <v>10.72</v>
+        <v>10.3</v>
       </c>
       <c r="E50" s="3">
-        <v>9.7200000000000006</v>
+        <v>9.6</v>
       </c>
       <c r="F50" s="3">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="G50" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H50" s="3">
-        <v>34.5</v>
+        <v>45</v>
       </c>
       <c r="I50" s="15">
-        <v>2.7047999999999999E-2</v>
+        <f t="shared" ref="I50" si="0">(F50*G50*H50)/1000000</f>
+        <v>5.9534999999999998E-2</v>
       </c>
       <c r="J50" s="6"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D51" s="3">
-        <v>12.75</v>
+        <v>10.72</v>
       </c>
       <c r="E51" s="3">
-        <v>11.2</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="F51" s="3">
-        <v>37.5</v>
+        <v>28</v>
       </c>
       <c r="G51" s="3">
-        <v>28.2</v>
+        <v>28</v>
       </c>
       <c r="H51" s="3">
-        <v>34.799999999999997</v>
+        <v>34.5</v>
       </c>
       <c r="I51" s="15">
-        <v>3.6801E-2</v>
+        <v>2.7047999999999999E-2</v>
       </c>
       <c r="J51" s="6"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B52" s="6"/>
-      <c r="C52" s="9"/>
+      <c r="C52" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="D52" s="3">
-        <v>16</v>
+        <v>12.75</v>
       </c>
       <c r="E52" s="3">
-        <v>15</v>
+        <v>11.2</v>
       </c>
       <c r="F52" s="3">
-        <v>22</v>
+        <v>37.5</v>
       </c>
       <c r="G52" s="3">
-        <v>7.8</v>
+        <v>28.2</v>
       </c>
       <c r="H52" s="3">
-        <v>21</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="I52" s="15">
-        <v>9.3348749999999994E-2</v>
+        <v>3.6801E-2</v>
       </c>
       <c r="J52" s="6"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" s="6" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="B53" s="6"/>
-      <c r="C53" s="9" t="s">
-        <v>37</v>
-      </c>
+      <c r="C53" s="9"/>
       <c r="D53" s="3">
-        <v>10.3</v>
+        <v>16</v>
       </c>
       <c r="E53" s="3">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="F53" s="3">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="G53" s="3">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="H53" s="3">
-        <v>14.1</v>
+        <v>21</v>
       </c>
       <c r="I53" s="15">
-        <v>9.4E-2</v>
+        <v>9.3348749999999994E-2</v>
       </c>
       <c r="J53" s="6"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D54" s="3">
         <v>10.3</v>
@@ -10647,101 +10661,121 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="9" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="D55" s="3">
-        <v>15.6</v>
+        <v>10.3</v>
       </c>
       <c r="E55" s="3">
-        <v>14.6</v>
+        <v>9.6</v>
       </c>
       <c r="F55" s="3">
-        <v>54</v>
+        <v>21.8</v>
       </c>
       <c r="G55" s="3">
-        <v>30</v>
+        <v>5.6</v>
       </c>
       <c r="H55" s="3">
-        <v>44.5</v>
+        <v>14.1</v>
       </c>
       <c r="I55" s="15">
-        <f t="shared" ref="I55:I56" si="1">(F55*G55*H55)/1000000</f>
-        <v>7.2090000000000001E-2</v>
+        <v>9.4E-2</v>
       </c>
       <c r="J55" s="6"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="9" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="D56" s="3">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E56" s="3">
-        <v>19.2</v>
+        <v>14.6</v>
       </c>
       <c r="F56" s="3">
-        <v>48.5</v>
+        <v>54</v>
       </c>
       <c r="G56" s="3">
-        <v>40.5</v>
+        <v>30</v>
       </c>
       <c r="H56" s="3">
-        <v>42</v>
+        <v>44.5</v>
       </c>
       <c r="I56" s="15">
-        <f t="shared" si="1"/>
-        <v>8.2498500000000002E-2</v>
+        <f t="shared" ref="I56:I57" si="1">(F56*G56*H56)/1000000</f>
+        <v>7.2090000000000001E-2</v>
       </c>
       <c r="J56" s="6"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B57" s="6"/>
       <c r="C57" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D57" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E57" s="3">
-        <v>28</v>
+        <v>19.2</v>
       </c>
       <c r="F57" s="3">
-        <f>12*4</f>
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="G57" s="3">
-        <f>25.5*2</f>
-        <v>51</v>
+        <v>40.5</v>
       </c>
       <c r="H57" s="3">
-        <f>2.5*18</f>
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I57" s="15">
-        <f>(F57*G57*H57)/1000000</f>
-        <v>0.11015999999999999</v>
+        <f t="shared" si="1"/>
+        <v>8.2498500000000002E-2</v>
       </c>
       <c r="J57" s="6"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3"/>
-      <c r="I58" s="15"/>
+      <c r="A58" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B58" s="6"/>
+      <c r="C58" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D58" s="3">
+        <v>30</v>
+      </c>
+      <c r="E58" s="3">
+        <v>28</v>
+      </c>
+      <c r="F58" s="3">
+        <f>12*4</f>
+        <v>48</v>
+      </c>
+      <c r="G58" s="3">
+        <f>25.5*2</f>
+        <v>51</v>
+      </c>
+      <c r="H58" s="3">
+        <f>2.5*18</f>
+        <v>45</v>
+      </c>
+      <c r="I58" s="15">
+        <f>(F58*G58*H58)/1000000</f>
+        <v>0.11015999999999999</v>
+      </c>
+      <c r="J58" s="6"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D59" s="3"/>
@@ -10751,368 +10785,377 @@
       <c r="H59" s="3"/>
       <c r="I59" s="15"/>
     </row>
-    <row r="60" spans="1:10" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A60" s="19" t="s">
-        <v>88</v>
-      </c>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="15"/>
     </row>
-    <row r="61" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B61" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C61" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="E61" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="F61" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="G61" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="H61" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="I61" s="25" t="s">
-        <v>7</v>
+    <row r="61" spans="1:10" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="A61" s="19" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="62" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D62" s="8">
+      <c r="A62" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B62" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C62" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="E62" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="H62" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="I62" s="25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D63" s="8">
         <v>9.6</v>
       </c>
-      <c r="E62" s="8">
+      <c r="E63" s="8">
         <v>8.8000000000000007</v>
       </c>
-      <c r="I62" s="13"/>
+      <c r="I63" s="13"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A63" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D63">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A64" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D64">
         <v>25</v>
       </c>
-      <c r="E63">
+      <c r="E64">
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D64" s="8">
+    <row r="65" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D65" s="8">
         <v>12.55</v>
       </c>
-      <c r="E64" s="8">
+      <c r="E65" s="8">
         <v>11.45</v>
       </c>
-      <c r="I64" s="13"/>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A65" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D65">
-        <v>15.7</v>
-      </c>
-      <c r="E65">
-        <v>14.7</v>
-      </c>
+      <c r="I65" s="13"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D66">
-        <v>15.2</v>
+        <v>15.7</v>
       </c>
       <c r="E66">
-        <v>14.2</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="D67">
+        <v>15.2</v>
+      </c>
+      <c r="E67">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A68" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D68">
         <v>13.2</v>
       </c>
-      <c r="E67">
+      <c r="E68">
         <v>12.5</v>
       </c>
     </row>
-    <row r="68" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D68">
+    <row r="69" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D69">
         <v>18.86</v>
       </c>
-      <c r="E68">
+      <c r="E69">
         <v>17.239999999999998</v>
       </c>
-      <c r="I68" s="13"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A69" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D69" s="8">
-        <v>17.600000000000001</v>
-      </c>
-      <c r="E69" s="8">
-        <v>16.600000000000001</v>
-      </c>
+      <c r="I69" s="13"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D70">
-        <v>28.5</v>
-      </c>
-      <c r="E70">
-        <v>27</v>
+        <v>80</v>
+      </c>
+      <c r="D70" s="8">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="E70" s="8">
+        <v>16.600000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A71" s="6"/>
+      <c r="A71" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D71">
+        <v>28.5</v>
+      </c>
+      <c r="E71">
+        <v>27</v>
+      </c>
     </row>
-    <row r="72" spans="1:9" s="8" customFormat="1" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A72" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="C72" s="3"/>
-      <c r="I72" s="13"/>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A72" s="6"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A73" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B73" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C73" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D73" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="E73" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="F73" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="G73" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="H73" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="I73" s="25" t="s">
-        <v>7</v>
-      </c>
+    <row r="73" spans="1:9" s="8" customFormat="1" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="A73" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C73" s="3"/>
+      <c r="I73" s="13"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A74" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D74">
-        <v>11.8</v>
-      </c>
-      <c r="E74">
-        <v>11.6</v>
-      </c>
-      <c r="F74">
-        <v>28.4</v>
-      </c>
-      <c r="G74">
-        <v>31.6</v>
-      </c>
-      <c r="H74">
-        <v>30</v>
-      </c>
-      <c r="I74" s="13">
-        <v>2.7E-2</v>
+      <c r="A74" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B74" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C74" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="E74" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="F74" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="G74" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="H74" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="I74" s="25" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" s="6" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D75">
-        <v>12.75</v>
+        <v>11.8</v>
       </c>
       <c r="E75">
-        <v>11.2</v>
+        <v>11.6</v>
       </c>
       <c r="F75">
-        <v>37.5</v>
+        <v>28.4</v>
       </c>
       <c r="G75">
-        <v>28.2</v>
+        <v>31.6</v>
       </c>
       <c r="H75">
-        <v>34.799999999999997</v>
+        <v>30</v>
       </c>
       <c r="I75" s="13">
-        <v>3.6999999999999998E-2</v>
+        <v>2.7E-2</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" s="6" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="D76">
-        <v>12</v>
+        <v>12.75</v>
       </c>
       <c r="E76">
-        <v>11.23</v>
+        <v>11.2</v>
       </c>
       <c r="F76">
-        <v>36</v>
+        <v>37.5</v>
       </c>
       <c r="G76">
-        <v>27</v>
+        <v>28.2</v>
       </c>
       <c r="H76">
-        <v>27</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="I76" s="13">
-        <v>2.6244E-2</v>
+        <v>3.6999999999999998E-2</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="D77">
-        <v>12.75</v>
+        <v>12</v>
       </c>
       <c r="E77">
-        <v>11.2</v>
+        <v>11.23</v>
       </c>
       <c r="F77">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="G77">
-        <v>28.2</v>
+        <v>27</v>
       </c>
       <c r="H77">
-        <v>34.799999999999997</v>
+        <v>27</v>
       </c>
       <c r="I77" s="13">
-        <v>3.6999999999999998E-2</v>
+        <v>2.6244E-2</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" s="6" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="D78">
-        <v>11</v>
+        <v>12.75</v>
       </c>
       <c r="E78">
-        <v>13</v>
+        <v>11.2</v>
       </c>
       <c r="F78">
-        <v>35</v>
+        <v>37.5</v>
       </c>
       <c r="G78">
-        <v>22</v>
+        <v>28.2</v>
       </c>
       <c r="H78">
-        <v>39</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="I78" s="13">
-        <v>0.03</v>
+        <v>3.6999999999999998E-2</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" s="6" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="D79">
-        <v>9.5440000000000005</v>
+        <v>11</v>
       </c>
       <c r="E79">
-        <v>8.5440000000000005</v>
+        <v>13</v>
       </c>
       <c r="F79">
-        <v>44.8</v>
+        <v>35</v>
       </c>
       <c r="G79">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H79">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="I79" s="13">
-        <v>1.2999999999999999E-2</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A80" s="6"/>
+      <c r="A80" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D80">
+        <v>9.5440000000000005</v>
+      </c>
+      <c r="E80">
+        <v>8.5440000000000005</v>
+      </c>
+      <c r="F80">
+        <v>44.8</v>
+      </c>
+      <c r="G80">
+        <v>30</v>
+      </c>
+      <c r="H80">
+        <v>10</v>
+      </c>
+      <c r="I80" s="13">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A81" s="6"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="32" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11127,7 +11170,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A1" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -11136,7 +11179,7 @@
     </row>
     <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A2" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -11145,7 +11188,7 @@
     </row>
     <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A3" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -11154,7 +11197,7 @@
     </row>
     <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A4" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -11163,7 +11206,7 @@
     </row>
     <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A5" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -11172,7 +11215,7 @@
     </row>
     <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A6" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -11181,7 +11224,7 @@
     </row>
     <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A7" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -11190,7 +11233,7 @@
     </row>
     <row r="8" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A8" s="11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -11199,7 +11242,7 @@
     </row>
     <row r="9" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A9" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -11208,7 +11251,7 @@
     </row>
     <row r="10" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A10" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -11217,7 +11260,7 @@
     </row>
     <row r="11" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A11" s="11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -11226,7 +11269,7 @@
     </row>
     <row r="12" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A12" s="11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -11235,7 +11278,7 @@
     </row>
     <row r="13" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A13" s="11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -11244,7 +11287,7 @@
     </row>
     <row r="14" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A14" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -11253,7 +11296,7 @@
     </row>
     <row r="15" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A15" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -11262,7 +11305,7 @@
     </row>
     <row r="16" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A16" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -11271,7 +11314,7 @@
     </row>
     <row r="17" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A17" s="11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>

--- a/Case Size.xlsx
+++ b/Case Size.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ee11846ce882123f/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="297" documentId="8_{B5CB9DC2-2DBC-48FC-8A4C-3FED4FBFDA8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56518CD2-2572-42FA-B83D-418CBBC903D3}"/>
+  <xr:revisionPtr revIDLastSave="303" documentId="8_{B5CB9DC2-2DBC-48FC-8A4C-3FED4FBFDA8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5374F466-7400-4845-8231-FFC7EA51121C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{94297B88-8998-40EB-8FA5-F929672964CF}"/>
   </bookViews>
@@ -5737,7 +5737,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="134" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="134" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -5751,14 +5751,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -5782,7 +5780,6 @@
     <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -9167,7 +9164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{624BC790-9AE4-4E34-8AB5-C11F6DB95162}">
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="41.453125" bestFit="1" customWidth="1"/>
@@ -9178,17 +9175,15 @@
     <col min="6" max="6" width="14.81640625" customWidth="1"/>
     <col min="7" max="7" width="15.453125" customWidth="1"/>
     <col min="8" max="8" width="11.26953125" customWidth="1"/>
-    <col min="9" max="9" width="10.6328125" style="13" customWidth="1"/>
+    <col min="9" max="9" width="10.6328125" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.6">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.6">
+      <c r="A1" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="I1" s="13"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -9198,30 +9193,30 @@
       <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="7"/>
+      <c r="B3" s="6"/>
       <c r="C3" s="3" t="s">
         <v>18</v>
       </c>
@@ -9240,15 +9235,15 @@
       <c r="H3" s="3">
         <v>20</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="13">
         <v>0.02</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="7"/>
+      <c r="B4" s="6"/>
       <c r="C4" s="3" t="s">
         <v>19</v>
       </c>
@@ -9267,15 +9262,15 @@
       <c r="H4" s="3">
         <v>27.5</v>
       </c>
-      <c r="I4" s="15">
+      <c r="I4" s="13">
         <v>0.04</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="7"/>
+      <c r="B5" s="6"/>
       <c r="C5" s="3" t="s">
         <v>50</v>
       </c>
@@ -9294,15 +9289,15 @@
       <c r="H5" s="3">
         <v>54</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="7"/>
+      <c r="B6" s="6"/>
       <c r="C6" s="3" t="s">
         <v>11</v>
       </c>
@@ -9321,15 +9316,15 @@
       <c r="H6" s="3">
         <v>54</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="13">
         <v>0.09</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="7"/>
+      <c r="B7" s="6"/>
       <c r="C7" s="3" t="s">
         <v>9</v>
       </c>
@@ -9348,15 +9343,15 @@
       <c r="H7" s="3">
         <v>53.5</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="13">
         <v>0.08</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="7"/>
+      <c r="B8" s="6"/>
       <c r="C8" s="3" t="s">
         <v>18</v>
       </c>
@@ -9375,15 +9370,15 @@
       <c r="H8" s="3">
         <v>44</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="13">
         <v>0.05</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="7"/>
+      <c r="B9" s="6"/>
       <c r="C9" s="3" t="s">
         <v>51</v>
       </c>
@@ -9402,15 +9397,15 @@
       <c r="H9" s="3">
         <v>44.5</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I9" s="13">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="7"/>
+      <c r="B10" s="6"/>
       <c r="C10" s="3" t="s">
         <v>19</v>
       </c>
@@ -9429,15 +9424,15 @@
       <c r="H10" s="3">
         <v>45</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I10" s="13">
         <v>0.1</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="7"/>
+      <c r="B11" s="6"/>
       <c r="C11" s="3" t="s">
         <v>9</v>
       </c>
@@ -9456,16 +9451,15 @@
       <c r="H11" s="3">
         <v>53.5</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I11" s="13">
         <v>8.0851875000000004E-2</v>
       </c>
-      <c r="J11" s="5"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="7"/>
+      <c r="B12" s="6"/>
       <c r="C12" s="3" t="s">
         <v>11</v>
       </c>
@@ -9484,16 +9478,15 @@
       <c r="H12" s="3">
         <v>45</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="10">
         <v>0.06</v>
       </c>
-      <c r="J12" s="5"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="7"/>
+      <c r="B13" s="6"/>
       <c r="C13" s="3" t="s">
         <v>11</v>
       </c>
@@ -9512,16 +9505,15 @@
       <c r="H13" s="3">
         <v>45</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="J13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="7"/>
+      <c r="B14" s="6"/>
       <c r="C14" s="3" t="s">
         <v>15</v>
       </c>
@@ -9540,16 +9532,15 @@
       <c r="H14" s="3">
         <v>51.2</v>
       </c>
-      <c r="I14" s="15">
+      <c r="I14" s="13">
         <v>9.2851200000000009E-2</v>
       </c>
-      <c r="J14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="7"/>
+      <c r="B15" s="6"/>
       <c r="C15" s="3" t="s">
         <v>15</v>
       </c>
@@ -9568,16 +9559,15 @@
       <c r="H15" s="3">
         <v>51.2</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="13">
         <v>9.2851200000000009E-2</v>
       </c>
-      <c r="J15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="7"/>
+      <c r="B16" s="6"/>
       <c r="C16" s="3" t="s">
         <v>18</v>
       </c>
@@ -9596,16 +9586,15 @@
       <c r="H16" s="3">
         <v>49.5</v>
       </c>
-      <c r="I16" s="15">
+      <c r="I16" s="13">
         <v>0.06</v>
       </c>
-      <c r="J16" s="5"/>
     </row>
-    <row r="17" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="7"/>
+      <c r="B17" s="6"/>
       <c r="C17" s="3" t="s">
         <v>43</v>
       </c>
@@ -9624,15 +9613,15 @@
       <c r="H17" s="3">
         <v>32</v>
       </c>
-      <c r="I17" s="15">
+      <c r="I17" s="13">
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="7"/>
+      <c r="B18" s="6"/>
       <c r="C18" s="3" t="s">
         <v>19</v>
       </c>
@@ -9651,16 +9640,15 @@
       <c r="H18" s="3">
         <v>45.5</v>
       </c>
-      <c r="I18" s="15">
+      <c r="I18" s="13">
         <v>5.5E-2</v>
       </c>
-      <c r="J18" s="5"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="7"/>
+      <c r="B19" s="6"/>
       <c r="C19" s="3" t="s">
         <v>19</v>
       </c>
@@ -9679,16 +9667,15 @@
       <c r="H19" s="3">
         <v>16</v>
       </c>
-      <c r="I19" s="15">
+      <c r="I19" s="13">
         <v>1.1368E-2</v>
       </c>
-      <c r="J19" s="5"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A20" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="7"/>
+      <c r="B20" s="6"/>
       <c r="C20" s="3" t="s">
         <v>18</v>
       </c>
@@ -9707,16 +9694,16 @@
       <c r="H20" s="3">
         <v>45</v>
       </c>
-      <c r="I20" s="15">
+      <c r="I20" s="13">
         <v>0.04</v>
       </c>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A21" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B21" s="6"/>
+      <c r="B21" s="5"/>
       <c r="C21" s="3" t="s">
         <v>23</v>
       </c>
@@ -9735,16 +9722,16 @@
       <c r="H21" s="3">
         <v>32</v>
       </c>
-      <c r="I21" s="15">
+      <c r="I21" s="13">
         <v>3.1088000000000001E-2</v>
       </c>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A22" s="6" t="s">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A22" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="6"/>
+      <c r="B22" s="5"/>
       <c r="C22" s="3" t="s">
         <v>25</v>
       </c>
@@ -9763,16 +9750,16 @@
       <c r="H22" s="3">
         <v>28.5</v>
       </c>
-      <c r="I22" s="15">
+      <c r="I22" s="13">
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A23" s="6" t="s">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A23" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="6"/>
+      <c r="B23" s="5"/>
       <c r="C23" s="3" t="s">
         <v>26</v>
       </c>
@@ -9791,16 +9778,16 @@
       <c r="H23" s="3">
         <v>48</v>
       </c>
-      <c r="I23" s="15">
+      <c r="I23" s="13">
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A24" s="6" t="s">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A24" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="6"/>
+      <c r="B24" s="5"/>
       <c r="C24" s="3" t="s">
         <v>11</v>
       </c>
@@ -9819,16 +9806,16 @@
       <c r="H24" s="3">
         <v>54</v>
       </c>
-      <c r="I24" s="15">
+      <c r="I24" s="13">
         <v>9.9629999999999996E-2</v>
       </c>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A25" s="6" t="s">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A25" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="6"/>
+      <c r="B25" s="5"/>
       <c r="C25" s="3" t="s">
         <v>28</v>
       </c>
@@ -9847,16 +9834,16 @@
       <c r="H25" s="3">
         <v>35</v>
       </c>
-      <c r="I25" s="15">
+      <c r="I25" s="13">
         <v>9.9015000000000006E-2</v>
       </c>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A26" s="6" t="s">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A26" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="6"/>
+      <c r="B26" s="5"/>
       <c r="C26" s="3" t="s">
         <v>19</v>
       </c>
@@ -9875,16 +9862,16 @@
       <c r="H26" s="3">
         <v>49</v>
       </c>
-      <c r="I26" s="15">
+      <c r="I26" s="13">
         <v>6.6640000000000005E-2</v>
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A27" s="6" t="s">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="6"/>
+      <c r="B27" s="5"/>
       <c r="C27" s="3" t="s">
         <v>31</v>
       </c>
@@ -9903,16 +9890,16 @@
       <c r="H27" s="3">
         <v>34.799999999999997</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="13">
         <v>3.6801E-2</v>
       </c>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A28" s="6" t="s">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A28" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="6"/>
+      <c r="B28" s="5"/>
       <c r="C28" s="3" t="s">
         <v>15</v>
       </c>
@@ -9931,98 +9918,98 @@
       <c r="H28" s="3">
         <v>51.2</v>
       </c>
-      <c r="I28" s="15">
+      <c r="I28" s="13">
         <v>9.2851200000000009E-2</v>
       </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A29" s="6" t="s">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A29" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="9" t="s">
+      <c r="B29" s="5"/>
+      <c r="C29" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="7">
         <v>13.5</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="7">
         <v>12.4</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="7">
         <v>47.5</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="7">
         <v>44.3</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="7">
         <v>32.5</v>
       </c>
-      <c r="I29" s="14">
+      <c r="I29" s="12">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A30" s="6" t="s">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A30" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="9" t="s">
+      <c r="B30" s="5"/>
+      <c r="C30" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="7">
         <v>15.3</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="7">
         <v>13.95</v>
       </c>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A31" s="6" t="s">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A31" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="9" t="s">
+      <c r="B31" s="5"/>
+      <c r="C31" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="7">
         <v>11</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="7">
         <v>10</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F31" s="7">
         <v>41.5</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="7">
         <v>27.5</v>
       </c>
-      <c r="H31" s="9">
+      <c r="H31" s="7">
         <v>21</v>
       </c>
-      <c r="I31" s="14">
+      <c r="I31" s="12">
         <v>2.3966250000000001E-2</v>
       </c>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A32" s="7" t="s">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A32" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="7"/>
+      <c r="B32" s="6"/>
       <c r="C32" s="3" t="s">
         <v>11</v>
       </c>
@@ -10041,19 +10028,15 @@
       <c r="H32" s="3">
         <v>41</v>
       </c>
-      <c r="I32" s="15">
+      <c r="I32" s="13">
         <v>8.2655999999999993E-2</v>
       </c>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A33" s="7" t="s">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="7"/>
+      <c r="B33" s="6"/>
       <c r="C33" s="3" t="s">
         <v>40</v>
       </c>
@@ -10072,19 +10055,15 @@
       <c r="H33" s="3">
         <v>46</v>
       </c>
-      <c r="I33" s="15">
+      <c r="I33" s="13">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="J33" s="18"/>
-      <c r="K33" s="18"/>
-      <c r="L33" s="18"/>
-      <c r="M33" s="18"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A34" s="7" t="s">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="7"/>
+      <c r="B34" s="6"/>
       <c r="C34" s="3" t="s">
         <v>18</v>
       </c>
@@ -10103,19 +10082,15 @@
       <c r="H34" s="3">
         <v>34.5</v>
       </c>
-      <c r="I34" s="15">
+      <c r="I34" s="13">
         <v>2.7047999999999999E-2</v>
       </c>
-      <c r="J34" s="18"/>
-      <c r="K34" s="18"/>
-      <c r="L34" s="18"/>
-      <c r="M34" s="18"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A35" s="7" t="s">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="7"/>
+      <c r="B35" s="6"/>
       <c r="C35" s="3" t="s">
         <v>43</v>
       </c>
@@ -10134,19 +10109,15 @@
       <c r="H35" s="3">
         <v>39</v>
       </c>
-      <c r="I35" s="15">
+      <c r="I35" s="13">
         <v>0.03</v>
       </c>
-      <c r="J35" s="18"/>
-      <c r="K35" s="18"/>
-      <c r="L35" s="18"/>
-      <c r="M35" s="18"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A36" s="7" t="s">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B36" s="7"/>
+      <c r="B36" s="6"/>
       <c r="C36" s="3" t="s">
         <v>18</v>
       </c>
@@ -10165,19 +10136,15 @@
       <c r="H36" s="3">
         <v>34.799999999999997</v>
       </c>
-      <c r="I36" s="15">
+      <c r="I36" s="13">
         <v>3.6801E-2</v>
       </c>
-      <c r="J36" s="18"/>
-      <c r="K36" s="18"/>
-      <c r="L36" s="18"/>
-      <c r="M36" s="18"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A37" s="7" t="s">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="7"/>
+      <c r="B37" s="6"/>
       <c r="C37" s="3" t="s">
         <v>47</v>
       </c>
@@ -10196,19 +10163,15 @@
       <c r="H37" s="3">
         <v>54.7</v>
       </c>
-      <c r="I37" s="15">
+      <c r="I37" s="13">
         <v>9.4207075000000001E-2</v>
       </c>
-      <c r="J37" s="18"/>
-      <c r="K37" s="18"/>
-      <c r="L37" s="18"/>
-      <c r="M37" s="18"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A38" s="7" t="s">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A38" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="7"/>
+      <c r="B38" s="6"/>
       <c r="C38" s="3" t="s">
         <v>19</v>
       </c>
@@ -10227,45 +10190,20 @@
       <c r="H38" s="3">
         <v>60</v>
       </c>
-      <c r="I38" s="15">
+      <c r="I38" s="13">
         <v>0.104</v>
       </c>
-      <c r="J38" s="18"/>
-      <c r="K38" s="18"/>
-      <c r="L38" s="18"/>
-      <c r="M38" s="18"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A39" s="18"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="J39" s="18"/>
-      <c r="K39" s="18"/>
-      <c r="L39" s="18"/>
-      <c r="M39" s="18"/>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C39"/>
     </row>
-    <row r="40" spans="1:13" ht="23" x14ac:dyDescent="0.35">
-      <c r="A40" s="20" t="s">
+    <row r="40" spans="1:10" ht="23" x14ac:dyDescent="0.35">
+      <c r="A40" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="B40" s="18"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
-      <c r="J40" s="18"/>
-      <c r="K40" s="18"/>
-      <c r="L40" s="18"/>
-      <c r="M40" s="18"/>
+      <c r="C40"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>0</v>
       </c>
@@ -10275,35 +10213,31 @@
       <c r="C41" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="D41" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="E41" s="17" t="s">
+      <c r="E41" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="F41" s="17" t="s">
+      <c r="F41" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="G41" s="17" t="s">
+      <c r="G41" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="H41" s="17" t="s">
+      <c r="H41" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I41" s="16" t="s">
+      <c r="I41" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J41" s="18"/>
-      <c r="K41" s="18"/>
-      <c r="L41" s="18"/>
-      <c r="M41" s="18"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A42" s="6" t="s">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A42" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="9" t="s">
+      <c r="B42" s="5"/>
+      <c r="C42" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3"/>
@@ -10317,17 +10251,17 @@
       <c r="H42" s="3">
         <v>60</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="13">
         <v>0.12093840000000002</v>
       </c>
-      <c r="J42" s="6"/>
+      <c r="J42" s="5"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A43" s="6" t="s">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A43" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="9" t="s">
+      <c r="B43" s="5"/>
+      <c r="C43" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
@@ -10345,17 +10279,17 @@
       <c r="H43" s="3">
         <v>70</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="13">
         <v>0.12705</v>
       </c>
-      <c r="J43" s="6"/>
+      <c r="J43" s="5"/>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A44" s="6" t="s">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A44" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B44" s="6"/>
-      <c r="C44" s="9" t="s">
+      <c r="B44" s="5"/>
+      <c r="C44" s="7" t="s">
         <v>70</v>
       </c>
       <c r="D44" s="3">
@@ -10373,17 +10307,17 @@
       <c r="H44" s="3">
         <v>45</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="13">
         <v>0.11015999999999999</v>
       </c>
-      <c r="J44" s="6"/>
+      <c r="J44" s="5"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A45" s="6" t="s">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A45" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B45" s="6"/>
-      <c r="C45" s="9"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="7"/>
       <c r="D45" s="3">
         <v>8</v>
       </c>
@@ -10399,17 +10333,17 @@
       <c r="H45" s="3">
         <v>33</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="13">
         <v>7.0223999999999995E-2</v>
       </c>
-      <c r="J45" s="6"/>
+      <c r="J45" s="5"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A46" s="6" t="s">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A46" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B46" s="6"/>
-      <c r="C46" s="9" t="s">
+      <c r="B46" s="5"/>
+      <c r="C46" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D46" s="3">
@@ -10427,18 +10361,18 @@
       <c r="H46" s="3">
         <v>55</v>
       </c>
-      <c r="I46" s="15">
+      <c r="I46" s="13">
         <f>(F46*G46*H46)/1000000</f>
         <v>9.3348749999999994E-2</v>
       </c>
-      <c r="J46" s="6"/>
+      <c r="J46" s="5"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A47" s="6" t="s">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A47" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B47" s="6"/>
-      <c r="C47" s="9" t="s">
+      <c r="B47" s="5"/>
+      <c r="C47" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D47" s="3">
@@ -10456,18 +10390,18 @@
       <c r="H47" s="3">
         <v>33.5</v>
       </c>
-      <c r="I47" s="15">
+      <c r="I47" s="13">
         <f>(F47*G47*H47)/1000000</f>
         <v>3.3767999999999999E-2</v>
       </c>
-      <c r="J47" s="6"/>
+      <c r="J47" s="5"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A48" s="6" t="s">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A48" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B48" s="6"/>
-      <c r="C48" s="9" t="s">
+      <c r="B48" s="5"/>
+      <c r="C48" s="7" t="s">
         <v>70</v>
       </c>
       <c r="D48" s="3">
@@ -10485,18 +10419,18 @@
       <c r="H48" s="3">
         <v>55</v>
       </c>
-      <c r="I48" s="15">
+      <c r="I48" s="13">
         <f>(F48*G48*H48)/1000000</f>
         <v>9.3348749999999994E-2</v>
       </c>
-      <c r="J48" s="6"/>
+      <c r="J48" s="5"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B49" s="6"/>
-      <c r="C49" s="9" t="s">
+      <c r="B49" s="5"/>
+      <c r="C49" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D49" s="3">
@@ -10514,18 +10448,18 @@
       <c r="H49" s="3">
         <v>45</v>
       </c>
-      <c r="I49" s="15">
+      <c r="I49" s="13">
         <f>(F49*G49*H49)/1000000</f>
         <v>5.9534999999999998E-2</v>
       </c>
-      <c r="J49" s="6"/>
+      <c r="J49" s="5"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B50" s="6"/>
-      <c r="C50" s="9" t="s">
+      <c r="B50" s="5"/>
+      <c r="C50" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D50" s="3">
@@ -10543,18 +10477,18 @@
       <c r="H50" s="3">
         <v>45</v>
       </c>
-      <c r="I50" s="15">
+      <c r="I50" s="13">
         <f t="shared" ref="I50" si="0">(F50*G50*H50)/1000000</f>
         <v>5.9534999999999998E-2</v>
       </c>
-      <c r="J50" s="6"/>
+      <c r="J50" s="5"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="9" t="s">
+      <c r="B51" s="5"/>
+      <c r="C51" s="7" t="s">
         <v>71</v>
       </c>
       <c r="D51" s="3">
@@ -10572,17 +10506,17 @@
       <c r="H51" s="3">
         <v>34.5</v>
       </c>
-      <c r="I51" s="15">
+      <c r="I51" s="13">
         <v>2.7047999999999999E-2</v>
       </c>
-      <c r="J51" s="6"/>
+      <c r="J51" s="5"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B52" s="6"/>
-      <c r="C52" s="9" t="s">
+      <c r="B52" s="5"/>
+      <c r="C52" s="7" t="s">
         <v>72</v>
       </c>
       <c r="D52" s="3">
@@ -10600,17 +10534,17 @@
       <c r="H52" s="3">
         <v>34.799999999999997</v>
       </c>
-      <c r="I52" s="15">
+      <c r="I52" s="13">
         <v>3.6801E-2</v>
       </c>
-      <c r="J52" s="6"/>
+      <c r="J52" s="5"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B53" s="6"/>
-      <c r="C53" s="9"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="7"/>
       <c r="D53" s="3">
         <v>16</v>
       </c>
@@ -10626,17 +10560,17 @@
       <c r="H53" s="3">
         <v>21</v>
       </c>
-      <c r="I53" s="15">
+      <c r="I53" s="13">
         <v>9.3348749999999994E-2</v>
       </c>
-      <c r="J53" s="6"/>
+      <c r="J53" s="5"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B54" s="6"/>
-      <c r="C54" s="9" t="s">
+      <c r="B54" s="5"/>
+      <c r="C54" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D54" s="3">
@@ -10654,17 +10588,17 @@
       <c r="H54" s="3">
         <v>14.1</v>
       </c>
-      <c r="I54" s="15">
+      <c r="I54" s="13">
         <v>9.4E-2</v>
       </c>
-      <c r="J54" s="6"/>
+      <c r="J54" s="5"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B55" s="6"/>
-      <c r="C55" s="9" t="s">
+      <c r="B55" s="5"/>
+      <c r="C55" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D55" s="3">
@@ -10682,17 +10616,17 @@
       <c r="H55" s="3">
         <v>14.1</v>
       </c>
-      <c r="I55" s="15">
+      <c r="I55" s="13">
         <v>9.4E-2</v>
       </c>
-      <c r="J55" s="6"/>
+      <c r="J55" s="5"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B56" s="6"/>
-      <c r="C56" s="9" t="s">
+      <c r="B56" s="5"/>
+      <c r="C56" s="7" t="s">
         <v>51</v>
       </c>
       <c r="D56" s="3">
@@ -10710,18 +10644,18 @@
       <c r="H56" s="3">
         <v>44.5</v>
       </c>
-      <c r="I56" s="15">
+      <c r="I56" s="13">
         <f t="shared" ref="I56:I57" si="1">(F56*G56*H56)/1000000</f>
         <v>7.2090000000000001E-2</v>
       </c>
-      <c r="J56" s="6"/>
+      <c r="J56" s="5"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B57" s="6"/>
-      <c r="C57" s="9" t="s">
+      <c r="B57" s="5"/>
+      <c r="C57" s="7" t="s">
         <v>73</v>
       </c>
       <c r="D57" s="3">
@@ -10739,18 +10673,18 @@
       <c r="H57" s="3">
         <v>42</v>
       </c>
-      <c r="I57" s="15">
+      <c r="I57" s="13">
         <f t="shared" si="1"/>
         <v>8.2498500000000002E-2</v>
       </c>
-      <c r="J57" s="6"/>
+      <c r="J57" s="5"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B58" s="6"/>
-      <c r="C58" s="9" t="s">
+      <c r="B58" s="5"/>
+      <c r="C58" s="7" t="s">
         <v>70</v>
       </c>
       <c r="D58" s="3">
@@ -10771,11 +10705,11 @@
         <f>2.5*18</f>
         <v>45</v>
       </c>
-      <c r="I58" s="15">
+      <c r="I58" s="13">
         <f>(F58*G58*H58)/1000000</f>
         <v>0.11015999999999999</v>
       </c>
-      <c r="J58" s="6"/>
+      <c r="J58" s="5"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D59" s="3"/>
@@ -10783,7 +10717,7 @@
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
-      <c r="I59" s="15"/>
+      <c r="I59" s="13"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D60" s="3"/>
@@ -10791,59 +10725,58 @@
       <c r="F60" s="3"/>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
-      <c r="I60" s="15"/>
+      <c r="I60" s="13"/>
     </row>
     <row r="61" spans="1:10" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A61" s="19" t="s">
+      <c r="A61" s="16" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="62" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="21" t="s">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A62" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B62" s="22" t="s">
+      <c r="B62" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C62" s="23" t="s">
+      <c r="C62" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="D62" s="24" t="s">
+      <c r="D62" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E62" s="24" t="s">
+      <c r="E62" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F62" s="24" t="s">
+      <c r="F62" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="G62" s="24" t="s">
+      <c r="G62" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="H62" s="24" t="s">
+      <c r="H62" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="I62" s="25" t="s">
+      <c r="I62" s="22" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="6" t="s">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A63" s="5" t="s">
         <v>74</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D63" s="8">
+      <c r="D63">
         <v>9.6</v>
       </c>
-      <c r="E63" s="8">
+      <c r="E63">
         <v>8.8000000000000007</v>
       </c>
-      <c r="I63" s="13"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="5" t="s">
         <v>74</v>
       </c>
       <c r="C64" s="3" t="s">
@@ -10856,23 +10789,22 @@
         <v>24</v>
       </c>
     </row>
-    <row r="65" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="6" t="s">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A65" s="5" t="s">
         <v>75</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D65" s="8">
+      <c r="D65">
         <v>12.55</v>
       </c>
-      <c r="E65" s="8">
+      <c r="E65">
         <v>11.45</v>
       </c>
-      <c r="I65" s="13"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="5" t="s">
         <v>75</v>
       </c>
       <c r="C66" s="3" t="s">
@@ -10886,7 +10818,7 @@
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="5" t="s">
         <v>76</v>
       </c>
       <c r="C67" s="3" t="s">
@@ -10900,7 +10832,7 @@
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="5" t="s">
         <v>77</v>
       </c>
       <c r="C68" s="3" t="s">
@@ -10913,8 +10845,8 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="69" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="6" t="s">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A69" s="5" t="s">
         <v>78</v>
       </c>
       <c r="C69" s="3" t="s">
@@ -10926,24 +10858,23 @@
       <c r="E69">
         <v>17.239999999999998</v>
       </c>
-      <c r="I69" s="13"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="5" t="s">
         <v>78</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D70" s="8">
+      <c r="D70">
         <v>17.600000000000001</v>
       </c>
-      <c r="E70" s="8">
+      <c r="E70">
         <v>16.600000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="5" t="s">
         <v>79</v>
       </c>
       <c r="C71" s="3" t="s">
@@ -10957,46 +10888,44 @@
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A72" s="6"/>
+      <c r="A72" s="5"/>
     </row>
-    <row r="73" spans="1:9" s="8" customFormat="1" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A73" s="19" t="s">
+    <row r="73" spans="1:9" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="A73" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C73" s="3"/>
-      <c r="I73" s="13"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A74" s="21" t="s">
+      <c r="A74" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B74" s="22" t="s">
+      <c r="B74" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C74" s="23" t="s">
+      <c r="C74" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="D74" s="24" t="s">
+      <c r="D74" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E74" s="24" t="s">
+      <c r="E74" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F74" s="24" t="s">
+      <c r="F74" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="G74" s="24" t="s">
+      <c r="G74" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="H74" s="24" t="s">
+      <c r="H74" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="I74" s="25" t="s">
+      <c r="I74" s="22" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A75" s="6" t="s">
+      <c r="A75" s="5" t="s">
         <v>88</v>
       </c>
       <c r="C75" s="3" t="s">
@@ -11017,12 +10946,12 @@
       <c r="H75">
         <v>30</v>
       </c>
-      <c r="I75" s="13">
+      <c r="I75" s="11">
         <v>2.7E-2</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A76" s="6" t="s">
+      <c r="A76" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C76" s="3" t="s">
@@ -11043,12 +10972,12 @@
       <c r="H76">
         <v>34.799999999999997</v>
       </c>
-      <c r="I76" s="13">
+      <c r="I76" s="11">
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A77" s="6" t="s">
+      <c r="A77" s="5" t="s">
         <v>89</v>
       </c>
       <c r="C77" s="3" t="s">
@@ -11069,12 +10998,12 @@
       <c r="H77">
         <v>27</v>
       </c>
-      <c r="I77" s="13">
+      <c r="I77" s="11">
         <v>2.6244E-2</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A78" s="6" t="s">
+      <c r="A78" s="5" t="s">
         <v>90</v>
       </c>
       <c r="C78" s="3" t="s">
@@ -11095,12 +11024,12 @@
       <c r="H78">
         <v>34.799999999999997</v>
       </c>
-      <c r="I78" s="13">
+      <c r="I78" s="11">
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A79" s="6" t="s">
+      <c r="A79" s="5" t="s">
         <v>42</v>
       </c>
       <c r="C79" s="3" t="s">
@@ -11121,12 +11050,12 @@
       <c r="H79">
         <v>39</v>
       </c>
-      <c r="I79" s="13">
+      <c r="I79" s="11">
         <v>0.03</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A80" s="6" t="s">
+      <c r="A80" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C80" s="3" t="s">
@@ -11147,12 +11076,12 @@
       <c r="H80">
         <v>10</v>
       </c>
-      <c r="I80" s="13">
+      <c r="I80" s="11">
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A81" s="6"/>
+      <c r="A81" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="32" type="noConversion"/>
@@ -11169,157 +11098,157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
     </row>
     <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
     </row>
     <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
     </row>
-    <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A4" s="11" t="s">
+    <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
     </row>
     <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
     </row>
     <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
     </row>
     <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
     </row>
-    <row r="9" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A9" s="11" t="s">
+    <row r="9" spans="1:5" ht="16.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
     </row>
-    <row r="10" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A10" s="11" t="s">
+    <row r="10" spans="1:5" ht="16.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
     </row>
-    <row r="11" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A11" s="11" t="s">
+    <row r="11" spans="1:5" ht="16.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
     </row>
-    <row r="12" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A12" s="11" t="s">
+    <row r="12" spans="1:5" ht="16.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
     </row>
-    <row r="13" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A13" s="11" t="s">
+    <row r="13" spans="1:5" ht="16.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
     </row>
-    <row r="14" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A14" s="11" t="s">
+    <row r="14" spans="1:5" ht="16.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
     </row>
-    <row r="15" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A15" s="11" t="s">
+    <row r="15" spans="1:5" ht="16.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
     </row>
-    <row r="16" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A16" s="11" t="s">
+    <row r="16" spans="1:5" ht="16.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
     </row>
-    <row r="17" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A17" s="11" t="s">
+    <row r="17" spans="1:5" ht="16.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
